--- a/BOSS.DE.xlsx
+++ b/BOSS.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729D13D3-0DEB-402E-BE4F-123D264156DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2AE8AE-882C-45B3-9B5F-216374AD629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{09B18DE7-4EEF-4A72-AC57-80486CCDDA74}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{09B18DE7-4EEF-4A72-AC57-80486CCDDA74}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <author>tc={D81B57CA-BD4B-4035-AE68-E24052A657A2}</author>
   </authors>
   <commentList>
-    <comment ref="L21" authorId="0" shapeId="0" xr:uid="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
+    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="81">
   <si>
     <t>Hugo Boss</t>
   </si>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>Asia Pacific Stores</t>
-  </si>
-  <si>
-    <t>Freestanding retail stores</t>
   </si>
   <si>
     <t>Boss Meanswear</t>
@@ -296,14 +293,19 @@
   <si>
     <t>Own Retail Stores</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>There of freestanding retail stores</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -398,13 +400,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -428,16 +430,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>42862</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>138113</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -452,8 +454,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9267825" y="0"/>
-          <a:ext cx="14287" cy="8362950"/>
+          <a:off x="9863137" y="33338"/>
+          <a:ext cx="14287" cy="8201025"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -802,7 +804,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="L21" dT="2025-05-06T11:33:50.96" personId="{BC3090F9-DCFB-461E-938B-BB97A04862C6}" id="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
+  <threadedComment ref="L20" dT="2025-05-06T11:33:50.96" personId="{BC3090F9-DCFB-461E-938B-BB97A04862C6}" id="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
     <text>Consensus of 4 analysts</text>
   </threadedComment>
 </ThreadedComments>
@@ -830,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>36.520000000000003</v>
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -838,9 +840,9 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="K3" s="14" t="s">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -853,7 +855,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>2571.0080000000003</v>
+        <v>2505.286971</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -864,10 +866,9 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <f>106+46</f>
-        <v>152</v>
-      </c>
-      <c r="K5" s="14" t="s">
+        <v>343.12599999999998</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -876,10 +877,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <f>284+62</f>
-        <v>346</v>
-      </c>
-      <c r="K6" s="14" t="s">
+        <f>93.258+202.512</f>
+        <v>295.77</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -889,12 +890,12 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>2765.0080000000003</v>
+        <v>2457.9309710000002</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J9" s="2">
         <v>1924</v>
@@ -902,7 +903,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J10" s="3">
         <v>18376</v>
@@ -910,21 +911,21 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -937,7 +938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20D4061-CFF8-435B-9C35-BFCD41DEF5B1}">
-  <dimension ref="A1:BI218"/>
+  <dimension ref="A1:BI217"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -976,34 +977,37 @@
         <v>18</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="P2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>67</v>
+      <c r="V2" s="13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.2">
@@ -1052,7 +1056,10 @@
       <c r="M3" s="7">
         <v>558</v>
       </c>
-      <c r="N3" s="7"/>
+      <c r="N3" s="7">
+        <f>+V3</f>
+        <v>540</v>
+      </c>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
@@ -1068,7 +1075,9 @@
       <c r="U3" s="7">
         <v>572</v>
       </c>
-      <c r="V3" s="7"/>
+      <c r="V3" s="7">
+        <v>540</v>
+      </c>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -1141,7 +1150,10 @@
       <c r="M4" s="7">
         <v>559</v>
       </c>
-      <c r="N4" s="7"/>
+      <c r="N4" s="7">
+        <f t="shared" ref="N4:N7" si="1">+V4</f>
+        <v>558</v>
+      </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
@@ -1157,7 +1169,9 @@
       <c r="U4" s="7">
         <v>579</v>
       </c>
-      <c r="V4" s="7"/>
+      <c r="V4" s="7">
+        <v>558</v>
+      </c>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
@@ -1230,7 +1244,10 @@
       <c r="M5" s="7">
         <v>368</v>
       </c>
-      <c r="N5" s="7"/>
+      <c r="N5" s="7">
+        <f t="shared" si="1"/>
+        <v>364</v>
+      </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -1246,7 +1263,9 @@
       <c r="U5" s="7">
         <v>381</v>
       </c>
-      <c r="V5" s="7"/>
+      <c r="V5" s="7">
+        <v>364</v>
+      </c>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
@@ -1276,7 +1295,7 @@
     <row r="6" spans="1:47" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="8">
         <v>1418</v>
@@ -1314,7 +1333,10 @@
         <f>+SUM(M3:M5)</f>
         <v>1485</v>
       </c>
-      <c r="N6" s="8"/>
+      <c r="N6" s="8">
+        <f t="shared" si="1"/>
+        <v>1462</v>
+      </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -1328,7 +1350,10 @@
       <c r="U6" s="8">
         <v>1532</v>
       </c>
-      <c r="V6" s="8"/>
+      <c r="V6" s="8">
+        <f>+SUM(V3:V5)</f>
+        <v>1462</v>
+      </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
       <c r="Y6" s="8"/>
@@ -1356,8 +1381,8 @@
       <c r="AU6" s="8"/>
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>35</v>
+      <c r="B7" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="C7" s="7">
         <v>489</v>
@@ -1393,7 +1418,10 @@
       <c r="M7" s="7">
         <v>485</v>
       </c>
-      <c r="N7" s="7"/>
+      <c r="N7" s="7">
+        <f t="shared" si="1"/>
+        <v>485</v>
+      </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -1407,7 +1435,9 @@
       <c r="U7" s="7">
         <v>500</v>
       </c>
-      <c r="V7" s="7"/>
+      <c r="V7" s="7">
+        <v>485</v>
+      </c>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
@@ -1530,7 +1560,7 @@
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="7">
         <v>746</v>
@@ -1567,7 +1597,10 @@
       <c r="M10" s="7">
         <v>764</v>
       </c>
-      <c r="N10" s="7"/>
+      <c r="N10" s="7">
+        <f>+V10-SUM(K10:M10)</f>
+        <v>1008</v>
+      </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
@@ -1581,7 +1614,9 @@
       <c r="U10" s="7">
         <v>3329</v>
       </c>
-      <c r="V10" s="7"/>
+      <c r="V10" s="7">
+        <v>3346</v>
+      </c>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
@@ -1610,7 +1645,7 @@
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7">
         <v>67</v>
@@ -1622,7 +1657,7 @@
         <v>73</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" ref="F11:F31" si="1">+T11-SUM(C11:E11)</f>
+        <f t="shared" ref="F11:F30" si="2">+T11-SUM(C11:E11)</f>
         <v>81</v>
       </c>
       <c r="G11" s="7">
@@ -1635,7 +1670,7 @@
         <v>74</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" ref="J11:J31" si="2">+U11-SUM(G11:I11)</f>
+        <f t="shared" ref="J11:J30" si="3">+U11-SUM(G11:I11)</f>
         <v>85</v>
       </c>
       <c r="K11" s="7">
@@ -1647,7 +1682,10 @@
       <c r="M11" s="7">
         <v>67</v>
       </c>
-      <c r="N11" s="7"/>
+      <c r="N11" s="7">
+        <f t="shared" ref="N11:N30" si="4">+V11-SUM(K11:M11)</f>
+        <v>81</v>
+      </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -1661,7 +1699,9 @@
       <c r="U11" s="7">
         <v>297</v>
       </c>
-      <c r="V11" s="7"/>
+      <c r="V11" s="7">
+        <v>280</v>
+      </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
@@ -1690,7 +1730,7 @@
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="7">
         <v>155</v>
@@ -1702,7 +1742,7 @@
         <v>169</v>
       </c>
       <c r="F12" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
       <c r="G12" s="7">
@@ -1715,7 +1755,7 @@
         <v>171</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>192</v>
       </c>
       <c r="K12" s="7">
@@ -1727,7 +1767,10 @@
       <c r="M12" s="7">
         <v>158</v>
       </c>
-      <c r="N12" s="7"/>
+      <c r="N12" s="7">
+        <f t="shared" si="4"/>
+        <v>191</v>
+      </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
@@ -1741,7 +1784,9 @@
       <c r="U12" s="7">
         <v>682</v>
       </c>
-      <c r="V12" s="7"/>
+      <c r="V12" s="7">
+        <v>644</v>
+      </c>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
@@ -1770,7 +1815,7 @@
     </row>
     <row r="13" spans="1:47" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="7">
         <v>609</v>
@@ -1782,7 +1827,7 @@
         <v>653</v>
       </c>
       <c r="F13" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>680</v>
       </c>
       <c r="G13" s="7">
@@ -1795,7 +1840,7 @@
         <v>662</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>725</v>
       </c>
       <c r="K13" s="7">
@@ -1807,7 +1852,10 @@
       <c r="M13" s="7">
         <v>641</v>
       </c>
-      <c r="N13" s="7"/>
+      <c r="N13" s="7">
+        <f t="shared" si="4"/>
+        <v>878.16200000000026</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -1821,7 +1869,10 @@
       <c r="U13" s="7">
         <v>2625</v>
       </c>
-      <c r="V13" s="7"/>
+      <c r="V13" s="7">
+        <f>2159.001+609.161</f>
+        <v>2768.1620000000003</v>
+      </c>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
@@ -1850,7 +1901,7 @@
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="7">
         <v>195</v>
@@ -1862,7 +1913,7 @@
         <v>228</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>296</v>
       </c>
       <c r="G14" s="7">
@@ -1875,7 +1926,7 @@
         <v>228</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>324</v>
       </c>
       <c r="K14" s="7">
@@ -1887,7 +1938,10 @@
       <c r="M14" s="7">
         <v>223</v>
       </c>
-      <c r="N14" s="7"/>
+      <c r="N14" s="7">
+        <f t="shared" si="4"/>
+        <v>321.70000000000005</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -1901,7 +1955,10 @@
       <c r="U14" s="7">
         <v>1020</v>
       </c>
-      <c r="V14" s="7"/>
+      <c r="V14" s="7">
+        <f>629.726+362.974</f>
+        <v>992.7</v>
+      </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
@@ -1930,7 +1987,7 @@
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="7">
         <v>141</v>
@@ -1942,7 +1999,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="G15" s="7">
@@ -1955,7 +2012,7 @@
         <v>110</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>170</v>
       </c>
       <c r="K15" s="7">
@@ -1967,7 +2024,10 @@
       <c r="M15" s="7">
         <v>101</v>
       </c>
-      <c r="N15" s="7"/>
+      <c r="N15" s="7">
+        <f t="shared" si="4"/>
+        <v>153.97500000000002</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -1981,7 +2041,10 @@
       <c r="U15" s="7">
         <v>553</v>
       </c>
-      <c r="V15" s="7"/>
+      <c r="V15" s="7">
+        <f>199.667+309.308</f>
+        <v>508.97500000000002</v>
+      </c>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
@@ -2013,55 +2076,60 @@
         <v>42</v>
       </c>
       <c r="C16" s="7">
-        <v>23</v>
+        <v>485</v>
       </c>
       <c r="D16" s="7">
-        <v>26</v>
+        <v>580</v>
       </c>
       <c r="E16" s="7">
-        <v>26</v>
+        <v>521</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="1"/>
-        <v>29</v>
+        <f t="shared" si="2"/>
+        <v>676</v>
       </c>
       <c r="G16" s="7">
-        <v>23</v>
+        <v>492</v>
       </c>
       <c r="H16" s="7">
-        <v>26</v>
+        <v>563</v>
       </c>
       <c r="I16" s="7">
-        <v>29</v>
+        <v>499</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f t="shared" si="3"/>
+        <v>687.32400000000007</v>
       </c>
       <c r="K16" s="7">
-        <v>26</v>
+        <v>473</v>
       </c>
       <c r="L16" s="7">
-        <v>24</v>
+        <v>542</v>
       </c>
       <c r="M16" s="7">
-        <v>25</v>
-      </c>
-      <c r="N16" s="7"/>
+        <v>483</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="4"/>
+        <v>669.26200000000017</v>
+      </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7">
-        <v>92</v>
+        <v>2016</v>
       </c>
       <c r="T16" s="7">
-        <v>104</v>
+        <v>2262</v>
       </c>
       <c r="U16" s="7">
-        <v>109</v>
-      </c>
-      <c r="V16" s="7"/>
+        <v>2241.3240000000001</v>
+      </c>
+      <c r="V16" s="7">
+        <v>2167.2620000000002</v>
+      </c>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
@@ -2093,55 +2161,60 @@
         <v>43</v>
       </c>
       <c r="C17" s="7">
-        <v>485</v>
+        <v>282</v>
       </c>
       <c r="D17" s="7">
-        <v>580</v>
+        <v>224</v>
       </c>
       <c r="E17" s="7">
-        <v>521</v>
+        <v>293</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="1"/>
-        <v>676</v>
+        <f t="shared" si="2"/>
+        <v>234</v>
       </c>
       <c r="G17" s="7">
-        <v>492</v>
+        <v>303</v>
       </c>
       <c r="H17" s="7">
-        <v>563</v>
+        <v>236</v>
       </c>
       <c r="I17" s="7">
-        <v>499</v>
+        <v>302</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="2"/>
-        <v>677</v>
+        <f t="shared" si="3"/>
+        <v>270.00700000000006</v>
       </c>
       <c r="K17" s="7">
-        <v>473</v>
+        <v>296</v>
       </c>
       <c r="L17" s="7">
-        <v>542</v>
+        <v>237</v>
       </c>
       <c r="M17" s="7">
-        <v>483</v>
-      </c>
-      <c r="N17" s="7"/>
+        <v>281</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="4"/>
+        <v>294.38000000000011</v>
+      </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7">
-        <v>2016</v>
+        <v>895</v>
       </c>
       <c r="T17" s="7">
-        <v>2262</v>
+        <v>1033</v>
       </c>
       <c r="U17" s="7">
-        <v>2231</v>
-      </c>
-      <c r="V17" s="7"/>
+        <v>1111.0070000000001</v>
+      </c>
+      <c r="V17" s="7">
+        <v>1108.3800000000001</v>
+      </c>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
@@ -2173,55 +2246,60 @@
         <v>44</v>
       </c>
       <c r="C18" s="7">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="D18" s="7">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E18" s="7">
-        <v>293</v>
+        <v>187</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="1"/>
-        <v>234</v>
+        <f t="shared" si="2"/>
+        <v>237</v>
       </c>
       <c r="G18" s="7">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="H18" s="7">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="I18" s="7">
-        <v>302</v>
+        <v>199</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="2"/>
-        <v>270</v>
+        <f t="shared" si="3"/>
+        <v>262.95299999999997</v>
       </c>
       <c r="K18" s="7">
-        <v>296</v>
+        <v>204</v>
       </c>
       <c r="L18" s="7">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="M18" s="7">
-        <v>281</v>
-      </c>
-      <c r="N18" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="4"/>
+        <v>286.65200000000004</v>
+      </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7">
-        <v>895</v>
+        <v>648</v>
       </c>
       <c r="T18" s="7">
-        <v>1033</v>
+        <v>798</v>
       </c>
       <c r="U18" s="7">
-        <v>1111</v>
-      </c>
-      <c r="V18" s="7"/>
+        <v>845.95299999999997</v>
+      </c>
+      <c r="V18" s="7">
+        <v>890.65200000000004</v>
+      </c>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
@@ -2250,58 +2328,63 @@
     </row>
     <row r="19" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C19" s="7">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="D19" s="7">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="E19" s="7">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="1"/>
-        <v>237</v>
+        <f t="shared" si="2"/>
+        <v>29</v>
       </c>
       <c r="G19" s="7">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="H19" s="7">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="I19" s="7">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="2"/>
-        <v>263</v>
+        <f t="shared" si="3"/>
+        <v>31.064999999999998</v>
       </c>
       <c r="K19" s="7">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="L19" s="7">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="M19" s="7">
-        <v>201</v>
-      </c>
-      <c r="N19" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="4"/>
+        <v>28.543999999999997</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7">
-        <v>648</v>
+        <v>92</v>
       </c>
       <c r="T19" s="7">
-        <v>798</v>
+        <v>104</v>
       </c>
       <c r="U19" s="7">
-        <v>846</v>
-      </c>
-      <c r="V19" s="7"/>
+        <v>109.065</v>
+      </c>
+      <c r="V19" s="7">
+        <v>103.544</v>
+      </c>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
@@ -2327,61 +2410,80 @@
       <c r="AS19" s="7"/>
       <c r="AT19" s="7"/>
       <c r="AU19" s="7"/>
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+      <c r="AZ19" s="3"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="3"/>
+      <c r="BC19" s="3"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="3"/>
+      <c r="BF19" s="3"/>
+      <c r="BG19" s="3"/>
+      <c r="BH19" s="3"/>
+      <c r="BI19" s="3"/>
     </row>
     <row r="20" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="7">
-        <v>23</v>
-      </c>
-      <c r="D20" s="7">
-        <v>26</v>
-      </c>
-      <c r="E20" s="7">
-        <v>26</v>
-      </c>
-      <c r="F20" s="7">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="G20" s="7">
-        <v>23</v>
-      </c>
-      <c r="H20" s="7">
-        <v>26</v>
-      </c>
-      <c r="I20" s="7">
-        <v>29</v>
-      </c>
-      <c r="J20" s="7">
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8">
+        <v>968</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1026</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1027</v>
+      </c>
+      <c r="F20" s="8">
         <f t="shared" si="2"/>
-        <v>31</v>
-      </c>
-      <c r="K20" s="7">
-        <v>26</v>
-      </c>
-      <c r="L20" s="7">
-        <v>24</v>
-      </c>
-      <c r="M20" s="7">
-        <v>25</v>
-      </c>
-      <c r="N20" s="7"/>
+        <v>1176</v>
+      </c>
+      <c r="G20" s="8">
+        <v>1014</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1015</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1029</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="3"/>
+        <v>1249</v>
+      </c>
+      <c r="K20" s="8">
+        <v>999</v>
+      </c>
+      <c r="L20" s="8">
+        <v>1002</v>
+      </c>
+      <c r="M20" s="8">
+        <v>989</v>
+      </c>
+      <c r="N20" s="8">
+        <f t="shared" si="4"/>
+        <v>1279.8379999999997</v>
+      </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
-      <c r="S20" s="7">
-        <v>92</v>
-      </c>
-      <c r="T20" s="7">
-        <v>104</v>
-      </c>
-      <c r="U20" s="7">
-        <v>109</v>
-      </c>
-      <c r="V20" s="7"/>
+      <c r="S20" s="8">
+        <v>3651</v>
+      </c>
+      <c r="T20" s="8">
+        <v>4197</v>
+      </c>
+      <c r="U20" s="8">
+        <v>4307</v>
+      </c>
+      <c r="V20" s="8">
+        <v>4269.8379999999997</v>
+      </c>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
@@ -2423,59 +2525,64 @@
       <c r="BI20" s="3"/>
     </row>
     <row r="21" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="8">
-        <v>968</v>
-      </c>
-      <c r="D21" s="8">
-        <v>1026</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1027</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="1"/>
-        <v>1176</v>
-      </c>
-      <c r="G21" s="8">
-        <v>1014</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1015</v>
-      </c>
-      <c r="I21" s="8">
-        <v>1029</v>
-      </c>
-      <c r="J21" s="8">
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="7">
+        <v>374</v>
+      </c>
+      <c r="D21" s="7">
+        <v>386</v>
+      </c>
+      <c r="E21" s="7">
+        <v>404</v>
+      </c>
+      <c r="F21" s="7">
         <f t="shared" si="2"/>
-        <v>1249</v>
-      </c>
-      <c r="K21" s="8">
-        <v>999</v>
-      </c>
-      <c r="L21" s="8">
-        <v>1002</v>
-      </c>
-      <c r="M21" s="8">
-        <v>989</v>
-      </c>
-      <c r="N21" s="8"/>
+        <v>453</v>
+      </c>
+      <c r="G21" s="7">
+        <v>391</v>
+      </c>
+      <c r="H21" s="7">
+        <v>377</v>
+      </c>
+      <c r="I21" s="7">
+        <v>410</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="3"/>
+        <v>470</v>
+      </c>
+      <c r="K21" s="7">
+        <v>386</v>
+      </c>
+      <c r="L21" s="7">
+        <v>372</v>
+      </c>
+      <c r="M21" s="7">
+        <v>384</v>
+      </c>
+      <c r="N21" s="7">
+        <f t="shared" si="4"/>
+        <v>501.45800000000008</v>
+      </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
-      <c r="S21" s="8">
-        <v>3651</v>
-      </c>
-      <c r="T21" s="8">
-        <v>4197</v>
-      </c>
-      <c r="U21" s="8">
-        <v>4307</v>
-      </c>
-      <c r="V21" s="7"/>
+      <c r="S21" s="7">
+        <v>1395</v>
+      </c>
+      <c r="T21" s="7">
+        <v>1617</v>
+      </c>
+      <c r="U21" s="7">
+        <v>1648</v>
+      </c>
+      <c r="V21" s="7">
+        <v>1643.4580000000001</v>
+      </c>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
@@ -2518,58 +2625,76 @@
     </row>
     <row r="22" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" s="7">
-        <v>374</v>
+        <f t="shared" ref="C22:H22" si="5">+C20-C21</f>
+        <v>594</v>
       </c>
       <c r="D22" s="7">
-        <v>386</v>
+        <f t="shared" si="5"/>
+        <v>640</v>
       </c>
       <c r="E22" s="7">
-        <v>404</v>
+        <f t="shared" si="5"/>
+        <v>623</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="1"/>
-        <v>453</v>
+        <f t="shared" si="5"/>
+        <v>723</v>
       </c>
       <c r="G22" s="7">
-        <v>391</v>
+        <f t="shared" si="5"/>
+        <v>623</v>
       </c>
       <c r="H22" s="7">
-        <v>377</v>
+        <f t="shared" si="5"/>
+        <v>638</v>
       </c>
       <c r="I22" s="7">
-        <v>410</v>
+        <f>+I20-I21</f>
+        <v>619</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="2"/>
-        <v>470</v>
+        <f>+J20-J21</f>
+        <v>779</v>
       </c>
       <c r="K22" s="7">
-        <v>386</v>
+        <f>+K20-K21</f>
+        <v>613</v>
       </c>
       <c r="L22" s="7">
-        <v>372</v>
+        <f>+L20-L21</f>
+        <v>630</v>
       </c>
       <c r="M22" s="7">
-        <v>384</v>
-      </c>
-      <c r="N22" s="7"/>
+        <f>+M20-M21</f>
+        <v>605</v>
+      </c>
+      <c r="N22" s="7">
+        <f>+N20-N21</f>
+        <v>778.37999999999965</v>
+      </c>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7">
-        <v>1395</v>
+        <f>+S20-S21</f>
+        <v>2256</v>
       </c>
       <c r="T22" s="7">
-        <v>1617</v>
+        <f>+T20-T21</f>
+        <v>2580</v>
       </c>
       <c r="U22" s="7">
-        <v>1648</v>
-      </c>
-      <c r="V22" s="7"/>
+        <f>+U20-U21</f>
+        <v>2659</v>
+      </c>
+      <c r="V22" s="7">
+        <f>+V20-V21</f>
+        <v>2626.3799999999997</v>
+      </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
@@ -2612,70 +2737,63 @@
     </row>
     <row r="23" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="7">
-        <f t="shared" ref="C23:H23" si="3">+C21-C22</f>
-        <v>594</v>
+        <v>414</v>
       </c>
       <c r="D23" s="7">
+        <v>410</v>
+      </c>
+      <c r="E23" s="7">
+        <v>424</v>
+      </c>
+      <c r="F23" s="7">
+        <f t="shared" si="2"/>
+        <v>497</v>
+      </c>
+      <c r="G23" s="7">
+        <v>442</v>
+      </c>
+      <c r="H23" s="7">
+        <v>450</v>
+      </c>
+      <c r="I23" s="7">
+        <v>433</v>
+      </c>
+      <c r="J23" s="7">
         <f t="shared" si="3"/>
-        <v>640</v>
-      </c>
-      <c r="E23" s="7">
-        <f t="shared" si="3"/>
-        <v>623</v>
-      </c>
-      <c r="F23" s="7">
-        <f t="shared" si="3"/>
-        <v>723</v>
-      </c>
-      <c r="G23" s="7">
-        <f t="shared" si="3"/>
-        <v>623</v>
-      </c>
-      <c r="H23" s="7">
-        <f t="shared" si="3"/>
-        <v>638</v>
-      </c>
-      <c r="I23" s="7">
-        <f>+I21-I22</f>
-        <v>619</v>
-      </c>
-      <c r="J23" s="7">
-        <f>+J21-J22</f>
-        <v>779</v>
+        <v>543</v>
       </c>
       <c r="K23" s="7">
-        <f>+K21-K22</f>
-        <v>613</v>
+        <v>441</v>
       </c>
       <c r="L23" s="7">
-        <f>+L21-L22</f>
-        <v>630</v>
+        <v>433</v>
       </c>
       <c r="M23" s="7">
-        <f>+M21-M22</f>
-        <v>605</v>
-      </c>
-      <c r="N23" s="7"/>
+        <v>420</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="4"/>
+        <v>510.63699999999994</v>
+      </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7">
-        <f>+S21-S22</f>
-        <v>2256</v>
+        <v>1539</v>
       </c>
       <c r="T23" s="7">
-        <f>+T21-T22</f>
-        <v>2580</v>
+        <v>1745</v>
       </c>
       <c r="U23" s="7">
-        <f>+U21-U22</f>
-        <v>2659</v>
-      </c>
-      <c r="V23" s="7"/>
+        <v>1868</v>
+      </c>
+      <c r="V23" s="7">
+        <v>1804.6369999999999</v>
+      </c>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
@@ -2718,58 +2836,63 @@
     </row>
     <row r="24" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="7">
-        <v>414</v>
+        <v>114</v>
       </c>
       <c r="D24" s="7">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="E24" s="7">
-        <v>424</v>
+        <v>96</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" si="1"/>
-        <v>497</v>
+        <f t="shared" si="2"/>
+        <v>108</v>
       </c>
       <c r="G24" s="7">
-        <v>442</v>
+        <v>112</v>
       </c>
       <c r="H24" s="7">
-        <v>450</v>
+        <v>117</v>
       </c>
       <c r="I24" s="7">
-        <v>433</v>
+        <v>91</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="2"/>
-        <v>543</v>
+        <f t="shared" si="3"/>
+        <v>111</v>
       </c>
       <c r="K24" s="7">
-        <v>441</v>
+        <v>110</v>
       </c>
       <c r="L24" s="7">
-        <v>433</v>
+        <v>116</v>
       </c>
       <c r="M24" s="7">
-        <v>420</v>
-      </c>
-      <c r="N24" s="7"/>
+        <v>90</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="4"/>
+        <v>114.99000000000001</v>
+      </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7">
-        <v>1539</v>
+        <v>382</v>
       </c>
       <c r="T24" s="7">
-        <v>1745</v>
+        <v>426</v>
       </c>
       <c r="U24" s="7">
-        <v>1868</v>
-      </c>
-      <c r="V24" s="7"/>
+        <v>431</v>
+      </c>
+      <c r="V24" s="7">
+        <v>430.99</v>
+      </c>
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
@@ -2812,58 +2935,76 @@
     </row>
     <row r="25" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="7">
-        <v>114</v>
+        <f t="shared" ref="C25:H25" si="6">+C22-SUM(C23:C24)</f>
+        <v>66</v>
       </c>
       <c r="D25" s="7">
-        <v>108</v>
+        <f t="shared" si="6"/>
+        <v>122</v>
       </c>
       <c r="E25" s="7">
-        <v>96</v>
+        <f t="shared" si="6"/>
+        <v>103</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="1"/>
-        <v>108</v>
+        <f t="shared" si="6"/>
+        <v>118</v>
       </c>
       <c r="G25" s="7">
-        <v>112</v>
+        <f t="shared" si="6"/>
+        <v>69</v>
       </c>
       <c r="H25" s="7">
-        <v>117</v>
+        <f t="shared" si="6"/>
+        <v>71</v>
       </c>
       <c r="I25" s="7">
-        <v>91</v>
+        <f>+I22-SUM(I23:I24)</f>
+        <v>95</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" si="2"/>
-        <v>111</v>
+        <f t="shared" ref="J25:N25" si="7">+J22-SUM(J23:J24)</f>
+        <v>125</v>
       </c>
       <c r="K25" s="7">
-        <v>110</v>
+        <f t="shared" si="7"/>
+        <v>62</v>
       </c>
       <c r="L25" s="7">
-        <v>116</v>
+        <f t="shared" si="7"/>
+        <v>81</v>
       </c>
       <c r="M25" s="7">
-        <v>90</v>
-      </c>
-      <c r="N25" s="7"/>
+        <f t="shared" si="7"/>
+        <v>95</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="7"/>
+        <v>152.7529999999997</v>
+      </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7">
-        <v>382</v>
+        <f>+S22-S23-S24</f>
+        <v>335</v>
       </c>
       <c r="T25" s="7">
-        <v>426</v>
+        <f>+T22-T23-T24</f>
+        <v>409</v>
       </c>
       <c r="U25" s="7">
-        <v>431</v>
-      </c>
-      <c r="V25" s="7"/>
+        <f>+U22-U23-U24</f>
+        <v>360</v>
+      </c>
+      <c r="V25" s="7">
+        <f>+V22-V23-V24</f>
+        <v>390.7529999999997</v>
+      </c>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
@@ -2906,70 +3047,63 @@
     </row>
     <row r="26" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" s="7">
-        <f t="shared" ref="C26:H26" si="4">+C23-SUM(C24:C25)</f>
-        <v>66</v>
+        <v>-12</v>
       </c>
       <c r="D26" s="7">
+        <v>-12</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-15</v>
+      </c>
+      <c r="F26" s="7">
+        <f t="shared" si="2"/>
+        <v>-14</v>
+      </c>
+      <c r="G26" s="7">
+        <v>-12</v>
+      </c>
+      <c r="H26" s="7">
+        <v>-16</v>
+      </c>
+      <c r="I26" s="7">
+        <v>-18</v>
+      </c>
+      <c r="J26" s="7">
+        <f t="shared" si="3"/>
+        <v>-13</v>
+      </c>
+      <c r="K26" s="7">
+        <v>-9</v>
+      </c>
+      <c r="L26" s="7">
+        <v>-12</v>
+      </c>
+      <c r="M26" s="7">
+        <v>-12</v>
+      </c>
+      <c r="N26" s="7">
         <f t="shared" si="4"/>
-        <v>122</v>
-      </c>
-      <c r="E26" s="7">
-        <f t="shared" si="4"/>
-        <v>103</v>
-      </c>
-      <c r="F26" s="7">
-        <f t="shared" si="4"/>
-        <v>118</v>
-      </c>
-      <c r="G26" s="7">
-        <f t="shared" si="4"/>
-        <v>69</v>
-      </c>
-      <c r="H26" s="7">
-        <f t="shared" si="4"/>
-        <v>71</v>
-      </c>
-      <c r="I26" s="7">
-        <f>+I23-SUM(I24:I25)</f>
-        <v>95</v>
-      </c>
-      <c r="J26" s="7">
-        <f t="shared" ref="J26:M26" si="5">+J23-SUM(J24:J25)</f>
-        <v>125</v>
-      </c>
-      <c r="K26" s="7">
-        <f t="shared" si="5"/>
-        <v>62</v>
-      </c>
-      <c r="L26" s="7">
-        <f t="shared" si="5"/>
-        <v>81</v>
-      </c>
-      <c r="M26" s="7">
-        <f t="shared" si="5"/>
-        <v>95</v>
-      </c>
-      <c r="N26" s="7"/>
+        <v>-12.901000000000003</v>
+      </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
       <c r="S26" s="7">
-        <f>+S23-S24-S25</f>
-        <v>335</v>
+        <v>-50</v>
       </c>
       <c r="T26" s="7">
-        <f>+T23-T24-T25</f>
-        <v>409</v>
+        <v>-53</v>
       </c>
       <c r="U26" s="7">
-        <f>+U23-U24-U25</f>
-        <v>360</v>
-      </c>
-      <c r="V26" s="7"/>
+        <v>-59</v>
+      </c>
+      <c r="V26" s="7">
+        <v>-45.901000000000003</v>
+      </c>
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
@@ -3012,58 +3146,76 @@
     </row>
     <row r="27" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" s="7">
-        <v>-12</v>
+        <f t="shared" ref="C27:H27" si="8">+C25+C26</f>
+        <v>54</v>
       </c>
       <c r="D27" s="7">
-        <v>-12</v>
+        <f t="shared" si="8"/>
+        <v>110</v>
       </c>
       <c r="E27" s="7">
-        <v>-15</v>
+        <f t="shared" si="8"/>
+        <v>88</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="1"/>
-        <v>-14</v>
+        <f t="shared" si="8"/>
+        <v>104</v>
       </c>
       <c r="G27" s="7">
-        <v>-12</v>
+        <f t="shared" si="8"/>
+        <v>57</v>
       </c>
       <c r="H27" s="7">
-        <v>-16</v>
+        <f t="shared" si="8"/>
+        <v>55</v>
       </c>
       <c r="I27" s="7">
-        <v>-18</v>
+        <f>+I25+I26</f>
+        <v>77</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" si="2"/>
-        <v>-13</v>
+        <f t="shared" ref="J27:N27" si="9">+J25+J26</f>
+        <v>112</v>
       </c>
       <c r="K27" s="7">
-        <v>-9</v>
+        <f t="shared" si="9"/>
+        <v>53</v>
       </c>
       <c r="L27" s="7">
-        <v>-12</v>
+        <f t="shared" si="9"/>
+        <v>69</v>
       </c>
       <c r="M27" s="7">
-        <v>-12</v>
-      </c>
-      <c r="N27" s="7"/>
+        <f t="shared" si="9"/>
+        <v>83</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="9"/>
+        <v>139.85199999999969</v>
+      </c>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7">
-        <v>-50</v>
+        <f>+S25+S26</f>
+        <v>285</v>
       </c>
       <c r="T27" s="7">
-        <v>-53</v>
+        <f>+T25+T26</f>
+        <v>356</v>
       </c>
       <c r="U27" s="7">
-        <v>-59</v>
-      </c>
-      <c r="V27" s="7"/>
+        <f>+U25+U26</f>
+        <v>301</v>
+      </c>
+      <c r="V27" s="7">
+        <f>+V25+V26</f>
+        <v>344.85199999999969</v>
+      </c>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
@@ -3106,70 +3258,63 @@
     </row>
     <row r="28" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" s="7">
-        <f t="shared" ref="C28:H28" si="6">+C26+C27</f>
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D28" s="7">
-        <f t="shared" si="6"/>
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="6"/>
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="6"/>
-        <v>104</v>
+        <f t="shared" si="2"/>
+        <v>17</v>
       </c>
       <c r="G28" s="7">
-        <f t="shared" si="6"/>
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="6"/>
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="I28" s="7">
-        <f>+I26+I27</f>
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" ref="J28:M28" si="7">+J26+J27</f>
-        <v>112</v>
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="K28" s="7">
-        <f t="shared" si="7"/>
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L28" s="7">
-        <f t="shared" si="7"/>
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="M28" s="7">
-        <f t="shared" si="7"/>
-        <v>83</v>
-      </c>
-      <c r="N28" s="7"/>
+        <v>23</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="4"/>
+        <v>28.566999999999993</v>
+      </c>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7">
-        <f>+S26+S27</f>
-        <v>285</v>
+        <v>63</v>
       </c>
       <c r="T28" s="7">
-        <f>+T26+T27</f>
-        <v>356</v>
+        <v>87</v>
       </c>
       <c r="U28" s="7">
-        <f>+U26+U27</f>
-        <v>301</v>
-      </c>
-      <c r="V28" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="V28" s="7">
+        <v>85.566999999999993</v>
+      </c>
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
@@ -3212,58 +3357,76 @@
     </row>
     <row r="29" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="7">
-        <v>15</v>
+        <f t="shared" ref="C29:H29" si="10">+C27-C28</f>
+        <v>39</v>
       </c>
       <c r="D29" s="7">
-        <v>30</v>
+        <f t="shared" si="10"/>
+        <v>80</v>
       </c>
       <c r="E29" s="7">
-        <v>25</v>
+        <f t="shared" si="10"/>
+        <v>63</v>
       </c>
       <c r="F29" s="7">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <f t="shared" si="10"/>
+        <v>87</v>
       </c>
       <c r="G29" s="7">
-        <v>16</v>
+        <f t="shared" si="10"/>
+        <v>41</v>
       </c>
       <c r="H29" s="7">
-        <v>15</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="I29" s="7">
-        <v>22</v>
+        <f>+I27-I28</f>
+        <v>55</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" si="2"/>
-        <v>25</v>
+        <f t="shared" ref="J29" si="11">+J27-J28</f>
+        <v>87</v>
       </c>
       <c r="K29" s="7">
-        <v>15</v>
+        <f>+K27-K28</f>
+        <v>38</v>
       </c>
       <c r="L29" s="7">
-        <v>19</v>
+        <f>+L27-L28</f>
+        <v>50</v>
       </c>
       <c r="M29" s="7">
-        <v>23</v>
-      </c>
-      <c r="N29" s="7"/>
+        <f>+M27-M28</f>
+        <v>60</v>
+      </c>
+      <c r="N29" s="7">
+        <f>+N27-N28</f>
+        <v>111.2849999999997</v>
+      </c>
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7">
-        <v>63</v>
+        <f>+S27-S28</f>
+        <v>222</v>
       </c>
       <c r="T29" s="7">
-        <v>87</v>
+        <f>+T27-T28</f>
+        <v>269</v>
       </c>
       <c r="U29" s="7">
-        <v>78</v>
-      </c>
-      <c r="V29" s="7"/>
+        <f>+U27-U28</f>
+        <v>223</v>
+      </c>
+      <c r="V29" s="7">
+        <f>+V27-V28</f>
+        <v>259.28499999999968</v>
+      </c>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
@@ -3306,70 +3469,63 @@
     </row>
     <row r="30" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C30" s="7">
-        <f t="shared" ref="C30:H30" si="8">+C28-C29</f>
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="D30" s="7">
-        <f t="shared" si="8"/>
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="E30" s="7">
-        <f t="shared" si="8"/>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F30" s="7">
-        <f t="shared" si="8"/>
-        <v>87</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="G30" s="7">
-        <f t="shared" si="8"/>
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="8"/>
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I30" s="7">
-        <f>+I28-I29</f>
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" ref="J30" si="9">+J28-J29</f>
-        <v>87</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="K30" s="7">
-        <f>+K28-K29</f>
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="L30" s="7">
-        <f>+L28-L29</f>
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M30" s="7">
-        <f>+M28-M29</f>
-        <v>60</v>
-      </c>
-      <c r="N30" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="4"/>
+        <v>3.8049999999999997</v>
+      </c>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7">
-        <f>+S28-S29</f>
-        <v>222</v>
+        <v>12</v>
       </c>
       <c r="T30" s="7">
-        <f>+T28-T29</f>
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="U30" s="7">
-        <f>+U28-U29</f>
-        <v>223</v>
-      </c>
-      <c r="V30" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="V30" s="7">
+        <v>9.8049999999999997</v>
+      </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
@@ -3412,58 +3568,76 @@
     </row>
     <row r="31" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" s="7">
-        <v>4</v>
+        <f t="shared" ref="C31:H31" si="12">+C29-C30</f>
+        <v>35</v>
       </c>
       <c r="D31" s="7">
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>77</v>
       </c>
       <c r="E31" s="7">
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>63</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" si="12"/>
+        <v>83</v>
       </c>
       <c r="G31" s="7">
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>38</v>
       </c>
       <c r="H31" s="7">
-        <v>2</v>
+        <f t="shared" si="12"/>
+        <v>38</v>
       </c>
       <c r="I31" s="7">
-        <v>1</v>
+        <f>+I29-I30</f>
+        <v>54</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f t="shared" ref="J31" si="13">+J29-J30</f>
+        <v>83</v>
       </c>
       <c r="K31" s="7">
-        <v>2</v>
+        <f>+K29-K30</f>
+        <v>36</v>
       </c>
       <c r="L31" s="7">
-        <v>3</v>
+        <f>+L29-L30</f>
+        <v>47</v>
       </c>
       <c r="M31" s="7">
-        <v>1</v>
-      </c>
-      <c r="N31" s="7"/>
+        <f>+M29-M30</f>
+        <v>59</v>
+      </c>
+      <c r="N31" s="7">
+        <f>+N29-N30</f>
+        <v>107.47999999999971</v>
+      </c>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7">
-        <v>12</v>
+        <f>+S29-S30</f>
+        <v>210</v>
       </c>
       <c r="T31" s="7">
-        <v>11</v>
+        <f>+T29-T30</f>
+        <v>258</v>
       </c>
       <c r="U31" s="7">
-        <v>10</v>
-      </c>
-      <c r="V31" s="7"/>
+        <f>+U29-U30</f>
+        <v>213</v>
+      </c>
+      <c r="V31" s="7">
+        <f>+V29-V30</f>
+        <v>249.47999999999968</v>
+      </c>
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
@@ -3505,96 +3679,51 @@
       <c r="BI31" s="3"/>
     </row>
     <row r="32" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="7">
-        <f t="shared" ref="C32:H32" si="10">+C30-C31</f>
-        <v>35</v>
-      </c>
-      <c r="D32" s="7">
-        <f t="shared" si="10"/>
-        <v>77</v>
-      </c>
-      <c r="E32" s="7">
-        <f t="shared" si="10"/>
-        <v>63</v>
-      </c>
-      <c r="F32" s="7">
-        <f t="shared" si="10"/>
-        <v>83</v>
-      </c>
-      <c r="G32" s="7">
-        <f t="shared" si="10"/>
-        <v>38</v>
-      </c>
-      <c r="H32" s="7">
-        <f t="shared" si="10"/>
-        <v>38</v>
-      </c>
-      <c r="I32" s="7">
-        <f>+I30-I31</f>
-        <v>54</v>
-      </c>
-      <c r="J32" s="7">
-        <f t="shared" ref="J32" si="11">+J30-J31</f>
-        <v>83</v>
-      </c>
-      <c r="K32" s="7">
-        <f>+K30-K31</f>
-        <v>36</v>
-      </c>
-      <c r="L32" s="7">
-        <f>+L30-L31</f>
-        <v>47</v>
-      </c>
-      <c r="M32" s="7">
-        <f>+M30-M31</f>
-        <v>59</v>
-      </c>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7">
-        <f>+S30-S31</f>
-        <v>210</v>
-      </c>
-      <c r="T32" s="7">
-        <f>+T30-T31</f>
-        <v>258</v>
-      </c>
-      <c r="U32" s="7">
-        <f>+U30-U31</f>
-        <v>213</v>
-      </c>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="7"/>
-      <c r="AC32" s="7"/>
-      <c r="AD32" s="7"/>
-      <c r="AE32" s="7"/>
-      <c r="AF32" s="7"/>
-      <c r="AG32" s="7"/>
-      <c r="AH32" s="7"/>
-      <c r="AI32" s="7"/>
-      <c r="AJ32" s="7"/>
-      <c r="AK32" s="7"/>
-      <c r="AL32" s="7"/>
-      <c r="AM32" s="7"/>
-      <c r="AN32" s="7"/>
-      <c r="AO32" s="7"/>
-      <c r="AP32" s="7"/>
-      <c r="AQ32" s="7"/>
-      <c r="AR32" s="7"/>
-      <c r="AS32" s="7"/>
-      <c r="AT32" s="7"/>
-      <c r="AU32" s="7"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="3"/>
+      <c r="AK32" s="3"/>
+      <c r="AL32" s="3"/>
+      <c r="AM32" s="3"/>
+      <c r="AN32" s="3"/>
+      <c r="AO32" s="3"/>
+      <c r="AP32" s="3"/>
+      <c r="AQ32" s="3"/>
+      <c r="AR32" s="3"/>
+      <c r="AS32" s="3"/>
+      <c r="AT32" s="3"/>
+      <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
       <c r="AW32" s="3"/>
       <c r="AX32" s="3"/>
@@ -3611,26 +3740,86 @@
       <c r="BI32" s="3"/>
     </row>
     <row r="33" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
+      <c r="B33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="9">
+        <f t="shared" ref="C33:D33" si="14">+C31/C34</f>
+        <v>0.507127532576786</v>
+      </c>
+      <c r="D33" s="9">
+        <f t="shared" si="14"/>
+        <v>1.1156805716689291</v>
+      </c>
+      <c r="E33" s="9">
+        <f>+E31/E34</f>
+        <v>0.9128295586382148</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" ref="F33:J33" si="15">+F31/F34</f>
+        <v>1.2026167201106639</v>
+      </c>
+      <c r="G33" s="9">
+        <f t="shared" si="15"/>
+        <v>0.55059560679765329</v>
+      </c>
+      <c r="H33" s="9">
+        <f t="shared" si="15"/>
+        <v>0.55059560679765329</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="15"/>
+        <v>0.78242533597561259</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="15"/>
+        <v>1.2026167201106639</v>
+      </c>
+      <c r="K33" s="9">
+        <f>+K31/K34</f>
+        <v>0.52161689065040839</v>
+      </c>
+      <c r="L33" s="9">
+        <f>+L31/L34</f>
+        <v>0.6809998294602555</v>
+      </c>
+      <c r="M33" s="9">
+        <f>+M31/M34</f>
+        <v>0.85487212634372489</v>
+      </c>
+      <c r="N33" s="9">
+        <f>+N31/N34</f>
+        <v>1.5573162057529373</v>
+      </c>
       <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+      <c r="P33" s="9" t="e">
+        <f t="shared" ref="P33:S33" si="16">+P31/P34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q33" s="9">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="9">
+        <f t="shared" si="16"/>
+        <v>3.0427651954607158</v>
+      </c>
+      <c r="T33" s="9">
+        <f>+T31/T34</f>
+        <v>3.7382543829945938</v>
+      </c>
+      <c r="U33" s="9">
+        <f>+U31/U34</f>
+        <v>3.0862332696815833</v>
+      </c>
+      <c r="V33" s="9">
+        <f>+V31/V34</f>
+        <v>3.6148050522073256</v>
+      </c>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
@@ -3673,79 +3862,64 @@
     </row>
     <row r="34" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="9">
-        <f t="shared" ref="C34:D34" si="12">+C32/C35</f>
-        <v>0.49715909090909088</v>
-      </c>
-      <c r="D34" s="9">
-        <f t="shared" si="12"/>
-        <v>1.09375</v>
-      </c>
-      <c r="E34" s="9">
-        <f>+E32/E35</f>
-        <v>0.89488636363636354</v>
-      </c>
-      <c r="F34" s="9">
-        <f t="shared" ref="F34:J34" si="13">+F32/F35</f>
-        <v>1.1789772727272727</v>
-      </c>
-      <c r="G34" s="9">
-        <f t="shared" si="13"/>
-        <v>0.53977272727272718</v>
-      </c>
-      <c r="H34" s="9">
-        <f t="shared" si="13"/>
-        <v>0.53977272727272718</v>
-      </c>
-      <c r="I34" s="9">
-        <f t="shared" si="13"/>
-        <v>0.76704545454545447</v>
-      </c>
-      <c r="J34" s="9">
-        <f t="shared" si="13"/>
-        <v>1.1789772727272727</v>
-      </c>
-      <c r="K34" s="9">
-        <f>+K32/K35</f>
-        <v>0.51136363636363635</v>
-      </c>
-      <c r="L34" s="9">
-        <f>+L32/L35</f>
-        <v>0.66761363636363635</v>
-      </c>
-      <c r="M34" s="9">
-        <f>+M32/M35</f>
-        <v>0.83806818181818177</v>
-      </c>
-      <c r="N34" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="C34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="D34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="E34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="F34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="G34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="H34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="I34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="J34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="K34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="L34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="M34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="N34" s="3">
+        <v>69.016170000000002</v>
+      </c>
       <c r="O34" s="3"/>
-      <c r="P34" s="9" t="e">
-        <f t="shared" ref="P34:S34" si="14">+P32/P35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q34" s="9" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R34" s="9" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S34" s="9">
-        <f t="shared" si="14"/>
-        <v>2.9829545454545454</v>
-      </c>
-      <c r="T34" s="9">
-        <f>+T32/T35</f>
-        <v>3.6647727272727271</v>
-      </c>
-      <c r="U34" s="9">
-        <f>+U32/U35</f>
-        <v>3.0255681818181817</v>
-      </c>
-      <c r="V34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="R34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="S34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="T34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="U34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="V34" s="3">
+        <v>69.016170000000002</v>
+      </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
@@ -3787,56 +3961,25 @@
       <c r="BI34" s="3"/>
     </row>
     <row r="35" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="D35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="E35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="F35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="G35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="H35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="I35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="J35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="K35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="L35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="M35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="N35" s="10"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
-      <c r="S35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="T35" s="10">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="U35" s="10">
-        <v>70.400000000000006</v>
-      </c>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
@@ -3879,26 +4022,71 @@
       <c r="BI35" s="3"/>
     </row>
     <row r="36" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
+      <c r="G36" s="10">
+        <f>+G6/C6-1</f>
+        <v>5.6417489421720646E-3</v>
+      </c>
+      <c r="H36" s="10">
+        <f>+H6/D6-1</f>
+        <v>5.0775740479548581E-2</v>
+      </c>
+      <c r="I36" s="10">
+        <f>+I6/E6-1</f>
+        <v>4.6544428772919533E-2</v>
+      </c>
+      <c r="J36" s="10">
+        <f>+J6/F6-1</f>
+        <v>8.0394922425952142E-2</v>
+      </c>
+      <c r="K36" s="10">
+        <f>+K6/G6-1</f>
+        <v>6.5217391304347894E-2</v>
+      </c>
+      <c r="L36" s="10">
+        <f t="shared" ref="L36:N36" si="17">+L6/H6-1</f>
+        <v>3.3557046979866278E-3</v>
+      </c>
+      <c r="M36" s="10">
+        <f t="shared" si="17"/>
+        <v>6.738544474393926E-4</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="17"/>
+        <v>-4.5691906005221883E-2</v>
+      </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+      <c r="Q36" s="10" t="e">
+        <f t="shared" ref="Q36:V36" si="18">+Q6/P6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R36" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S36" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T36" s="10">
+        <f t="shared" si="18"/>
+        <v>7.7507598784194442E-2</v>
+      </c>
+      <c r="U36" s="10">
+        <f t="shared" si="18"/>
+        <v>8.0394922425952142E-2</v>
+      </c>
+      <c r="V36" s="10">
+        <f>+V6/U6-1</f>
+        <v>-4.5691906005221883E-2</v>
+      </c>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
@@ -3947,52 +4135,64 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="11">
-        <f t="shared" ref="G37:K38" si="15">+G6/C6-1</f>
-        <v>5.6417489421720646E-3</v>
-      </c>
-      <c r="H37" s="11">
-        <f t="shared" si="15"/>
-        <v>5.0775740479548581E-2</v>
-      </c>
-      <c r="I37" s="11">
-        <f t="shared" si="15"/>
-        <v>4.6544428772919533E-2</v>
-      </c>
-      <c r="J37" s="11">
-        <f t="shared" si="15"/>
-        <v>8.0394922425952142E-2</v>
-      </c>
-      <c r="K37" s="11">
-        <f t="shared" si="15"/>
-        <v>6.5217391304347894E-2</v>
-      </c>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
+      <c r="G37" s="10">
+        <f>+G7/C7-1</f>
+        <v>2.044989775051187E-3</v>
+      </c>
+      <c r="H37" s="10">
+        <f>+H7/D7-1</f>
+        <v>1.0224948875255713E-2</v>
+      </c>
+      <c r="I37" s="10">
+        <f>+I7/E7-1</f>
+        <v>2.044989775051187E-3</v>
+      </c>
+      <c r="J37" s="10">
+        <f>+J7/F7-1</f>
+        <v>2.249488752556239E-2</v>
+      </c>
+      <c r="K37" s="10">
+        <f>+K7/G7-1</f>
+        <v>2.0408163265306145E-2</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" ref="L37:N37" si="19">+L7/H7-1</f>
+        <v>-6.0728744939271273E-3</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="19"/>
+        <v>-1.0204081632653073E-2</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="19"/>
+        <v>-3.0000000000000027E-2</v>
+      </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
-      <c r="Q37" s="11" t="e">
-        <f t="shared" ref="Q37:U38" si="16">+Q6/P6-1</f>
+      <c r="Q37" s="10" t="e">
+        <f t="shared" ref="Q37:V37" si="20">+Q7/P7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R37" s="11" t="e">
-        <f t="shared" si="16"/>
+      <c r="R37" s="10" t="e">
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S37" s="11" t="e">
-        <f t="shared" si="16"/>
+      <c r="S37" s="10" t="e">
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T37" s="11">
-        <f t="shared" si="16"/>
-        <v>7.7507598784194442E-2</v>
-      </c>
-      <c r="U37" s="11">
-        <f t="shared" si="16"/>
-        <v>8.0394922425952142E-2</v>
-      </c>
-      <c r="V37" s="3"/>
+      <c r="T37" s="10">
+        <f t="shared" si="20"/>
+        <v>4.042553191489362E-2</v>
+      </c>
+      <c r="U37" s="10">
+        <f t="shared" si="20"/>
+        <v>2.249488752556239E-2</v>
+      </c>
+      <c r="V37" s="10">
+        <f>+V7/U7-1</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
@@ -4035,58 +4235,70 @@
     </row>
     <row r="38" spans="2:61" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="11">
-        <f t="shared" si="15"/>
-        <v>2.044989775051187E-3</v>
-      </c>
-      <c r="H38" s="11">
-        <f t="shared" si="15"/>
-        <v>1.0224948875255713E-2</v>
-      </c>
-      <c r="I38" s="11">
-        <f t="shared" si="15"/>
-        <v>2.044989775051187E-3</v>
-      </c>
-      <c r="J38" s="11">
-        <f t="shared" si="15"/>
-        <v>2.249488752556239E-2</v>
-      </c>
-      <c r="K38" s="11">
-        <f t="shared" si="15"/>
-        <v>2.0408163265306145E-2</v>
-      </c>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
+      <c r="G38" s="10">
+        <f t="shared" ref="G38:J47" si="21">+G10/C10-1</f>
+        <v>4.1554959785522705E-2</v>
+      </c>
+      <c r="H38" s="10">
+        <f t="shared" si="21"/>
+        <v>-1.9753086419753041E-2</v>
+      </c>
+      <c r="I38" s="10">
+        <f t="shared" si="21"/>
+        <v>-1.2722646310432406E-3</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="21"/>
+        <v>6.4551422319474749E-2</v>
+      </c>
+      <c r="K38" s="10">
+        <f>+K10/G10-1</f>
+        <v>-1.4157014157014203E-2</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" ref="L38:N48" si="22">+L10/H10-1</f>
+        <v>1.7632241813602123E-2</v>
+      </c>
+      <c r="M38" s="10">
+        <f t="shared" si="22"/>
+        <v>-2.6751592356687892E-2</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="22"/>
+        <v>3.5971223021582732E-2</v>
+      </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
-      <c r="Q38" s="11" t="e">
-        <f t="shared" si="16"/>
+      <c r="Q38" s="10" t="e">
+        <f t="shared" ref="Q38:V48" si="23">+Q10/P10-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R38" s="11" t="e">
-        <f t="shared" si="16"/>
+      <c r="R38" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S38" s="11" t="e">
-        <f t="shared" si="16"/>
+      <c r="S38" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T38" s="11">
-        <f t="shared" si="16"/>
-        <v>4.042553191489362E-2</v>
-      </c>
-      <c r="U38" s="11">
-        <f t="shared" si="16"/>
-        <v>2.249488752556239E-2</v>
-      </c>
-      <c r="V38" s="3"/>
+      <c r="T38" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13528591352859132</v>
+      </c>
+      <c r="U38" s="10">
+        <f t="shared" si="23"/>
+        <v>2.2420147420147529E-2</v>
+      </c>
+      <c r="V38" s="10">
+        <f>+V10/U10-1</f>
+        <v>5.1066386302192068E-3</v>
+      </c>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
@@ -4135,52 +4347,64 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="11">
-        <f t="shared" ref="G39:H48" si="17">+G10/C10-1</f>
-        <v>4.1554959785522705E-2</v>
-      </c>
-      <c r="H39" s="11">
-        <f t="shared" si="17"/>
-        <v>-1.9753086419753041E-2</v>
-      </c>
-      <c r="I39" s="11">
-        <f>+I10/E10-1</f>
-        <v>-1.2722646310432406E-3</v>
-      </c>
-      <c r="J39" s="11">
-        <f>+J10/F10-1</f>
-        <v>6.4551422319474749E-2</v>
-      </c>
-      <c r="K39" s="11">
-        <f>+K10/G10-1</f>
-        <v>-1.4157014157014203E-2</v>
-      </c>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
+      <c r="G39" s="10">
+        <f t="shared" si="21"/>
+        <v>4.4776119402984982E-2</v>
+      </c>
+      <c r="H39" s="10">
+        <f t="shared" si="21"/>
+        <v>1.4925373134328401E-2</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="21"/>
+        <v>1.3698630136986356E-2</v>
+      </c>
+      <c r="J39" s="10">
+        <f t="shared" si="21"/>
+        <v>4.9382716049382713E-2</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" ref="K39:K47" si="24">+K11/G11-1</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="22"/>
+        <v>-8.8235294117647078E-2</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="22"/>
+        <v>-9.4594594594594628E-2</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="22"/>
+        <v>-4.705882352941182E-2</v>
+      </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-      <c r="Q39" s="11" t="e">
-        <f t="shared" ref="Q39:S48" si="18">+Q10/P10-1</f>
+      <c r="Q39" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R39" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R39" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S39" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S39" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T39" s="11">
-        <f>+T10/S10-1</f>
-        <v>0.13528591352859132</v>
-      </c>
-      <c r="U39" s="11">
-        <f>+U10/T10-1</f>
-        <v>2.2420147420147529E-2</v>
-      </c>
-      <c r="V39" s="3"/>
+      <c r="T39" s="10">
+        <f t="shared" si="23"/>
+        <v>0.20502092050209209</v>
+      </c>
+      <c r="U39" s="10">
+        <f t="shared" si="23"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="V39" s="10">
+        <f t="shared" ref="V39:V48" si="25">+V11/U11-1</f>
+        <v>-5.7239057239057201E-2</v>
+      </c>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
@@ -4229,52 +4453,64 @@
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="11">
-        <f t="shared" si="17"/>
-        <v>4.4776119402984982E-2</v>
-      </c>
-      <c r="H40" s="11">
-        <f t="shared" si="17"/>
-        <v>1.4925373134328401E-2</v>
-      </c>
-      <c r="I40" s="11">
-        <f t="shared" ref="I40:K48" si="19">+I11/E11-1</f>
-        <v>1.3698630136986356E-2</v>
-      </c>
-      <c r="J40" s="11">
-        <f t="shared" si="19"/>
-        <v>4.9382716049382713E-2</v>
-      </c>
-      <c r="K40" s="11">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
+      <c r="G40" s="10">
+        <f t="shared" si="21"/>
+        <v>7.7419354838709653E-2</v>
+      </c>
+      <c r="H40" s="10">
+        <f t="shared" si="21"/>
+        <v>2.7027027027026973E-2</v>
+      </c>
+      <c r="I40" s="10">
+        <f t="shared" si="21"/>
+        <v>1.1834319526627279E-2</v>
+      </c>
+      <c r="J40" s="10">
+        <f t="shared" si="21"/>
+        <v>6.0773480662983381E-2</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="24"/>
+        <v>-2.39520958083832E-2</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="22"/>
+        <v>-0.13157894736842102</v>
+      </c>
+      <c r="M40" s="10">
+        <f t="shared" si="22"/>
+        <v>-7.6023391812865548E-2</v>
+      </c>
+      <c r="N40" s="10">
+        <f t="shared" si="22"/>
+        <v>-5.2083333333333703E-3</v>
+      </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-      <c r="Q40" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q40" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R40" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R40" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S40" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S40" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T40" s="11">
-        <f t="shared" ref="T40:U48" si="20">+T11/S11-1</f>
-        <v>0.20502092050209209</v>
-      </c>
-      <c r="U40" s="11">
-        <f t="shared" si="20"/>
-        <v>3.125E-2</v>
-      </c>
-      <c r="V40" s="3"/>
+      <c r="T40" s="10">
+        <f t="shared" si="23"/>
+        <v>0.19816513761467891</v>
+      </c>
+      <c r="U40" s="10">
+        <f t="shared" si="23"/>
+        <v>4.4410413476263511E-2</v>
+      </c>
+      <c r="V40" s="10">
+        <f t="shared" si="25"/>
+        <v>-5.5718475073313734E-2</v>
+      </c>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
@@ -4323,52 +4559,64 @@
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="11">
-        <f t="shared" si="17"/>
-        <v>7.7419354838709653E-2</v>
-      </c>
-      <c r="H41" s="11">
-        <f t="shared" si="17"/>
-        <v>2.7027027027026973E-2</v>
-      </c>
-      <c r="I41" s="11">
-        <f t="shared" si="19"/>
-        <v>1.1834319526627279E-2</v>
-      </c>
-      <c r="J41" s="11">
-        <f t="shared" si="19"/>
-        <v>6.0773480662983381E-2</v>
-      </c>
-      <c r="K41" s="11">
-        <f t="shared" si="19"/>
-        <v>-2.39520958083832E-2</v>
-      </c>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
+      <c r="G41" s="10">
+        <f t="shared" si="21"/>
+        <v>4.1050903119868698E-2</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" si="21"/>
+        <v>-2.5806451612903181E-2</v>
+      </c>
+      <c r="I41" s="10">
+        <f t="shared" si="21"/>
+        <v>1.3782542113323082E-2</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="21"/>
+        <v>6.6176470588235281E-2</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="24"/>
+        <v>-4.7318611987381409E-3</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="22"/>
+        <v>2.3178807947019875E-2</v>
+      </c>
+      <c r="M41" s="10">
+        <f t="shared" si="22"/>
+        <v>-3.1722054380664666E-2</v>
+      </c>
+      <c r="N41" s="10">
+        <f t="shared" si="22"/>
+        <v>0.21125793103448309</v>
+      </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
-      <c r="Q41" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q41" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R41" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R41" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S41" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S41" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T41" s="11">
-        <f t="shared" si="20"/>
-        <v>0.19816513761467891</v>
-      </c>
-      <c r="U41" s="11">
-        <f t="shared" si="20"/>
-        <v>4.4410413476263511E-2</v>
-      </c>
-      <c r="V41" s="3"/>
+      <c r="T41" s="10">
+        <f t="shared" si="23"/>
+        <v>0.11246200607902734</v>
+      </c>
+      <c r="U41" s="10">
+        <f t="shared" si="23"/>
+        <v>2.4590163934426146E-2</v>
+      </c>
+      <c r="V41" s="10">
+        <f t="shared" si="25"/>
+        <v>5.4537904761904787E-2</v>
+      </c>
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
@@ -4417,52 +4665,64 @@
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="11">
-        <f t="shared" si="17"/>
-        <v>4.1050903119868698E-2</v>
-      </c>
-      <c r="H42" s="11">
-        <f t="shared" si="17"/>
-        <v>-2.5806451612903181E-2</v>
-      </c>
-      <c r="I42" s="11">
-        <f t="shared" si="19"/>
-        <v>1.3782542113323082E-2</v>
-      </c>
-      <c r="J42" s="11">
-        <f t="shared" si="19"/>
-        <v>6.6176470588235281E-2</v>
-      </c>
-      <c r="K42" s="11">
-        <f t="shared" si="19"/>
-        <v>-4.7318611987381409E-3</v>
-      </c>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
+      <c r="G42" s="10">
+        <f t="shared" si="21"/>
+        <v>0.11794871794871797</v>
+      </c>
+      <c r="H42" s="10">
+        <f t="shared" si="21"/>
+        <v>5.9322033898305149E-2</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="21"/>
+        <v>9.4594594594594517E-2</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="24"/>
+        <v>-2.752293577981646E-2</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="22"/>
+        <v>-5.600000000000005E-2</v>
+      </c>
+      <c r="M42" s="10">
+        <f t="shared" si="22"/>
+        <v>-2.1929824561403466E-2</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="22"/>
+        <v>-7.0987654320986415E-3</v>
+      </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
-      <c r="Q42" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q42" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R42" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R42" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S42" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S42" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T42" s="11">
-        <f t="shared" si="20"/>
-        <v>0.11246200607902734</v>
-      </c>
-      <c r="U42" s="11">
-        <f t="shared" si="20"/>
-        <v>2.4590163934426146E-2</v>
-      </c>
-      <c r="V42" s="3"/>
+      <c r="T42" s="10">
+        <f t="shared" si="23"/>
+        <v>0.21039290240811148</v>
+      </c>
+      <c r="U42" s="10">
+        <f t="shared" si="23"/>
+        <v>6.8062827225130906E-2</v>
+      </c>
+      <c r="V42" s="10">
+        <f t="shared" si="25"/>
+        <v>-2.6764705882352913E-2</v>
+      </c>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
@@ -4511,52 +4771,64 @@
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="11">
-        <f t="shared" si="17"/>
-        <v>0.11794871794871797</v>
-      </c>
-      <c r="H43" s="11">
-        <f t="shared" si="17"/>
-        <v>5.9322033898305149E-2</v>
-      </c>
-      <c r="I43" s="11">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="11">
-        <f t="shared" si="19"/>
-        <v>9.4594594594594517E-2</v>
-      </c>
-      <c r="K43" s="11">
-        <f t="shared" si="19"/>
-        <v>-2.752293577981646E-2</v>
-      </c>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
+      <c r="G43" s="10">
+        <f t="shared" si="21"/>
+        <v>-1.4184397163120588E-2</v>
+      </c>
+      <c r="H43" s="10">
+        <f t="shared" si="21"/>
+        <v>-6.944444444444442E-2</v>
+      </c>
+      <c r="I43" s="10">
+        <f t="shared" si="21"/>
+        <v>-8.333333333333337E-2</v>
+      </c>
+      <c r="J43" s="10">
+        <f t="shared" si="21"/>
+        <v>-5.8479532163743242E-3</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="24"/>
+        <v>-6.4748201438848962E-2</v>
+      </c>
+      <c r="L43" s="10">
+        <f t="shared" si="22"/>
+        <v>-7.4626865671641784E-2</v>
+      </c>
+      <c r="M43" s="10">
+        <f t="shared" si="22"/>
+        <v>-8.181818181818179E-2</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="22"/>
+        <v>-9.4264705882352806E-2</v>
+      </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
-      <c r="Q43" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q43" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R43" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R43" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S43" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S43" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T43" s="11">
-        <f t="shared" si="20"/>
-        <v>0.21039290240811148</v>
-      </c>
-      <c r="U43" s="11">
-        <f t="shared" si="20"/>
-        <v>6.8062827225130906E-2</v>
-      </c>
-      <c r="V43" s="3"/>
+      <c r="T43" s="10">
+        <f t="shared" si="23"/>
+        <v>0.23340471092077086</v>
+      </c>
+      <c r="U43" s="10">
+        <f t="shared" si="23"/>
+        <v>-3.993055555555558E-2</v>
+      </c>
+      <c r="V43" s="10">
+        <f t="shared" si="25"/>
+        <v>-7.9611211573236806E-2</v>
+      </c>
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
@@ -4605,52 +4877,64 @@
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="11">
-        <f t="shared" si="17"/>
-        <v>-1.4184397163120588E-2</v>
-      </c>
-      <c r="H44" s="11">
-        <f t="shared" si="17"/>
-        <v>-6.944444444444442E-2</v>
-      </c>
-      <c r="I44" s="11">
-        <f t="shared" si="19"/>
-        <v>-8.333333333333337E-2</v>
-      </c>
-      <c r="J44" s="11">
-        <f t="shared" si="19"/>
-        <v>-5.8479532163743242E-3</v>
-      </c>
-      <c r="K44" s="11">
-        <f t="shared" si="19"/>
-        <v>-6.4748201438848962E-2</v>
-      </c>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
+      <c r="G44" s="10">
+        <f t="shared" si="21"/>
+        <v>1.4432989690721598E-2</v>
+      </c>
+      <c r="H44" s="10">
+        <f t="shared" si="21"/>
+        <v>-2.931034482758621E-2</v>
+      </c>
+      <c r="I44" s="10">
+        <f t="shared" si="21"/>
+        <v>-4.2226487523992273E-2</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="21"/>
+        <v>1.6751479289941029E-2</v>
+      </c>
+      <c r="K44" s="10">
+        <f t="shared" si="24"/>
+        <v>-3.8617886178861749E-2</v>
+      </c>
+      <c r="L44" s="10">
+        <f t="shared" si="22"/>
+        <v>-3.730017761989346E-2</v>
+      </c>
+      <c r="M44" s="10">
+        <f t="shared" si="22"/>
+        <v>-3.2064128256513058E-2</v>
+      </c>
+      <c r="N44" s="10">
+        <f t="shared" si="22"/>
+        <v>-2.6278727354202558E-2</v>
+      </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
-      <c r="Q44" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q44" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R44" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R44" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S44" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S44" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T44" s="11">
-        <f t="shared" si="20"/>
-        <v>0.23340471092077086</v>
-      </c>
-      <c r="U44" s="11">
-        <f t="shared" si="20"/>
-        <v>-3.993055555555558E-2</v>
-      </c>
-      <c r="V44" s="3"/>
+      <c r="T44" s="10">
+        <f t="shared" si="23"/>
+        <v>0.12202380952380953</v>
+      </c>
+      <c r="U44" s="10">
+        <f t="shared" si="23"/>
+        <v>-9.1405835543766356E-3</v>
+      </c>
+      <c r="V44" s="10">
+        <f t="shared" si="25"/>
+        <v>-3.3043861574676314E-2</v>
+      </c>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
@@ -4699,52 +4983,64 @@
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="11">
-        <f t="shared" si="19"/>
-        <v>0.11538461538461542</v>
-      </c>
-      <c r="J45" s="11">
-        <f t="shared" si="19"/>
-        <v>6.8965517241379226E-2</v>
-      </c>
-      <c r="K45" s="11">
-        <f t="shared" si="19"/>
-        <v>0.13043478260869557</v>
-      </c>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
+      <c r="G45" s="10">
+        <f t="shared" si="21"/>
+        <v>7.4468085106383031E-2</v>
+      </c>
+      <c r="H45" s="10">
+        <f t="shared" si="21"/>
+        <v>5.3571428571428603E-2</v>
+      </c>
+      <c r="I45" s="10">
+        <f t="shared" si="21"/>
+        <v>3.0716723549488067E-2</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="21"/>
+        <v>0.15387606837606871</v>
+      </c>
+      <c r="K45" s="10">
+        <f t="shared" si="24"/>
+        <v>-2.3102310231023049E-2</v>
+      </c>
+      <c r="L45" s="10">
+        <f t="shared" si="22"/>
+        <v>4.237288135593209E-3</v>
+      </c>
+      <c r="M45" s="10">
+        <f t="shared" si="22"/>
+        <v>-6.9536423841059625E-2</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="22"/>
+        <v>9.0268030088108908E-2</v>
+      </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
-      <c r="Q45" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q45" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R45" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R45" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S45" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S45" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T45" s="11">
-        <f t="shared" si="20"/>
-        <v>0.13043478260869557</v>
-      </c>
-      <c r="U45" s="11">
-        <f t="shared" si="20"/>
-        <v>4.8076923076923128E-2</v>
-      </c>
-      <c r="V45" s="3"/>
+      <c r="T45" s="10">
+        <f t="shared" si="23"/>
+        <v>0.15418994413407816</v>
+      </c>
+      <c r="U45" s="10">
+        <f t="shared" si="23"/>
+        <v>7.5515004840271072E-2</v>
+      </c>
+      <c r="V45" s="10">
+        <f t="shared" si="25"/>
+        <v>-2.3645215556696852E-3</v>
+      </c>
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
@@ -4793,52 +5089,64 @@
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="11">
-        <f t="shared" si="17"/>
-        <v>1.4432989690721598E-2</v>
-      </c>
-      <c r="H46" s="11">
-        <f t="shared" si="17"/>
-        <v>-2.931034482758621E-2</v>
-      </c>
-      <c r="I46" s="11">
-        <f t="shared" si="19"/>
-        <v>-4.2226487523992273E-2</v>
-      </c>
-      <c r="J46" s="11">
-        <f t="shared" si="19"/>
-        <v>1.4792899408284654E-3</v>
-      </c>
-      <c r="K46" s="11">
-        <f t="shared" si="19"/>
-        <v>-3.8617886178861749E-2</v>
-      </c>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
+      <c r="G46" s="10">
+        <f t="shared" si="21"/>
+        <v>9.550561797752799E-2</v>
+      </c>
+      <c r="H46" s="10">
+        <f t="shared" si="21"/>
+        <v>-3.5714285714285698E-2</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="21"/>
+        <v>6.4171122994652441E-2</v>
+      </c>
+      <c r="J46" s="10">
+        <f t="shared" si="21"/>
+        <v>0.10950632911392399</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="24"/>
+        <v>4.6153846153846212E-2</v>
+      </c>
+      <c r="L46" s="10">
+        <f t="shared" si="22"/>
+        <v>5.2910052910053018E-2</v>
+      </c>
+      <c r="M46" s="10">
+        <f t="shared" si="22"/>
+        <v>1.0050251256281451E-2</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="22"/>
+        <v>9.0126372393545928E-2</v>
+      </c>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
-      <c r="Q46" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q46" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R46" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R46" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S46" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S46" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T46" s="11">
-        <f t="shared" si="20"/>
-        <v>0.12202380952380953</v>
-      </c>
-      <c r="U46" s="11">
-        <f t="shared" si="20"/>
-        <v>-1.3704686118479192E-2</v>
-      </c>
-      <c r="V46" s="3"/>
+      <c r="T46" s="10">
+        <f t="shared" si="23"/>
+        <v>0.2314814814814814</v>
+      </c>
+      <c r="U46" s="10">
+        <f t="shared" si="23"/>
+        <v>6.0091478696741918E-2</v>
+      </c>
+      <c r="V46" s="10">
+        <f t="shared" si="25"/>
+        <v>5.2838632879131708E-2</v>
+      </c>
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
@@ -4887,52 +5195,64 @@
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="11">
-        <f t="shared" si="17"/>
-        <v>7.4468085106383031E-2</v>
-      </c>
-      <c r="H47" s="11">
-        <f t="shared" si="17"/>
-        <v>5.3571428571428603E-2</v>
-      </c>
-      <c r="I47" s="11">
-        <f t="shared" si="19"/>
-        <v>3.0716723549488067E-2</v>
-      </c>
-      <c r="J47" s="11">
-        <f t="shared" si="19"/>
-        <v>0.15384615384615374</v>
-      </c>
-      <c r="K47" s="11">
-        <f t="shared" si="19"/>
-        <v>-2.3102310231023049E-2</v>
-      </c>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
+      <c r="G47" s="10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" si="21"/>
+        <v>0.11538461538461542</v>
+      </c>
+      <c r="J47" s="10">
+        <f t="shared" si="21"/>
+        <v>7.1206896551724075E-2</v>
+      </c>
+      <c r="K47" s="10">
+        <f t="shared" si="24"/>
+        <v>0.13043478260869557</v>
+      </c>
+      <c r="L47" s="10">
+        <f t="shared" si="22"/>
+        <v>-7.6923076923076872E-2</v>
+      </c>
+      <c r="M47" s="10">
+        <f t="shared" si="22"/>
+        <v>-0.13793103448275867</v>
+      </c>
+      <c r="N47" s="10">
+        <f t="shared" si="22"/>
+        <v>-8.1152422340254327E-2</v>
+      </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
-      <c r="Q47" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="Q47" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R47" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R47" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S47" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S47" s="10" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T47" s="11">
-        <f t="shared" si="20"/>
-        <v>0.15418994413407816</v>
-      </c>
-      <c r="U47" s="11">
-        <f t="shared" si="20"/>
-        <v>7.5508228460793747E-2</v>
-      </c>
-      <c r="V47" s="3"/>
+      <c r="T47" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13043478260869557</v>
+      </c>
+      <c r="U47" s="10">
+        <f t="shared" si="23"/>
+        <v>4.8701923076923004E-2</v>
+      </c>
+      <c r="V47" s="10">
+        <f t="shared" si="25"/>
+        <v>-5.0621189199101413E-2</v>
+      </c>
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
@@ -4974,60 +5294,72 @@
       <c r="BI47" s="3"/>
     </row>
     <row r="48" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="11">
-        <f t="shared" si="17"/>
-        <v>9.550561797752799E-2</v>
-      </c>
-      <c r="H48" s="11">
-        <f t="shared" si="17"/>
-        <v>-3.5714285714285698E-2</v>
-      </c>
-      <c r="I48" s="11">
-        <f t="shared" si="19"/>
-        <v>6.4171122994652441E-2</v>
-      </c>
-      <c r="J48" s="11">
-        <f t="shared" si="19"/>
-        <v>0.10970464135021096</v>
-      </c>
-      <c r="K48" s="11">
-        <f t="shared" si="19"/>
-        <v>4.6153846153846212E-2</v>
-      </c>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="12">
+        <f t="shared" ref="G48:H48" si="26">+G20/C20-1</f>
+        <v>4.7520661157024691E-2</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="26"/>
+        <v>-1.0721247563352798E-2</v>
+      </c>
+      <c r="I48" s="12">
+        <f>+I20/E20-1</f>
+        <v>1.9474196689386325E-3</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" ref="J48:K48" si="27">+J20/F20-1</f>
+        <v>6.2074829931972886E-2</v>
+      </c>
+      <c r="K48" s="12">
+        <f t="shared" si="27"/>
+        <v>-1.4792899408283988E-2</v>
+      </c>
+      <c r="L48" s="12">
+        <f t="shared" si="22"/>
+        <v>-1.2807881773398977E-2</v>
+      </c>
+      <c r="M48" s="12">
+        <f t="shared" si="22"/>
+        <v>-3.8872691933916403E-2</v>
+      </c>
+      <c r="N48" s="12">
+        <f t="shared" si="22"/>
+        <v>2.4690152121697118E-2</v>
+      </c>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="12" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R48" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="R48" s="12" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S48" s="11" t="e">
-        <f t="shared" si="18"/>
+      <c r="S48" s="12" t="e">
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T48" s="11">
-        <f t="shared" si="20"/>
-        <v>0.2314814814814814</v>
-      </c>
-      <c r="U48" s="11">
-        <f t="shared" si="20"/>
-        <v>6.0150375939849621E-2</v>
-      </c>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
+      <c r="T48" s="12">
+        <f t="shared" si="23"/>
+        <v>0.14954806902218576</v>
+      </c>
+      <c r="U48" s="12">
+        <f t="shared" si="23"/>
+        <v>2.6209197045508725E-2</v>
+      </c>
+      <c r="V48" s="12">
+        <f t="shared" si="25"/>
+        <v>-8.6282795449269534E-3</v>
+      </c>
+      <c r="W48" s="11"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
@@ -5068,60 +5400,87 @@
       <c r="BI48" s="3"/>
     </row>
     <row r="49" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="13">
-        <f t="shared" ref="G49:H49" si="21">+G21/C21-1</f>
-        <v>4.7520661157024691E-2</v>
-      </c>
-      <c r="H49" s="13">
-        <f t="shared" si="21"/>
-        <v>-1.0721247563352798E-2</v>
-      </c>
-      <c r="I49" s="13">
-        <f>+I21/E21-1</f>
-        <v>1.9474196689386325E-3</v>
-      </c>
-      <c r="J49" s="13">
-        <f t="shared" ref="J49:K49" si="22">+J21/F21-1</f>
-        <v>6.2074829931972886E-2</v>
-      </c>
-      <c r="K49" s="13">
-        <f t="shared" si="22"/>
-        <v>-1.4792899408283988E-2</v>
-      </c>
-      <c r="L49" s="11"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="12"/>
-      <c r="P49" s="12"/>
-      <c r="Q49" s="13" t="e">
-        <f t="shared" ref="Q49:S49" si="23">+Q21/P21-1</f>
+      <c r="C49" s="10">
+        <f t="shared" ref="C49:H49" si="28">+C22/C20</f>
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="28"/>
+        <v>0.62378167641325533</v>
+      </c>
+      <c r="E49" s="10">
+        <f t="shared" si="28"/>
+        <v>0.60662122687439146</v>
+      </c>
+      <c r="F49" s="10">
+        <f t="shared" si="28"/>
+        <v>0.61479591836734693</v>
+      </c>
+      <c r="G49" s="10">
+        <f t="shared" si="28"/>
+        <v>0.61439842209072981</v>
+      </c>
+      <c r="H49" s="10">
+        <f t="shared" si="28"/>
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="I49" s="10">
+        <f>+I22/I20</f>
+        <v>0.60155490767735664</v>
+      </c>
+      <c r="J49" s="10">
+        <f>+J22/J20</f>
+        <v>0.62369895916733387</v>
+      </c>
+      <c r="K49" s="10">
+        <f>+K22/K20</f>
+        <v>0.61361361361361366</v>
+      </c>
+      <c r="L49" s="10">
+        <f t="shared" ref="L49:N49" si="29">+L22/L20</f>
+        <v>0.62874251497005984</v>
+      </c>
+      <c r="M49" s="10">
+        <f t="shared" si="29"/>
+        <v>0.61172901921132461</v>
+      </c>
+      <c r="N49" s="10">
+        <f t="shared" si="29"/>
+        <v>0.60818634858474263</v>
+      </c>
+      <c r="O49" s="3"/>
+      <c r="P49" s="10" t="e">
+        <f t="shared" ref="P49:S49" si="30">+P22/P20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R49" s="13" t="e">
-        <f t="shared" si="23"/>
+      <c r="Q49" s="10" t="e">
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S49" s="13" t="e">
-        <f t="shared" si="23"/>
+      <c r="R49" s="10" t="e">
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T49" s="13">
-        <f>+T21/S21-1</f>
-        <v>0.14954806902218576</v>
-      </c>
-      <c r="U49" s="13">
-        <f>+U21/T21-1</f>
-        <v>2.6209197045508725E-2</v>
-      </c>
-      <c r="V49" s="12"/>
-      <c r="W49" s="12"/>
+      <c r="S49" s="10">
+        <f t="shared" si="30"/>
+        <v>0.61791290057518489</v>
+      </c>
+      <c r="T49" s="10">
+        <f>+T22/T20</f>
+        <v>0.6147248034310222</v>
+      </c>
+      <c r="U49" s="10">
+        <f>+U22/U20</f>
+        <v>0.61736707685163683</v>
+      </c>
+      <c r="V49" s="10">
+        <f>+V22/V20</f>
+        <v>0.61510061974248198</v>
+      </c>
+      <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
@@ -5165,71 +5524,83 @@
       <c r="B50" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="11">
-        <f t="shared" ref="C50:H50" si="24">+C23/C21</f>
-        <v>0.61363636363636365</v>
-      </c>
-      <c r="D50" s="11">
-        <f t="shared" si="24"/>
-        <v>0.62378167641325533</v>
-      </c>
-      <c r="E50" s="11">
-        <f t="shared" si="24"/>
-        <v>0.60662122687439146</v>
-      </c>
-      <c r="F50" s="11">
-        <f t="shared" si="24"/>
-        <v>0.61479591836734693</v>
-      </c>
-      <c r="G50" s="11">
-        <f t="shared" si="24"/>
-        <v>0.61439842209072981</v>
-      </c>
-      <c r="H50" s="11">
-        <f t="shared" si="24"/>
-        <v>0.62857142857142856</v>
-      </c>
-      <c r="I50" s="11">
-        <f>+I23/I21</f>
-        <v>0.60155490767735664</v>
-      </c>
-      <c r="J50" s="11">
-        <f>+J23/J21</f>
-        <v>0.62369895916733387</v>
-      </c>
-      <c r="K50" s="11">
-        <f>+K23/K21</f>
-        <v>0.61361361361361366</v>
-      </c>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
+      <c r="C50" s="10">
+        <f t="shared" ref="C50:H50" si="31">+C25/C20</f>
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="31"/>
+        <v>0.1189083820662768</v>
+      </c>
+      <c r="E50" s="10">
+        <f t="shared" si="31"/>
+        <v>0.10029211295034079</v>
+      </c>
+      <c r="F50" s="10">
+        <f t="shared" si="31"/>
+        <v>0.10034013605442177</v>
+      </c>
+      <c r="G50" s="10">
+        <f t="shared" si="31"/>
+        <v>6.8047337278106509E-2</v>
+      </c>
+      <c r="H50" s="10">
+        <f t="shared" si="31"/>
+        <v>6.9950738916256153E-2</v>
+      </c>
+      <c r="I50" s="10">
+        <f>+I25/I20</f>
+        <v>9.23226433430515E-2</v>
+      </c>
+      <c r="J50" s="10">
+        <f>+J25/J20</f>
+        <v>0.10008006405124099</v>
+      </c>
+      <c r="K50" s="10">
+        <f>+K25/K20</f>
+        <v>6.2062062062062065E-2</v>
+      </c>
+      <c r="L50" s="10">
+        <f t="shared" ref="L50:N50" si="32">+L25/L20</f>
+        <v>8.0838323353293412E-2</v>
+      </c>
+      <c r="M50" s="10">
+        <f t="shared" si="32"/>
+        <v>9.6056622851365014E-2</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="32"/>
+        <v>0.11935338691303098</v>
+      </c>
       <c r="O50" s="3"/>
-      <c r="P50" s="11" t="e">
-        <f t="shared" ref="P50:S50" si="25">+P23/P21</f>
+      <c r="P50" s="10" t="e">
+        <f t="shared" ref="P50:S50" si="33">+P25/P20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q50" s="11" t="e">
-        <f t="shared" si="25"/>
+      <c r="Q50" s="10" t="e">
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R50" s="11" t="e">
-        <f t="shared" si="25"/>
+      <c r="R50" s="10" t="e">
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S50" s="11">
-        <f t="shared" si="25"/>
-        <v>0.61791290057518489</v>
-      </c>
-      <c r="T50" s="11">
-        <f>+T23/T21</f>
-        <v>0.6147248034310222</v>
-      </c>
-      <c r="U50" s="11">
-        <f>+U23/U21</f>
-        <v>0.61736707685163683</v>
-      </c>
-      <c r="V50" s="3"/>
+      <c r="S50" s="10">
+        <f t="shared" si="33"/>
+        <v>9.1755683374417973E-2</v>
+      </c>
+      <c r="T50" s="10">
+        <f>+T25/T20</f>
+        <v>9.7450559923755065E-2</v>
+      </c>
+      <c r="U50" s="10">
+        <f>+U25/U20</f>
+        <v>8.3584861852797773E-2</v>
+      </c>
+      <c r="V50" s="10">
+        <f>+V25/V20</f>
+        <v>9.1514713204575854E-2</v>
+      </c>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
@@ -5274,71 +5645,83 @@
       <c r="B51" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="11">
-        <f t="shared" ref="C51:H51" si="26">+C26/C21</f>
-        <v>6.8181818181818177E-2</v>
-      </c>
-      <c r="D51" s="11">
-        <f t="shared" si="26"/>
-        <v>0.1189083820662768</v>
-      </c>
-      <c r="E51" s="11">
-        <f t="shared" si="26"/>
-        <v>0.10029211295034079</v>
-      </c>
-      <c r="F51" s="11">
-        <f t="shared" si="26"/>
-        <v>0.10034013605442177</v>
-      </c>
-      <c r="G51" s="11">
-        <f t="shared" si="26"/>
-        <v>6.8047337278106509E-2</v>
-      </c>
-      <c r="H51" s="11">
-        <f t="shared" si="26"/>
-        <v>6.9950738916256153E-2</v>
-      </c>
-      <c r="I51" s="11">
-        <f>+I26/I21</f>
-        <v>9.23226433430515E-2</v>
-      </c>
-      <c r="J51" s="11">
-        <f>+J26/J21</f>
-        <v>0.10008006405124099</v>
-      </c>
-      <c r="K51" s="11">
-        <f>+K26/K21</f>
-        <v>6.2062062062062065E-2</v>
-      </c>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
+      <c r="C51" s="10">
+        <f t="shared" ref="C51:H51" si="34">+C28/C27</f>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="D51" s="10">
+        <f t="shared" si="34"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="E51" s="10">
+        <f t="shared" si="34"/>
+        <v>0.28409090909090912</v>
+      </c>
+      <c r="F51" s="10">
+        <f t="shared" si="34"/>
+        <v>0.16346153846153846</v>
+      </c>
+      <c r="G51" s="10">
+        <f t="shared" si="34"/>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="H51" s="10">
+        <f t="shared" si="34"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="I51" s="10">
+        <f>+I28/I27</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J51" s="10">
+        <f>+J28/J27</f>
+        <v>0.22321428571428573</v>
+      </c>
+      <c r="K51" s="10">
+        <f>+K28/K27</f>
+        <v>0.28301886792452829</v>
+      </c>
+      <c r="L51" s="10">
+        <f t="shared" ref="L51:N51" si="35">+L28/L27</f>
+        <v>0.27536231884057971</v>
+      </c>
+      <c r="M51" s="10">
+        <f t="shared" si="35"/>
+        <v>0.27710843373493976</v>
+      </c>
+      <c r="N51" s="10">
+        <f t="shared" si="35"/>
+        <v>0.20426593827760817</v>
+      </c>
       <c r="O51" s="3"/>
-      <c r="P51" s="11" t="e">
-        <f t="shared" ref="P51:S51" si="27">+P26/P21</f>
+      <c r="P51" s="10" t="e">
+        <f t="shared" ref="P51:S51" si="36">+P28/P27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q51" s="11" t="e">
-        <f t="shared" si="27"/>
+      <c r="Q51" s="10" t="e">
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R51" s="11" t="e">
-        <f t="shared" si="27"/>
+      <c r="R51" s="10" t="e">
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S51" s="11">
-        <f t="shared" si="27"/>
-        <v>9.1755683374417973E-2</v>
-      </c>
-      <c r="T51" s="11">
-        <f>+T26/T21</f>
-        <v>9.7450559923755065E-2</v>
-      </c>
-      <c r="U51" s="11">
-        <f>+U26/U21</f>
-        <v>8.3584861852797773E-2</v>
-      </c>
-      <c r="V51" s="3"/>
+      <c r="S51" s="10">
+        <f t="shared" si="36"/>
+        <v>0.22105263157894736</v>
+      </c>
+      <c r="T51" s="10">
+        <f>+T28/T27</f>
+        <v>0.2443820224719101</v>
+      </c>
+      <c r="U51" s="10">
+        <f>+U28/U27</f>
+        <v>0.25913621262458469</v>
+      </c>
+      <c r="V51" s="10">
+        <f>+V28/V27</f>
+        <v>0.24812673262733018</v>
+      </c>
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
@@ -5380,73 +5763,25 @@
       <c r="BI51" s="3"/>
     </row>
     <row r="52" spans="2:61" x14ac:dyDescent="0.2">
-      <c r="B52" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="11">
-        <f t="shared" ref="C52:H52" si="28">+C29/C28</f>
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="D52" s="11">
-        <f t="shared" si="28"/>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="E52" s="11">
-        <f t="shared" si="28"/>
-        <v>0.28409090909090912</v>
-      </c>
-      <c r="F52" s="11">
-        <f t="shared" si="28"/>
-        <v>0.16346153846153846</v>
-      </c>
-      <c r="G52" s="11">
-        <f t="shared" si="28"/>
-        <v>0.2807017543859649</v>
-      </c>
-      <c r="H52" s="11">
-        <f t="shared" si="28"/>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="I52" s="11">
-        <f>+I29/I28</f>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="J52" s="11">
-        <f>+J29/J28</f>
-        <v>0.22321428571428573</v>
-      </c>
-      <c r="K52" s="11">
-        <f>+K29/K28</f>
-        <v>0.28301886792452829</v>
-      </c>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="11" t="e">
-        <f t="shared" ref="P52:S52" si="29">+P29/P28</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q52" s="11" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R52" s="11" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S52" s="11">
-        <f t="shared" si="29"/>
-        <v>0.22105263157894736</v>
-      </c>
-      <c r="T52" s="11">
-        <f>+T29/T28</f>
-        <v>0.2443820224719101</v>
-      </c>
-      <c r="U52" s="11">
-        <f>+U29/U28</f>
-        <v>0.25913621262458469</v>
-      </c>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
@@ -15553,67 +15888,6 @@
       <c r="BH217" s="3"/>
       <c r="BI217" s="3"/>
     </row>
-    <row r="218" spans="3:61" x14ac:dyDescent="0.2">
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-      <c r="F218" s="3"/>
-      <c r="G218" s="3"/>
-      <c r="H218" s="3"/>
-      <c r="I218" s="3"/>
-      <c r="J218" s="3"/>
-      <c r="K218" s="3"/>
-      <c r="L218" s="3"/>
-      <c r="M218" s="3"/>
-      <c r="N218" s="3"/>
-      <c r="O218" s="3"/>
-      <c r="P218" s="3"/>
-      <c r="Q218" s="3"/>
-      <c r="R218" s="3"/>
-      <c r="S218" s="3"/>
-      <c r="T218" s="3"/>
-      <c r="U218" s="3"/>
-      <c r="V218" s="3"/>
-      <c r="W218" s="3"/>
-      <c r="X218" s="3"/>
-      <c r="Y218" s="3"/>
-      <c r="Z218" s="3"/>
-      <c r="AA218" s="3"/>
-      <c r="AB218" s="3"/>
-      <c r="AC218" s="3"/>
-      <c r="AD218" s="3"/>
-      <c r="AE218" s="3"/>
-      <c r="AF218" s="3"/>
-      <c r="AG218" s="3"/>
-      <c r="AH218" s="3"/>
-      <c r="AI218" s="3"/>
-      <c r="AJ218" s="3"/>
-      <c r="AK218" s="3"/>
-      <c r="AL218" s="3"/>
-      <c r="AM218" s="3"/>
-      <c r="AN218" s="3"/>
-      <c r="AO218" s="3"/>
-      <c r="AP218" s="3"/>
-      <c r="AQ218" s="3"/>
-      <c r="AR218" s="3"/>
-      <c r="AS218" s="3"/>
-      <c r="AT218" s="3"/>
-      <c r="AU218" s="3"/>
-      <c r="AV218" s="3"/>
-      <c r="AW218" s="3"/>
-      <c r="AX218" s="3"/>
-      <c r="AY218" s="3"/>
-      <c r="AZ218" s="3"/>
-      <c r="BA218" s="3"/>
-      <c r="BB218" s="3"/>
-      <c r="BC218" s="3"/>
-      <c r="BD218" s="3"/>
-      <c r="BE218" s="3"/>
-      <c r="BF218" s="3"/>
-      <c r="BG218" s="3"/>
-      <c r="BH218" s="3"/>
-      <c r="BI218" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{848A9855-F722-423E-95DB-AE2621A9CE62}"/>

--- a/BOSS.DE.xlsx
+++ b/BOSS.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2AE8AE-882C-45B3-9B5F-216374AD629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0933E8-840F-45A4-A0F5-165ACB6F5D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{09B18DE7-4EEF-4A72-AC57-80486CCDDA74}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{09B18DE7-4EEF-4A72-AC57-80486CCDDA74}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,19 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={086EDD8F-C502-47B8-A2FB-AA3518051BCF}</author>
     <author>tc={D81B57CA-BD4B-4035-AE68-E24052A657A2}</author>
   </authors>
   <commentList>
-    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
+    <comment ref="O11" authorId="0" shapeId="0" xr:uid="{086EDD8F-C502-47B8-A2FB-AA3518051BCF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Changed their sales reporting in Q126</t>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="1" shapeId="0" xr:uid="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="86">
   <si>
     <t>Hugo Boss</t>
   </si>
@@ -299,6 +308,21 @@
   <si>
     <t>There of freestanding retail stores</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
 </sst>
 </file>
 
@@ -307,13 +331,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -364,6 +394,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -384,29 +420,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -430,16 +473,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>14287</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>33338</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>28574</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>138113</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -454,7 +497,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9863137" y="33338"/>
+          <a:off x="10463212" y="0"/>
           <a:ext cx="14287" cy="8201025"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -804,6 +847,9 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="O11" dT="2026-05-14T15:17:21.38" personId="{BC3090F9-DCFB-461E-938B-BB97A04862C6}" id="{086EDD8F-C502-47B8-A2FB-AA3518051BCF}">
+    <text>Changed their sales reporting in Q126</text>
+  </threadedComment>
   <threadedComment ref="L20" dT="2025-05-06T11:33:50.96" personId="{BC3090F9-DCFB-461E-938B-BB97A04862C6}" id="{D81B57CA-BD4B-4035-AE68-E24052A657A2}">
     <text>Consensus of 4 analysts</text>
   </threadedComment>
@@ -832,7 +878,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>36.299999999999997</v>
+        <v>35.700000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -842,8 +888,8 @@
       <c r="J3" s="3">
         <v>69.016170000000002</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>75</v>
+      <c r="K3" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -855,7 +901,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>2505.286971</v>
+        <v>2463.8772690000001</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -866,10 +912,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>343.12599999999998</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>75</v>
+        <v>314</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -877,11 +923,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <f>93.258+202.512</f>
-        <v>295.77</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>75</v>
+        <v>297</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -890,7 +935,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>2457.9309710000002</v>
+        <v>2446.8772690000001</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -938,7 +983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20D4061-CFF8-435B-9C35-BFCD41DEF5B1}">
-  <dimension ref="A1:BI217"/>
+  <dimension ref="A1:BM217"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -946,12 +991,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -988,29 +1033,41 @@
       <c r="N2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="Z2" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
@@ -1027,7 +1084,7 @@
         <v>587</v>
       </c>
       <c r="F3" s="7">
-        <f>+T3</f>
+        <f>+X3</f>
         <v>587</v>
       </c>
       <c r="G3" s="7">
@@ -1057,31 +1114,33 @@
         <v>558</v>
       </c>
       <c r="N3" s="7">
-        <f>+V3</f>
+        <f>+Z3</f>
         <v>540</v>
       </c>
-      <c r="O3" s="7"/>
+      <c r="O3" s="7">
+        <v>522</v>
+      </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="S3" s="7">
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7">
         <f>581</f>
         <v>581</v>
       </c>
-      <c r="T3" s="7">
+      <c r="X3" s="7">
         <f>587</f>
         <v>587</v>
       </c>
-      <c r="U3" s="7">
+      <c r="Y3" s="7">
         <v>572</v>
       </c>
-      <c r="V3" s="7">
+      <c r="Z3" s="7">
         <v>540</v>
       </c>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -1103,8 +1162,12 @@
       <c r="AS3" s="7"/>
       <c r="AT3" s="7"/>
       <c r="AU3" s="7"/>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV3" s="7"/>
+      <c r="AW3" s="7"/>
+      <c r="AX3" s="7"/>
+      <c r="AY3" s="7"/>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>33</v>
       </c>
@@ -1121,7 +1184,7 @@
         <v>456</v>
       </c>
       <c r="F4" s="7">
-        <f t="shared" ref="F4:F7" si="0">+T4</f>
+        <f t="shared" ref="F4:F7" si="0">+X4</f>
         <v>456</v>
       </c>
       <c r="G4" s="7">
@@ -1151,31 +1214,33 @@
         <v>559</v>
       </c>
       <c r="N4" s="7">
-        <f t="shared" ref="N4:N7" si="1">+V4</f>
+        <f t="shared" ref="N4:O7" si="1">+Z4</f>
         <v>558</v>
       </c>
-      <c r="O4" s="7"/>
+      <c r="O4" s="7">
+        <v>531</v>
+      </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="S4" s="7">
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7">
         <f>383</f>
         <v>383</v>
       </c>
-      <c r="T4" s="7">
+      <c r="X4" s="7">
         <f>456</f>
         <v>456</v>
       </c>
-      <c r="U4" s="7">
+      <c r="Y4" s="7">
         <v>579</v>
       </c>
-      <c r="V4" s="7">
+      <c r="Z4" s="7">
         <v>558</v>
       </c>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
@@ -1197,8 +1262,12 @@
       <c r="AS4" s="7"/>
       <c r="AT4" s="7"/>
       <c r="AU4" s="7"/>
-    </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV4" s="7"/>
+      <c r="AW4" s="7"/>
+      <c r="AX4" s="7"/>
+      <c r="AY4" s="7"/>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1248,28 +1317,30 @@
         <f t="shared" si="1"/>
         <v>364</v>
       </c>
-      <c r="O5" s="7"/>
+      <c r="O5" s="7">
+        <v>353</v>
+      </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="S5" s="7">
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
         <f>352</f>
         <v>352</v>
       </c>
-      <c r="T5" s="7">
+      <c r="X5" s="7">
         <f>375</f>
         <v>375</v>
       </c>
-      <c r="U5" s="7">
+      <c r="Y5" s="7">
         <v>381</v>
       </c>
-      <c r="V5" s="7">
+      <c r="Z5" s="7">
         <v>364</v>
       </c>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -1291,8 +1362,12 @@
       <c r="AS5" s="7"/>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
-    </row>
-    <row r="6" spans="1:47" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AV5" s="7"/>
+      <c r="AW5" s="7"/>
+      <c r="AX5" s="7"/>
+      <c r="AY5" s="7"/>
+    </row>
+    <row r="6" spans="1:51" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1" t="s">
         <v>78</v>
@@ -1337,27 +1412,30 @@
         <f t="shared" si="1"/>
         <v>1462</v>
       </c>
-      <c r="O6" s="8"/>
+      <c r="O6" s="8">
+        <f>+SUM(O3:O5)</f>
+        <v>1406</v>
+      </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
-      <c r="S6" s="8">
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8">
         <v>1316</v>
       </c>
-      <c r="T6" s="8">
+      <c r="X6" s="8">
         <v>1418</v>
       </c>
-      <c r="U6" s="8">
+      <c r="Y6" s="8">
         <v>1532</v>
       </c>
-      <c r="V6" s="8">
-        <f>+SUM(V3:V5)</f>
+      <c r="Z6" s="8">
+        <f>+SUM(Z3:Z5)</f>
         <v>1462</v>
       </c>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
@@ -1379,8 +1457,12 @@
       <c r="AS6" s="8"/>
       <c r="AT6" s="8"/>
       <c r="AU6" s="8"/>
-    </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV6" s="8"/>
+      <c r="AW6" s="8"/>
+      <c r="AX6" s="8"/>
+      <c r="AY6" s="8"/>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B7" s="14" t="s">
         <v>80</v>
       </c>
@@ -1422,26 +1504,28 @@
         <f t="shared" si="1"/>
         <v>485</v>
       </c>
-      <c r="O7" s="7"/>
+      <c r="O7" s="7">
+        <v>470</v>
+      </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="S7" s="7">
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7">
         <v>470</v>
       </c>
-      <c r="T7" s="7">
+      <c r="X7" s="7">
         <v>489</v>
       </c>
-      <c r="U7" s="7">
+      <c r="Y7" s="7">
         <v>500</v>
       </c>
-      <c r="V7" s="7">
+      <c r="Z7" s="7">
         <v>485</v>
       </c>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
@@ -1463,8 +1547,12 @@
       <c r="AS7" s="7"/>
       <c r="AT7" s="7"/>
       <c r="AU7" s="7"/>
-    </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV7" s="7"/>
+      <c r="AW7" s="7"/>
+      <c r="AX7" s="7"/>
+      <c r="AY7" s="7"/>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -1510,8 +1598,12 @@
       <c r="AS8" s="7"/>
       <c r="AT8" s="7"/>
       <c r="AU8" s="7"/>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV8" s="7"/>
+      <c r="AW8" s="7"/>
+      <c r="AX8" s="7"/>
+      <c r="AY8" s="7"/>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.2">
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -1557,8 +1649,12 @@
       <c r="AS9" s="7"/>
       <c r="AT9" s="7"/>
       <c r="AU9" s="7"/>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV9" s="7"/>
+      <c r="AW9" s="7"/>
+      <c r="AX9" s="7"/>
+      <c r="AY9" s="7"/>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
@@ -1572,7 +1668,7 @@
         <v>786</v>
       </c>
       <c r="F10" s="7">
-        <f>+T10-SUM(C10:E10)</f>
+        <f>+X10-SUM(C10:E10)</f>
         <v>914</v>
       </c>
       <c r="G10" s="7">
@@ -1585,7 +1681,7 @@
         <v>785</v>
       </c>
       <c r="J10" s="7">
-        <f>+U10-SUM(G10:I10)</f>
+        <f>+Y10-SUM(G10:I10)</f>
         <v>973</v>
       </c>
       <c r="K10" s="7">
@@ -1598,29 +1694,31 @@
         <v>764</v>
       </c>
       <c r="N10" s="7">
-        <f>+V10-SUM(K10:M10)</f>
+        <f>+Z10-SUM(K10:M10)</f>
         <v>1008</v>
       </c>
-      <c r="O10" s="7"/>
+      <c r="O10" s="7">
+        <v>779</v>
+      </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="S10" s="7">
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7">
         <v>2868</v>
       </c>
-      <c r="T10" s="7">
+      <c r="X10" s="7">
         <v>3256</v>
       </c>
-      <c r="U10" s="7">
+      <c r="Y10" s="7">
         <v>3329</v>
       </c>
-      <c r="V10" s="7">
+      <c r="Z10" s="7">
         <v>3346</v>
       </c>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
       <c r="AC10" s="7"/>
@@ -1642,8 +1740,12 @@
       <c r="AS10" s="7"/>
       <c r="AT10" s="7"/>
       <c r="AU10" s="7"/>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV10" s="7"/>
+      <c r="AW10" s="7"/>
+      <c r="AX10" s="7"/>
+      <c r="AY10" s="7"/>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
@@ -1657,7 +1759,7 @@
         <v>73</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" ref="F11:F30" si="2">+T11-SUM(C11:E11)</f>
+        <f>+X11-SUM(C11:E11)</f>
         <v>81</v>
       </c>
       <c r="G11" s="7">
@@ -1670,7 +1772,7 @@
         <v>74</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" ref="J11:J30" si="3">+U11-SUM(G11:I11)</f>
+        <f>+Y11-SUM(G11:I11)</f>
         <v>85</v>
       </c>
       <c r="K11" s="7">
@@ -1683,29 +1785,31 @@
         <v>67</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" ref="N11:N30" si="4">+V11-SUM(K11:M11)</f>
+        <f>+Z11-SUM(K11:M11)</f>
         <v>81</v>
       </c>
-      <c r="O11" s="7"/>
+      <c r="O11" s="17" t="s">
+        <v>85</v>
+      </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
-      <c r="S11" s="7">
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7">
         <v>239</v>
       </c>
-      <c r="T11" s="7">
+      <c r="X11" s="7">
         <v>288</v>
       </c>
-      <c r="U11" s="7">
+      <c r="Y11" s="7">
         <v>297</v>
       </c>
-      <c r="V11" s="7">
+      <c r="Z11" s="7">
         <v>280</v>
       </c>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
       <c r="AB11" s="7"/>
       <c r="AC11" s="7"/>
@@ -1727,8 +1831,12 @@
       <c r="AS11" s="7"/>
       <c r="AT11" s="7"/>
       <c r="AU11" s="7"/>
-    </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV11" s="7"/>
+      <c r="AW11" s="7"/>
+      <c r="AX11" s="7"/>
+      <c r="AY11" s="7"/>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>37</v>
       </c>
@@ -1742,7 +1850,7 @@
         <v>169</v>
       </c>
       <c r="F12" s="7">
-        <f t="shared" si="2"/>
+        <f>+X12-SUM(C12:E12)</f>
         <v>181</v>
       </c>
       <c r="G12" s="7">
@@ -1755,7 +1863,7 @@
         <v>171</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y12-SUM(G12:I12)</f>
         <v>192</v>
       </c>
       <c r="K12" s="7">
@@ -1768,29 +1876,31 @@
         <v>158</v>
       </c>
       <c r="N12" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z12-SUM(K12:M12)</f>
         <v>191</v>
       </c>
-      <c r="O12" s="7"/>
+      <c r="O12" s="7">
+        <v>125</v>
+      </c>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="7">
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7">
         <v>545</v>
       </c>
-      <c r="T12" s="7">
+      <c r="X12" s="7">
         <v>653</v>
       </c>
-      <c r="U12" s="7">
+      <c r="Y12" s="7">
         <v>682</v>
       </c>
-      <c r="V12" s="7">
+      <c r="Z12" s="7">
         <v>644</v>
       </c>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
@@ -1812,8 +1922,12 @@
       <c r="AS12" s="7"/>
       <c r="AT12" s="7"/>
       <c r="AU12" s="7"/>
-    </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV12" s="7"/>
+      <c r="AW12" s="7"/>
+      <c r="AX12" s="7"/>
+      <c r="AY12" s="7"/>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
@@ -1827,7 +1941,7 @@
         <v>653</v>
       </c>
       <c r="F13" s="7">
-        <f t="shared" si="2"/>
+        <f>+X13-SUM(C13:E13)</f>
         <v>680</v>
       </c>
       <c r="G13" s="7">
@@ -1840,7 +1954,7 @@
         <v>662</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y13-SUM(G13:I13)</f>
         <v>725</v>
       </c>
       <c r="K13" s="7">
@@ -1853,30 +1967,32 @@
         <v>641</v>
       </c>
       <c r="N13" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z13-SUM(K13:M13)</f>
         <v>878.16200000000026</v>
       </c>
-      <c r="O13" s="7"/>
+      <c r="O13" s="7">
+        <v>568</v>
+      </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
-      <c r="S13" s="7">
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7">
         <v>2303</v>
       </c>
-      <c r="T13" s="7">
+      <c r="X13" s="7">
         <v>2562</v>
       </c>
-      <c r="U13" s="7">
+      <c r="Y13" s="7">
         <v>2625</v>
       </c>
-      <c r="V13" s="7">
+      <c r="Z13" s="7">
         <f>2159.001+609.161</f>
         <v>2768.1620000000003</v>
       </c>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
       <c r="AC13" s="7"/>
@@ -1898,8 +2014,12 @@
       <c r="AS13" s="7"/>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
-    </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV13" s="7"/>
+      <c r="AW13" s="7"/>
+      <c r="AX13" s="7"/>
+      <c r="AY13" s="7"/>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
@@ -1913,7 +2033,7 @@
         <v>228</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="2"/>
+        <f>+X14-SUM(C14:E14)</f>
         <v>296</v>
       </c>
       <c r="G14" s="7">
@@ -1926,7 +2046,7 @@
         <v>228</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y14-SUM(G14:I14)</f>
         <v>324</v>
       </c>
       <c r="K14" s="7">
@@ -1939,30 +2059,32 @@
         <v>223</v>
       </c>
       <c r="N14" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z14-SUM(K14:M14)</f>
         <v>321.70000000000005</v>
       </c>
-      <c r="O14" s="7"/>
+      <c r="O14" s="7">
+        <v>188</v>
+      </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="7">
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7">
         <v>789</v>
       </c>
-      <c r="T14" s="7">
+      <c r="X14" s="7">
         <v>955</v>
       </c>
-      <c r="U14" s="7">
+      <c r="Y14" s="7">
         <v>1020</v>
       </c>
-      <c r="V14" s="7">
+      <c r="Z14" s="7">
         <f>629.726+362.974</f>
         <v>992.7</v>
       </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
       <c r="AB14" s="7"/>
       <c r="AC14" s="7"/>
@@ -1984,8 +2106,12 @@
       <c r="AS14" s="7"/>
       <c r="AT14" s="7"/>
       <c r="AU14" s="7"/>
-    </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV14" s="7"/>
+      <c r="AW14" s="7"/>
+      <c r="AX14" s="7"/>
+      <c r="AY14" s="7"/>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
@@ -1999,7 +2125,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="2"/>
+        <f>+X15-SUM(C15:E15)</f>
         <v>171</v>
       </c>
       <c r="G15" s="7">
@@ -2012,7 +2138,7 @@
         <v>110</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y15-SUM(G15:I15)</f>
         <v>170</v>
       </c>
       <c r="K15" s="7">
@@ -2025,30 +2151,32 @@
         <v>101</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z15-SUM(K15:M15)</f>
         <v>153.97500000000002</v>
       </c>
-      <c r="O15" s="7"/>
+      <c r="O15" s="7">
+        <v>123</v>
+      </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
-      <c r="S15" s="7">
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7">
         <v>467</v>
       </c>
-      <c r="T15" s="7">
+      <c r="X15" s="7">
         <v>576</v>
       </c>
-      <c r="U15" s="7">
+      <c r="Y15" s="7">
         <v>553</v>
       </c>
-      <c r="V15" s="7">
+      <c r="Z15" s="7">
         <f>199.667+309.308</f>
         <v>508.97500000000002</v>
       </c>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
       <c r="AC15" s="7"/>
@@ -2070,8 +2198,12 @@
       <c r="AS15" s="7"/>
       <c r="AT15" s="7"/>
       <c r="AU15" s="7"/>
-    </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AV15" s="7"/>
+      <c r="AW15" s="7"/>
+      <c r="AX15" s="7"/>
+      <c r="AY15" s="7"/>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
@@ -2085,7 +2217,7 @@
         <v>521</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="2"/>
+        <f>+X16-SUM(C16:E16)</f>
         <v>676</v>
       </c>
       <c r="G16" s="7">
@@ -2098,7 +2230,7 @@
         <v>499</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y16-SUM(G16:I16)</f>
         <v>687.32400000000007</v>
       </c>
       <c r="K16" s="7">
@@ -2111,29 +2243,31 @@
         <v>483</v>
       </c>
       <c r="N16" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z16-SUM(K16:M16)</f>
         <v>669.26200000000017</v>
       </c>
-      <c r="O16" s="7"/>
+      <c r="O16" s="7">
+        <v>510</v>
+      </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="7">
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7">
         <v>2016</v>
       </c>
-      <c r="T16" s="7">
+      <c r="X16" s="7">
         <v>2262</v>
       </c>
-      <c r="U16" s="7">
+      <c r="Y16" s="7">
         <v>2241.3240000000001</v>
       </c>
-      <c r="V16" s="7">
+      <c r="Z16" s="7">
         <v>2167.2620000000002</v>
       </c>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
       <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
       <c r="AC16" s="7"/>
@@ -2155,8 +2289,12 @@
       <c r="AS16" s="7"/>
       <c r="AT16" s="7"/>
       <c r="AU16" s="7"/>
-    </row>
-    <row r="17" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="AV16" s="7"/>
+      <c r="AW16" s="7"/>
+      <c r="AX16" s="7"/>
+      <c r="AY16" s="7"/>
+    </row>
+    <row r="17" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
@@ -2170,7 +2308,7 @@
         <v>293</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="2"/>
+        <f>+X17-SUM(C17:E17)</f>
         <v>234</v>
       </c>
       <c r="G17" s="7">
@@ -2183,7 +2321,7 @@
         <v>302</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y17-SUM(G17:I17)</f>
         <v>270.00700000000006</v>
       </c>
       <c r="K17" s="7">
@@ -2196,29 +2334,31 @@
         <v>281</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z17-SUM(K17:M17)</f>
         <v>294.38000000000011</v>
       </c>
-      <c r="O17" s="7"/>
+      <c r="O17" s="7">
+        <v>369</v>
+      </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
-      <c r="S17" s="7">
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7">
         <v>895</v>
       </c>
-      <c r="T17" s="7">
+      <c r="X17" s="7">
         <v>1033</v>
       </c>
-      <c r="U17" s="7">
+      <c r="Y17" s="7">
         <v>1111.0070000000001</v>
       </c>
-      <c r="V17" s="7">
+      <c r="Z17" s="7">
         <v>1108.3800000000001</v>
       </c>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
       <c r="AC17" s="7"/>
@@ -2240,8 +2380,12 @@
       <c r="AS17" s="7"/>
       <c r="AT17" s="7"/>
       <c r="AU17" s="7"/>
-    </row>
-    <row r="18" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="AV17" s="7"/>
+      <c r="AW17" s="7"/>
+      <c r="AX17" s="7"/>
+      <c r="AY17" s="7"/>
+    </row>
+    <row r="18" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>44</v>
       </c>
@@ -2255,7 +2399,7 @@
         <v>187</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="2"/>
+        <f>+X18-SUM(C18:E18)</f>
         <v>237</v>
       </c>
       <c r="G18" s="7">
@@ -2268,7 +2412,7 @@
         <v>199</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y18-SUM(G18:I18)</f>
         <v>262.95299999999997</v>
       </c>
       <c r="K18" s="7">
@@ -2281,29 +2425,31 @@
         <v>201</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z18-SUM(K18:M18)</f>
         <v>286.65200000000004</v>
       </c>
-      <c r="O18" s="7"/>
+      <c r="O18" s="17" t="s">
+        <v>85</v>
+      </c>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="7">
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7">
         <v>648</v>
       </c>
-      <c r="T18" s="7">
+      <c r="X18" s="7">
         <v>798</v>
       </c>
-      <c r="U18" s="7">
+      <c r="Y18" s="7">
         <v>845.95299999999997</v>
       </c>
-      <c r="V18" s="7">
+      <c r="Z18" s="7">
         <v>890.65200000000004</v>
       </c>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
       <c r="AA18" s="7"/>
       <c r="AB18" s="7"/>
       <c r="AC18" s="7"/>
@@ -2325,8 +2471,12 @@
       <c r="AS18" s="7"/>
       <c r="AT18" s="7"/>
       <c r="AU18" s="7"/>
-    </row>
-    <row r="19" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="AV18" s="7"/>
+      <c r="AW18" s="7"/>
+      <c r="AX18" s="7"/>
+      <c r="AY18" s="7"/>
+    </row>
+    <row r="19" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>41</v>
       </c>
@@ -2340,7 +2490,7 @@
         <v>26</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="2"/>
+        <f>+X19-SUM(C19:E19)</f>
         <v>29</v>
       </c>
       <c r="G19" s="7">
@@ -2353,7 +2503,7 @@
         <v>29</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y19-SUM(G19:I19)</f>
         <v>31.064999999999998</v>
       </c>
       <c r="K19" s="7">
@@ -2366,29 +2516,31 @@
         <v>25</v>
       </c>
       <c r="N19" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z19-SUM(K19:M19)</f>
         <v>28.543999999999997</v>
       </c>
-      <c r="O19" s="7"/>
+      <c r="O19" s="7">
+        <v>26</v>
+      </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
-      <c r="S19" s="7">
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7">
         <v>92</v>
       </c>
-      <c r="T19" s="7">
+      <c r="X19" s="7">
         <v>104</v>
       </c>
-      <c r="U19" s="7">
+      <c r="Y19" s="7">
         <v>109.065</v>
       </c>
-      <c r="V19" s="7">
+      <c r="Z19" s="7">
         <v>103.544</v>
       </c>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
       <c r="AC19" s="7"/>
@@ -2410,10 +2562,10 @@
       <c r="AS19" s="7"/>
       <c r="AT19" s="7"/>
       <c r="AU19" s="7"/>
-      <c r="AV19" s="3"/>
-      <c r="AW19" s="3"/>
-      <c r="AX19" s="3"/>
-      <c r="AY19" s="3"/>
+      <c r="AV19" s="7"/>
+      <c r="AW19" s="7"/>
+      <c r="AX19" s="7"/>
+      <c r="AY19" s="7"/>
       <c r="AZ19" s="3"/>
       <c r="BA19" s="3"/>
       <c r="BB19" s="3"/>
@@ -2424,8 +2576,12 @@
       <c r="BG19" s="3"/>
       <c r="BH19" s="3"/>
       <c r="BI19" s="3"/>
-    </row>
-    <row r="20" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ19" s="3"/>
+      <c r="BK19" s="3"/>
+      <c r="BL19" s="3"/>
+      <c r="BM19" s="3"/>
+    </row>
+    <row r="20" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2439,7 +2595,7 @@
         <v>1027</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="2"/>
+        <f>+X20-SUM(C20:E20)</f>
         <v>1176</v>
       </c>
       <c r="G20" s="8">
@@ -2452,7 +2608,7 @@
         <v>1029</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="3"/>
+        <f>+Y20-SUM(G20:I20)</f>
         <v>1249</v>
       </c>
       <c r="K20" s="8">
@@ -2465,29 +2621,31 @@
         <v>989</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="4"/>
+        <f>+Z20-SUM(K20:M20)</f>
         <v>1279.8379999999997</v>
       </c>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="8">
+      <c r="O20" s="8">
+        <v>905</v>
+      </c>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="8">
         <v>3651</v>
       </c>
-      <c r="T20" s="8">
+      <c r="X20" s="8">
         <v>4197</v>
       </c>
-      <c r="U20" s="8">
+      <c r="Y20" s="8">
         <v>4307</v>
       </c>
-      <c r="V20" s="8">
+      <c r="Z20" s="8">
         <v>4269.8379999999997</v>
       </c>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
       <c r="AB20" s="7"/>
       <c r="AC20" s="7"/>
@@ -2509,10 +2667,10 @@
       <c r="AS20" s="7"/>
       <c r="AT20" s="7"/>
       <c r="AU20" s="7"/>
-      <c r="AV20" s="3"/>
-      <c r="AW20" s="3"/>
-      <c r="AX20" s="3"/>
-      <c r="AY20" s="3"/>
+      <c r="AV20" s="7"/>
+      <c r="AW20" s="7"/>
+      <c r="AX20" s="7"/>
+      <c r="AY20" s="7"/>
       <c r="AZ20" s="3"/>
       <c r="BA20" s="3"/>
       <c r="BB20" s="3"/>
@@ -2523,8 +2681,12 @@
       <c r="BG20" s="3"/>
       <c r="BH20" s="3"/>
       <c r="BI20" s="3"/>
-    </row>
-    <row r="21" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ20" s="3"/>
+      <c r="BK20" s="3"/>
+      <c r="BL20" s="3"/>
+      <c r="BM20" s="3"/>
+    </row>
+    <row r="21" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2538,7 +2700,7 @@
         <v>404</v>
       </c>
       <c r="F21" s="7">
-        <f t="shared" si="2"/>
+        <f>+X21-SUM(C21:E21)</f>
         <v>453</v>
       </c>
       <c r="G21" s="7">
@@ -2551,7 +2713,7 @@
         <v>410</v>
       </c>
       <c r="J21" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y21-SUM(G21:I21)</f>
         <v>470</v>
       </c>
       <c r="K21" s="7">
@@ -2564,29 +2726,31 @@
         <v>384</v>
       </c>
       <c r="N21" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z21-SUM(K21:M21)</f>
         <v>501.45800000000008</v>
       </c>
-      <c r="O21" s="7"/>
+      <c r="O21" s="7">
+        <v>340</v>
+      </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
-      <c r="S21" s="7">
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7">
         <v>1395</v>
       </c>
-      <c r="T21" s="7">
+      <c r="X21" s="7">
         <v>1617</v>
       </c>
-      <c r="U21" s="7">
+      <c r="Y21" s="7">
         <v>1648</v>
       </c>
-      <c r="V21" s="7">
+      <c r="Z21" s="7">
         <v>1643.4580000000001</v>
       </c>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
       <c r="AC21" s="7"/>
@@ -2608,10 +2772,10 @@
       <c r="AS21" s="7"/>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
-      <c r="AV21" s="3"/>
-      <c r="AW21" s="3"/>
-      <c r="AX21" s="3"/>
-      <c r="AY21" s="3"/>
+      <c r="AV21" s="7"/>
+      <c r="AW21" s="7"/>
+      <c r="AX21" s="7"/>
+      <c r="AY21" s="7"/>
       <c r="AZ21" s="3"/>
       <c r="BA21" s="3"/>
       <c r="BB21" s="3"/>
@@ -2622,83 +2786,90 @@
       <c r="BG21" s="3"/>
       <c r="BH21" s="3"/>
       <c r="BI21" s="3"/>
-    </row>
-    <row r="22" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ21" s="3"/>
+      <c r="BK21" s="3"/>
+      <c r="BL21" s="3"/>
+      <c r="BM21" s="3"/>
+    </row>
+    <row r="22" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:H22" si="5">+C20-C21</f>
+        <f t="shared" ref="C22:H22" si="2">+C20-C21</f>
         <v>594</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>640</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>623</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>723</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>623</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>638</v>
       </c>
       <c r="I22" s="7">
-        <f>+I20-I21</f>
+        <f t="shared" ref="I22:O22" si="3">+I20-I21</f>
         <v>619</v>
       </c>
       <c r="J22" s="7">
-        <f>+J20-J21</f>
+        <f t="shared" si="3"/>
         <v>779</v>
       </c>
       <c r="K22" s="7">
-        <f>+K20-K21</f>
+        <f t="shared" si="3"/>
         <v>613</v>
       </c>
       <c r="L22" s="7">
-        <f>+L20-L21</f>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
       <c r="M22" s="7">
-        <f>+M20-M21</f>
+        <f t="shared" si="3"/>
         <v>605</v>
       </c>
       <c r="N22" s="7">
-        <f>+N20-N21</f>
+        <f t="shared" si="3"/>
         <v>778.37999999999965</v>
       </c>
-      <c r="O22" s="7"/>
+      <c r="O22" s="7">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
-      <c r="S22" s="7">
-        <f>+S20-S21</f>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7">
+        <f>+W20-W21</f>
         <v>2256</v>
       </c>
-      <c r="T22" s="7">
-        <f>+T20-T21</f>
+      <c r="X22" s="7">
+        <f>+X20-X21</f>
         <v>2580</v>
       </c>
-      <c r="U22" s="7">
-        <f>+U20-U21</f>
+      <c r="Y22" s="7">
+        <f>+Y20-Y21</f>
         <v>2659</v>
       </c>
-      <c r="V22" s="7">
-        <f>+V20-V21</f>
+      <c r="Z22" s="7">
+        <f>+Z20-Z21</f>
         <v>2626.3799999999997</v>
       </c>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
       <c r="AB22" s="7"/>
       <c r="AC22" s="7"/>
@@ -2720,10 +2891,10 @@
       <c r="AS22" s="7"/>
       <c r="AT22" s="7"/>
       <c r="AU22" s="7"/>
-      <c r="AV22" s="3"/>
-      <c r="AW22" s="3"/>
-      <c r="AX22" s="3"/>
-      <c r="AY22" s="3"/>
+      <c r="AV22" s="7"/>
+      <c r="AW22" s="7"/>
+      <c r="AX22" s="7"/>
+      <c r="AY22" s="7"/>
       <c r="AZ22" s="3"/>
       <c r="BA22" s="3"/>
       <c r="BB22" s="3"/>
@@ -2734,8 +2905,12 @@
       <c r="BG22" s="3"/>
       <c r="BH22" s="3"/>
       <c r="BI22" s="3"/>
-    </row>
-    <row r="23" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ22" s="3"/>
+      <c r="BK22" s="3"/>
+      <c r="BL22" s="3"/>
+      <c r="BM22" s="3"/>
+    </row>
+    <row r="23" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2749,7 +2924,7 @@
         <v>424</v>
       </c>
       <c r="F23" s="7">
-        <f t="shared" si="2"/>
+        <f>+X23-SUM(C23:E23)</f>
         <v>497</v>
       </c>
       <c r="G23" s="7">
@@ -2762,7 +2937,7 @@
         <v>433</v>
       </c>
       <c r="J23" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y23-SUM(G23:I23)</f>
         <v>543</v>
       </c>
       <c r="K23" s="7">
@@ -2775,29 +2950,31 @@
         <v>420</v>
       </c>
       <c r="N23" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z23-SUM(K23:M23)</f>
         <v>510.63699999999994</v>
       </c>
-      <c r="O23" s="7"/>
+      <c r="O23" s="7">
+        <v>410</v>
+      </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
-      <c r="S23" s="7">
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7">
         <v>1539</v>
       </c>
-      <c r="T23" s="7">
+      <c r="X23" s="7">
         <v>1745</v>
       </c>
-      <c r="U23" s="7">
+      <c r="Y23" s="7">
         <v>1868</v>
       </c>
-      <c r="V23" s="7">
+      <c r="Z23" s="7">
         <v>1804.6369999999999</v>
       </c>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
       <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
       <c r="AC23" s="7"/>
@@ -2819,10 +2996,10 @@
       <c r="AS23" s="7"/>
       <c r="AT23" s="7"/>
       <c r="AU23" s="7"/>
-      <c r="AV23" s="3"/>
-      <c r="AW23" s="3"/>
-      <c r="AX23" s="3"/>
-      <c r="AY23" s="3"/>
+      <c r="AV23" s="7"/>
+      <c r="AW23" s="7"/>
+      <c r="AX23" s="7"/>
+      <c r="AY23" s="7"/>
       <c r="AZ23" s="3"/>
       <c r="BA23" s="3"/>
       <c r="BB23" s="3"/>
@@ -2833,8 +3010,12 @@
       <c r="BG23" s="3"/>
       <c r="BH23" s="3"/>
       <c r="BI23" s="3"/>
-    </row>
-    <row r="24" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ23" s="3"/>
+      <c r="BK23" s="3"/>
+      <c r="BL23" s="3"/>
+      <c r="BM23" s="3"/>
+    </row>
+    <row r="24" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
@@ -2848,7 +3029,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" si="2"/>
+        <f>+X24-SUM(C24:E24)</f>
         <v>108</v>
       </c>
       <c r="G24" s="7">
@@ -2861,7 +3042,7 @@
         <v>91</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y24-SUM(G24:I24)</f>
         <v>111</v>
       </c>
       <c r="K24" s="7">
@@ -2874,29 +3055,31 @@
         <v>90</v>
       </c>
       <c r="N24" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z24-SUM(K24:M24)</f>
         <v>114.99000000000001</v>
       </c>
-      <c r="O24" s="7"/>
+      <c r="O24" s="7">
+        <v>119</v>
+      </c>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
-      <c r="S24" s="7">
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7">
         <v>382</v>
       </c>
-      <c r="T24" s="7">
+      <c r="X24" s="7">
         <v>426</v>
       </c>
-      <c r="U24" s="7">
+      <c r="Y24" s="7">
         <v>431</v>
       </c>
-      <c r="V24" s="7">
+      <c r="Z24" s="7">
         <v>430.99</v>
       </c>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
       <c r="AB24" s="7"/>
       <c r="AC24" s="7"/>
@@ -2918,10 +3101,10 @@
       <c r="AS24" s="7"/>
       <c r="AT24" s="7"/>
       <c r="AU24" s="7"/>
-      <c r="AV24" s="3"/>
-      <c r="AW24" s="3"/>
-      <c r="AX24" s="3"/>
-      <c r="AY24" s="3"/>
+      <c r="AV24" s="7"/>
+      <c r="AW24" s="7"/>
+      <c r="AX24" s="7"/>
+      <c r="AY24" s="7"/>
       <c r="AZ24" s="3"/>
       <c r="BA24" s="3"/>
       <c r="BB24" s="3"/>
@@ -2932,33 +3115,37 @@
       <c r="BG24" s="3"/>
       <c r="BH24" s="3"/>
       <c r="BI24" s="3"/>
-    </row>
-    <row r="25" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ24" s="3"/>
+      <c r="BK24" s="3"/>
+      <c r="BL24" s="3"/>
+      <c r="BM24" s="3"/>
+    </row>
+    <row r="25" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="7">
-        <f t="shared" ref="C25:H25" si="6">+C22-SUM(C23:C24)</f>
+        <f t="shared" ref="C25:H25" si="4">+C22-SUM(C23:C24)</f>
         <v>66</v>
       </c>
       <c r="D25" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>122</v>
       </c>
       <c r="E25" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>103</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>118</v>
       </c>
       <c r="G25" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>71</v>
       </c>
       <c r="I25" s="7">
@@ -2966,49 +3153,52 @@
         <v>95</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" ref="J25:N25" si="7">+J22-SUM(J23:J24)</f>
+        <f t="shared" ref="J25:O25" si="5">+J22-SUM(J23:J24)</f>
         <v>125</v>
       </c>
       <c r="K25" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>62</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>81</v>
       </c>
       <c r="M25" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>95</v>
       </c>
       <c r="N25" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>152.7529999999997</v>
       </c>
-      <c r="O25" s="7"/>
+      <c r="O25" s="7">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
-      <c r="S25" s="7">
-        <f>+S22-S23-S24</f>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7">
+        <f>+W22-W23-W24</f>
         <v>335</v>
       </c>
-      <c r="T25" s="7">
-        <f>+T22-T23-T24</f>
+      <c r="X25" s="7">
+        <f>+X22-X23-X24</f>
         <v>409</v>
       </c>
-      <c r="U25" s="7">
-        <f>+U22-U23-U24</f>
+      <c r="Y25" s="7">
+        <f>+Y22-Y23-Y24</f>
         <v>360</v>
       </c>
-      <c r="V25" s="7">
-        <f>+V22-V23-V24</f>
+      <c r="Z25" s="7">
+        <f>+Z22-Z23-Z24</f>
         <v>390.7529999999997</v>
       </c>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
       <c r="AC25" s="7"/>
@@ -3030,10 +3220,10 @@
       <c r="AS25" s="7"/>
       <c r="AT25" s="7"/>
       <c r="AU25" s="7"/>
-      <c r="AV25" s="3"/>
-      <c r="AW25" s="3"/>
-      <c r="AX25" s="3"/>
-      <c r="AY25" s="3"/>
+      <c r="AV25" s="7"/>
+      <c r="AW25" s="7"/>
+      <c r="AX25" s="7"/>
+      <c r="AY25" s="7"/>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
       <c r="BB25" s="3"/>
@@ -3044,8 +3234,12 @@
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
       <c r="BI25" s="3"/>
-    </row>
-    <row r="26" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ25" s="3"/>
+      <c r="BK25" s="3"/>
+      <c r="BL25" s="3"/>
+      <c r="BM25" s="3"/>
+    </row>
+    <row r="26" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>25</v>
       </c>
@@ -3059,7 +3253,7 @@
         <v>-15</v>
       </c>
       <c r="F26" s="7">
-        <f t="shared" si="2"/>
+        <f>+X26-SUM(C26:E26)</f>
         <v>-14</v>
       </c>
       <c r="G26" s="7">
@@ -3072,7 +3266,7 @@
         <v>-18</v>
       </c>
       <c r="J26" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y26-SUM(G26:I26)</f>
         <v>-13</v>
       </c>
       <c r="K26" s="7">
@@ -3085,29 +3279,31 @@
         <v>-12</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z26-SUM(K26:M26)</f>
         <v>-12.901000000000003</v>
       </c>
-      <c r="O26" s="7"/>
+      <c r="O26" s="7">
+        <v>-10</v>
+      </c>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
-      <c r="S26" s="7">
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7">
         <v>-50</v>
       </c>
-      <c r="T26" s="7">
+      <c r="X26" s="7">
         <v>-53</v>
       </c>
-      <c r="U26" s="7">
+      <c r="Y26" s="7">
         <v>-59</v>
       </c>
-      <c r="V26" s="7">
+      <c r="Z26" s="7">
         <v>-45.901000000000003</v>
       </c>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
       <c r="AA26" s="7"/>
       <c r="AB26" s="7"/>
       <c r="AC26" s="7"/>
@@ -3129,10 +3325,10 @@
       <c r="AS26" s="7"/>
       <c r="AT26" s="7"/>
       <c r="AU26" s="7"/>
-      <c r="AV26" s="3"/>
-      <c r="AW26" s="3"/>
-      <c r="AX26" s="3"/>
-      <c r="AY26" s="3"/>
+      <c r="AV26" s="7"/>
+      <c r="AW26" s="7"/>
+      <c r="AX26" s="7"/>
+      <c r="AY26" s="7"/>
       <c r="AZ26" s="3"/>
       <c r="BA26" s="3"/>
       <c r="BB26" s="3"/>
@@ -3143,33 +3339,37 @@
       <c r="BG26" s="3"/>
       <c r="BH26" s="3"/>
       <c r="BI26" s="3"/>
-    </row>
-    <row r="27" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ26" s="3"/>
+      <c r="BK26" s="3"/>
+      <c r="BL26" s="3"/>
+      <c r="BM26" s="3"/>
+    </row>
+    <row r="27" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" ref="C27:H27" si="8">+C25+C26</f>
+        <f t="shared" ref="C27:H27" si="6">+C25+C26</f>
         <v>54</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>110</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>88</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>104</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>57</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="I27" s="7">
@@ -3177,49 +3377,52 @@
         <v>77</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" ref="J27:N27" si="9">+J25+J26</f>
+        <f t="shared" ref="J27:O27" si="7">+J25+J26</f>
         <v>112</v>
       </c>
       <c r="K27" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>53</v>
       </c>
       <c r="L27" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>69</v>
       </c>
       <c r="M27" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="N27" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>139.85199999999969</v>
       </c>
-      <c r="O27" s="7"/>
+      <c r="O27" s="7">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
-      <c r="S27" s="7">
-        <f>+S25+S26</f>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7">
+        <f>+W25+W26</f>
         <v>285</v>
       </c>
-      <c r="T27" s="7">
-        <f>+T25+T26</f>
+      <c r="X27" s="7">
+        <f>+X25+X26</f>
         <v>356</v>
       </c>
-      <c r="U27" s="7">
-        <f>+U25+U26</f>
+      <c r="Y27" s="7">
+        <f>+Y25+Y26</f>
         <v>301</v>
       </c>
-      <c r="V27" s="7">
-        <f>+V25+V26</f>
+      <c r="Z27" s="7">
+        <f>+Z25+Z26</f>
         <v>344.85199999999969</v>
       </c>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
       <c r="AA27" s="7"/>
       <c r="AB27" s="7"/>
       <c r="AC27" s="7"/>
@@ -3241,10 +3444,10 @@
       <c r="AS27" s="7"/>
       <c r="AT27" s="7"/>
       <c r="AU27" s="7"/>
-      <c r="AV27" s="3"/>
-      <c r="AW27" s="3"/>
-      <c r="AX27" s="3"/>
-      <c r="AY27" s="3"/>
+      <c r="AV27" s="7"/>
+      <c r="AW27" s="7"/>
+      <c r="AX27" s="7"/>
+      <c r="AY27" s="7"/>
       <c r="AZ27" s="3"/>
       <c r="BA27" s="3"/>
       <c r="BB27" s="3"/>
@@ -3255,8 +3458,12 @@
       <c r="BG27" s="3"/>
       <c r="BH27" s="3"/>
       <c r="BI27" s="3"/>
-    </row>
-    <row r="28" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ27" s="3"/>
+      <c r="BK27" s="3"/>
+      <c r="BL27" s="3"/>
+      <c r="BM27" s="3"/>
+    </row>
+    <row r="28" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>27</v>
       </c>
@@ -3270,7 +3477,7 @@
         <v>25</v>
       </c>
       <c r="F28" s="7">
-        <f t="shared" si="2"/>
+        <f>+X28-SUM(C28:E28)</f>
         <v>17</v>
       </c>
       <c r="G28" s="7">
@@ -3283,7 +3490,7 @@
         <v>22</v>
       </c>
       <c r="J28" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y28-SUM(G28:I28)</f>
         <v>25</v>
       </c>
       <c r="K28" s="7">
@@ -3296,29 +3503,31 @@
         <v>23</v>
       </c>
       <c r="N28" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z28-SUM(K28:M28)</f>
         <v>28.566999999999993</v>
       </c>
-      <c r="O28" s="7"/>
+      <c r="O28" s="7">
+        <v>7</v>
+      </c>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
-      <c r="S28" s="7">
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7">
         <v>63</v>
       </c>
-      <c r="T28" s="7">
+      <c r="X28" s="7">
         <v>87</v>
       </c>
-      <c r="U28" s="7">
+      <c r="Y28" s="7">
         <v>78</v>
       </c>
-      <c r="V28" s="7">
+      <c r="Z28" s="7">
         <v>85.566999999999993</v>
       </c>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
       <c r="AB28" s="7"/>
       <c r="AC28" s="7"/>
@@ -3340,10 +3549,10 @@
       <c r="AS28" s="7"/>
       <c r="AT28" s="7"/>
       <c r="AU28" s="7"/>
-      <c r="AV28" s="3"/>
-      <c r="AW28" s="3"/>
-      <c r="AX28" s="3"/>
-      <c r="AY28" s="3"/>
+      <c r="AV28" s="7"/>
+      <c r="AW28" s="7"/>
+      <c r="AX28" s="7"/>
+      <c r="AY28" s="7"/>
       <c r="AZ28" s="3"/>
       <c r="BA28" s="3"/>
       <c r="BB28" s="3"/>
@@ -3354,33 +3563,37 @@
       <c r="BG28" s="3"/>
       <c r="BH28" s="3"/>
       <c r="BI28" s="3"/>
-    </row>
-    <row r="29" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ28" s="3"/>
+      <c r="BK28" s="3"/>
+      <c r="BL28" s="3"/>
+      <c r="BM28" s="3"/>
+    </row>
+    <row r="29" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="7">
-        <f t="shared" ref="C29:H29" si="10">+C27-C28</f>
+        <f t="shared" ref="C29:H29" si="8">+C27-C28</f>
         <v>39</v>
       </c>
       <c r="D29" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="E29" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>63</v>
       </c>
       <c r="F29" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="G29" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>41</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="I29" s="7">
@@ -3388,7 +3601,7 @@
         <v>55</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" ref="J29" si="11">+J27-J28</f>
+        <f t="shared" ref="J29" si="9">+J27-J28</f>
         <v>87</v>
       </c>
       <c r="K29" s="7">
@@ -3407,30 +3620,33 @@
         <f>+N27-N28</f>
         <v>111.2849999999997</v>
       </c>
-      <c r="O29" s="7"/>
+      <c r="O29" s="7">
+        <f>+O27-O28</f>
+        <v>19</v>
+      </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
-      <c r="S29" s="7">
-        <f>+S27-S28</f>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7">
+        <f>+W27-W28</f>
         <v>222</v>
       </c>
-      <c r="T29" s="7">
-        <f>+T27-T28</f>
+      <c r="X29" s="7">
+        <f>+X27-X28</f>
         <v>269</v>
       </c>
-      <c r="U29" s="7">
-        <f>+U27-U28</f>
+      <c r="Y29" s="7">
+        <f>+Y27-Y28</f>
         <v>223</v>
       </c>
-      <c r="V29" s="7">
-        <f>+V27-V28</f>
+      <c r="Z29" s="7">
+        <f>+Z27-Z28</f>
         <v>259.28499999999968</v>
       </c>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
       <c r="AC29" s="7"/>
@@ -3452,10 +3668,10 @@
       <c r="AS29" s="7"/>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
-      <c r="AV29" s="3"/>
-      <c r="AW29" s="3"/>
-      <c r="AX29" s="3"/>
-      <c r="AY29" s="3"/>
+      <c r="AV29" s="7"/>
+      <c r="AW29" s="7"/>
+      <c r="AX29" s="7"/>
+      <c r="AY29" s="7"/>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="3"/>
       <c r="BB29" s="3"/>
@@ -3466,8 +3682,12 @@
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
       <c r="BI29" s="3"/>
-    </row>
-    <row r="30" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ29" s="3"/>
+      <c r="BK29" s="3"/>
+      <c r="BL29" s="3"/>
+      <c r="BM29" s="3"/>
+    </row>
+    <row r="30" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>29</v>
       </c>
@@ -3481,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="7">
-        <f t="shared" si="2"/>
+        <f>+X30-SUM(C30:E30)</f>
         <v>4</v>
       </c>
       <c r="G30" s="7">
@@ -3494,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="7">
-        <f t="shared" si="3"/>
+        <f>+Y30-SUM(G30:I30)</f>
         <v>4</v>
       </c>
       <c r="K30" s="7">
@@ -3507,29 +3727,31 @@
         <v>1</v>
       </c>
       <c r="N30" s="7">
-        <f t="shared" si="4"/>
+        <f>+Z30-SUM(K30:M30)</f>
         <v>3.8049999999999997</v>
       </c>
-      <c r="O30" s="7"/>
+      <c r="O30" s="16">
+        <v>1</v>
+      </c>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
-      <c r="S30" s="7">
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7">
         <v>12</v>
       </c>
-      <c r="T30" s="7">
+      <c r="X30" s="7">
         <v>11</v>
       </c>
-      <c r="U30" s="7">
+      <c r="Y30" s="7">
         <v>10</v>
       </c>
-      <c r="V30" s="7">
+      <c r="Z30" s="7">
         <v>9.8049999999999997</v>
       </c>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7"/>
       <c r="AC30" s="7"/>
@@ -3551,10 +3773,10 @@
       <c r="AS30" s="7"/>
       <c r="AT30" s="7"/>
       <c r="AU30" s="7"/>
-      <c r="AV30" s="3"/>
-      <c r="AW30" s="3"/>
-      <c r="AX30" s="3"/>
-      <c r="AY30" s="3"/>
+      <c r="AV30" s="7"/>
+      <c r="AW30" s="7"/>
+      <c r="AX30" s="7"/>
+      <c r="AY30" s="7"/>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3"/>
@@ -3565,33 +3787,37 @@
       <c r="BG30" s="3"/>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3"/>
-    </row>
-    <row r="31" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ30" s="3"/>
+      <c r="BK30" s="3"/>
+      <c r="BL30" s="3"/>
+      <c r="BM30" s="3"/>
+    </row>
+    <row r="31" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="7">
-        <f t="shared" ref="C31:H31" si="12">+C29-C30</f>
+        <f t="shared" ref="C31:H31" si="10">+C29-C30</f>
         <v>35</v>
       </c>
       <c r="D31" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>77</v>
       </c>
       <c r="E31" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>63</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>83</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="I31" s="7">
@@ -3599,7 +3825,7 @@
         <v>54</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" ref="J31" si="13">+J29-J30</f>
+        <f t="shared" ref="J31" si="11">+J29-J30</f>
         <v>83</v>
       </c>
       <c r="K31" s="7">
@@ -3618,30 +3844,33 @@
         <f>+N29-N30</f>
         <v>107.47999999999971</v>
       </c>
-      <c r="O31" s="7"/>
+      <c r="O31" s="7">
+        <f>+O29-O30</f>
+        <v>18</v>
+      </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
-      <c r="S31" s="7">
-        <f>+S29-S30</f>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7">
+        <f>+W29-W30</f>
         <v>210</v>
       </c>
-      <c r="T31" s="7">
-        <f>+T29-T30</f>
+      <c r="X31" s="7">
+        <f>+X29-X30</f>
         <v>258</v>
       </c>
-      <c r="U31" s="7">
-        <f>+U29-U30</f>
+      <c r="Y31" s="7">
+        <f>+Y29-Y30</f>
         <v>213</v>
       </c>
-      <c r="V31" s="7">
-        <f>+V29-V30</f>
+      <c r="Z31" s="7">
+        <f>+Z29-Z30</f>
         <v>249.47999999999968</v>
       </c>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
       <c r="AA31" s="7"/>
       <c r="AB31" s="7"/>
       <c r="AC31" s="7"/>
@@ -3663,10 +3892,10 @@
       <c r="AS31" s="7"/>
       <c r="AT31" s="7"/>
       <c r="AU31" s="7"/>
-      <c r="AV31" s="3"/>
-      <c r="AW31" s="3"/>
-      <c r="AX31" s="3"/>
-      <c r="AY31" s="3"/>
+      <c r="AV31" s="7"/>
+      <c r="AW31" s="7"/>
+      <c r="AX31" s="7"/>
+      <c r="AY31" s="7"/>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="3"/>
       <c r="BB31" s="3"/>
@@ -3677,8 +3906,12 @@
       <c r="BG31" s="3"/>
       <c r="BH31" s="3"/>
       <c r="BI31" s="3"/>
-    </row>
-    <row r="32" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ31" s="3"/>
+      <c r="BK31" s="3"/>
+      <c r="BL31" s="3"/>
+      <c r="BM31" s="3"/>
+    </row>
+    <row r="32" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -3738,17 +3971,21 @@
       <c r="BG32" s="3"/>
       <c r="BH32" s="3"/>
       <c r="BI32" s="3"/>
-    </row>
-    <row r="33" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ32" s="3"/>
+      <c r="BK32" s="3"/>
+      <c r="BL32" s="3"/>
+      <c r="BM32" s="3"/>
+    </row>
+    <row r="33" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:D33" si="14">+C31/C34</f>
+        <f t="shared" ref="C33:D33" si="12">+C31/C34</f>
         <v>0.507127532576786</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1.1156805716689291</v>
       </c>
       <c r="E33" s="9">
@@ -3756,23 +3993,23 @@
         <v>0.9128295586382148</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" ref="F33:J33" si="15">+F31/F34</f>
+        <f t="shared" ref="F33:J33" si="13">+F31/F34</f>
         <v>1.2026167201106639</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.55059560679765329</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.55059560679765329</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.78242533597561259</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1.2026167201106639</v>
       </c>
       <c r="K33" s="9">
@@ -3791,39 +4028,42 @@
         <f>+N31/N34</f>
         <v>1.5573162057529373</v>
       </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="9" t="e">
-        <f t="shared" ref="P33:S33" si="16">+P31/P34</f>
+      <c r="O33" s="9" t="e">
+        <f>+O31/O34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="16"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="9" t="e">
+        <f t="shared" ref="T33:W33" si="14">+T31/T34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" s="9">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R33" s="9">
-        <f t="shared" si="16"/>
+      <c r="V33" s="9">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S33" s="9">
-        <f t="shared" si="16"/>
+      <c r="W33" s="9">
+        <f t="shared" si="14"/>
         <v>3.0427651954607158</v>
       </c>
-      <c r="T33" s="9">
-        <f>+T31/T34</f>
+      <c r="X33" s="9">
+        <f>+X31/X34</f>
         <v>3.7382543829945938</v>
       </c>
-      <c r="U33" s="9">
-        <f>+U31/U34</f>
+      <c r="Y33" s="9">
+        <f>+Y31/Y34</f>
         <v>3.0862332696815833</v>
       </c>
-      <c r="V33" s="9">
-        <f>+V31/V34</f>
+      <c r="Z33" s="9">
+        <f>+Z31/Z34</f>
         <v>3.6148050522073256</v>
       </c>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
@@ -3859,8 +4099,12 @@
       <c r="BG33" s="3"/>
       <c r="BH33" s="3"/>
       <c r="BI33" s="3"/>
-    </row>
-    <row r="34" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ33" s="3"/>
+      <c r="BK33" s="3"/>
+      <c r="BL33" s="3"/>
+      <c r="BM33" s="3"/>
+    </row>
+    <row r="34" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>3</v>
       </c>
@@ -3902,28 +4146,28 @@
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
-      <c r="Q34" s="3">
-        <v>69.016170000000002</v>
-      </c>
-      <c r="R34" s="3">
-        <v>69.016170000000002</v>
-      </c>
-      <c r="S34" s="3">
-        <v>69.016170000000002</v>
-      </c>
-      <c r="T34" s="3">
-        <v>69.016170000000002</v>
-      </c>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
       <c r="U34" s="3">
         <v>69.016170000000002</v>
       </c>
       <c r="V34" s="3">
         <v>69.016170000000002</v>
       </c>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
+      <c r="W34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="X34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>69.016170000000002</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>69.016170000000002</v>
+      </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -3959,8 +4203,12 @@
       <c r="BG34" s="3"/>
       <c r="BH34" s="3"/>
       <c r="BI34" s="3"/>
-    </row>
-    <row r="35" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ34" s="3"/>
+      <c r="BK34" s="3"/>
+      <c r="BL34" s="3"/>
+      <c r="BM34" s="3"/>
+    </row>
+    <row r="35" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -4020,8 +4268,12 @@
       <c r="BG35" s="3"/>
       <c r="BH35" s="3"/>
       <c r="BI35" s="3"/>
-    </row>
-    <row r="36" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ35" s="3"/>
+      <c r="BK35" s="3"/>
+      <c r="BL35" s="3"/>
+      <c r="BM35" s="3"/>
+    </row>
+    <row r="36" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>59</v>
       </c>
@@ -4030,67 +4282,70 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="10">
-        <f>+G6/C6-1</f>
+        <f t="shared" ref="G36:K37" si="15">+G6/C6-1</f>
         <v>5.6417489421720646E-3</v>
       </c>
       <c r="H36" s="10">
-        <f>+H6/D6-1</f>
+        <f t="shared" si="15"/>
         <v>5.0775740479548581E-2</v>
       </c>
       <c r="I36" s="10">
-        <f>+I6/E6-1</f>
+        <f t="shared" si="15"/>
         <v>4.6544428772919533E-2</v>
       </c>
       <c r="J36" s="10">
-        <f>+J6/F6-1</f>
+        <f t="shared" si="15"/>
         <v>8.0394922425952142E-2</v>
       </c>
       <c r="K36" s="10">
-        <f>+K6/G6-1</f>
+        <f t="shared" si="15"/>
         <v>6.5217391304347894E-2</v>
       </c>
       <c r="L36" s="10">
-        <f t="shared" ref="L36:N36" si="17">+L6/H6-1</f>
+        <f t="shared" ref="L36:M36" si="16">+L6/H6-1</f>
         <v>3.3557046979866278E-3</v>
       </c>
       <c r="M36" s="10">
+        <f t="shared" si="16"/>
+        <v>6.738544474393926E-4</v>
+      </c>
+      <c r="N36" s="10">
+        <f>+N6/J6-1</f>
+        <v>-4.5691906005221883E-2</v>
+      </c>
+      <c r="O36" s="10">
+        <f>+O6/K6-1</f>
+        <v>-7.4391046741277167E-2</v>
+      </c>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="10" t="e">
+        <f t="shared" ref="U36:Y36" si="17">+U6/T6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V36" s="10" t="e">
         <f t="shared" si="17"/>
-        <v>6.738544474393926E-4</v>
-      </c>
-      <c r="N36" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W36" s="10" t="e">
         <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X36" s="10">
+        <f t="shared" si="17"/>
+        <v>7.7507598784194442E-2</v>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="17"/>
+        <v>8.0394922425952142E-2</v>
+      </c>
+      <c r="Z36" s="10">
+        <f>+Z6/Y6-1</f>
         <v>-4.5691906005221883E-2</v>
       </c>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="10" t="e">
-        <f t="shared" ref="Q36:V36" si="18">+Q6/P6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R36" s="10" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S36" s="10" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T36" s="10">
-        <f t="shared" si="18"/>
-        <v>7.7507598784194442E-2</v>
-      </c>
-      <c r="U36" s="10">
-        <f t="shared" si="18"/>
-        <v>8.0394922425952142E-2</v>
-      </c>
-      <c r="V36" s="10">
-        <f>+V6/U6-1</f>
-        <v>-4.5691906005221883E-2</v>
-      </c>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
@@ -4126,8 +4381,12 @@
       <c r="BG36" s="3"/>
       <c r="BH36" s="3"/>
       <c r="BI36" s="3"/>
-    </row>
-    <row r="37" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ36" s="3"/>
+      <c r="BK36" s="3"/>
+      <c r="BL36" s="3"/>
+      <c r="BM36" s="3"/>
+    </row>
+    <row r="37" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>60</v>
       </c>
@@ -4136,67 +4395,70 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="10">
-        <f>+G7/C7-1</f>
+        <f t="shared" si="15"/>
         <v>2.044989775051187E-3</v>
       </c>
       <c r="H37" s="10">
-        <f>+H7/D7-1</f>
+        <f t="shared" si="15"/>
         <v>1.0224948875255713E-2</v>
       </c>
       <c r="I37" s="10">
-        <f>+I7/E7-1</f>
+        <f t="shared" si="15"/>
         <v>2.044989775051187E-3</v>
       </c>
       <c r="J37" s="10">
-        <f>+J7/F7-1</f>
+        <f t="shared" si="15"/>
         <v>2.249488752556239E-2</v>
       </c>
       <c r="K37" s="10">
-        <f>+K7/G7-1</f>
+        <f t="shared" si="15"/>
         <v>2.0408163265306145E-2</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" ref="L37:N37" si="19">+L7/H7-1</f>
+        <f t="shared" ref="L37:M37" si="18">+L7/H7-1</f>
         <v>-6.0728744939271273E-3</v>
       </c>
       <c r="M37" s="10">
+        <f t="shared" si="18"/>
+        <v>-1.0204081632653073E-2</v>
+      </c>
+      <c r="N37" s="10">
+        <f>+N7/J7-1</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="O37" s="10">
+        <f>+O7/K7-1</f>
+        <v>-6.0000000000000053E-2</v>
+      </c>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="10" t="e">
+        <f t="shared" ref="U37:Y37" si="19">+U7/T7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V37" s="10" t="e">
         <f t="shared" si="19"/>
-        <v>-1.0204081632653073E-2</v>
-      </c>
-      <c r="N37" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W37" s="10" t="e">
         <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X37" s="10">
+        <f t="shared" si="19"/>
+        <v>4.042553191489362E-2</v>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="19"/>
+        <v>2.249488752556239E-2</v>
+      </c>
+      <c r="Z37" s="10">
+        <f>+Z7/Y7-1</f>
         <v>-3.0000000000000027E-2</v>
       </c>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="10" t="e">
-        <f t="shared" ref="Q37:V37" si="20">+Q7/P7-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R37" s="10" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S37" s="10" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T37" s="10">
-        <f t="shared" si="20"/>
-        <v>4.042553191489362E-2</v>
-      </c>
-      <c r="U37" s="10">
-        <f t="shared" si="20"/>
-        <v>2.249488752556239E-2</v>
-      </c>
-      <c r="V37" s="10">
-        <f>+V7/U7-1</f>
-        <v>-3.0000000000000027E-2</v>
-      </c>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -4232,8 +4494,12 @@
       <c r="BG37" s="3"/>
       <c r="BH37" s="3"/>
       <c r="BI37" s="3"/>
-    </row>
-    <row r="38" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ37" s="3"/>
+      <c r="BK37" s="3"/>
+      <c r="BL37" s="3"/>
+      <c r="BM37" s="3"/>
+    </row>
+    <row r="38" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>45</v>
       </c>
@@ -4242,19 +4508,19 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="10">
-        <f t="shared" ref="G38:J47" si="21">+G10/C10-1</f>
+        <f t="shared" ref="G38:J47" si="20">+G10/C10-1</f>
         <v>4.1554959785522705E-2</v>
       </c>
       <c r="H38" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-1.9753086419753041E-2</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-1.2722646310432406E-3</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>6.4551422319474749E-2</v>
       </c>
       <c r="K38" s="10">
@@ -4262,47 +4528,50 @@
         <v>-1.4157014157014203E-2</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" ref="L38:N48" si="22">+L10/H10-1</f>
+        <f t="shared" ref="L38:M48" si="21">+L10/H10-1</f>
         <v>1.7632241813602123E-2</v>
       </c>
       <c r="M38" s="10">
+        <f t="shared" si="21"/>
+        <v>-2.6751592356687892E-2</v>
+      </c>
+      <c r="N38" s="10">
+        <f>+N10/J10-1</f>
+        <v>3.5971223021582732E-2</v>
+      </c>
+      <c r="O38" s="10">
+        <f>+O10/K10-1</f>
+        <v>1.6971279373368064E-2</v>
+      </c>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="10" t="e">
+        <f t="shared" ref="U38:Y48" si="22">+U10/T10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V38" s="10" t="e">
         <f t="shared" si="22"/>
-        <v>-2.6751592356687892E-2</v>
-      </c>
-      <c r="N38" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W38" s="10" t="e">
         <f t="shared" si="22"/>
-        <v>3.5971223021582732E-2</v>
-      </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="10" t="e">
-        <f t="shared" ref="Q38:V48" si="23">+Q10/P10-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R38" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S38" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T38" s="10">
-        <f t="shared" si="23"/>
+      <c r="X38" s="10">
+        <f t="shared" si="22"/>
         <v>0.13528591352859132</v>
       </c>
-      <c r="U38" s="10">
-        <f t="shared" si="23"/>
+      <c r="Y38" s="10">
+        <f t="shared" si="22"/>
         <v>2.2420147420147529E-2</v>
       </c>
-      <c r="V38" s="10">
-        <f>+V10/U10-1</f>
+      <c r="Z38" s="10">
+        <f>+Z10/Y10-1</f>
         <v>5.1066386302192068E-3</v>
       </c>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -4338,8 +4607,12 @@
       <c r="BG38" s="3"/>
       <c r="BH38" s="3"/>
       <c r="BI38" s="3"/>
-    </row>
-    <row r="39" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ38" s="3"/>
+      <c r="BK38" s="3"/>
+      <c r="BL38" s="3"/>
+      <c r="BM38" s="3"/>
+    </row>
+    <row r="39" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>46</v>
       </c>
@@ -4348,67 +4621,70 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="10">
+        <f t="shared" si="20"/>
+        <v>4.4776119402984982E-2</v>
+      </c>
+      <c r="H39" s="10">
+        <f t="shared" si="20"/>
+        <v>1.4925373134328401E-2</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="20"/>
+        <v>1.3698630136986356E-2</v>
+      </c>
+      <c r="J39" s="10">
+        <f t="shared" si="20"/>
+        <v>4.9382716049382713E-2</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" ref="K39:K47" si="23">+K11/G11-1</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="10">
         <f t="shared" si="21"/>
-        <v>4.4776119402984982E-2</v>
-      </c>
-      <c r="H39" s="10">
+        <v>-8.8235294117647078E-2</v>
+      </c>
+      <c r="M39" s="10">
         <f t="shared" si="21"/>
-        <v>1.4925373134328401E-2</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="21"/>
-        <v>1.3698630136986356E-2</v>
-      </c>
-      <c r="J39" s="10">
-        <f t="shared" si="21"/>
-        <v>4.9382716049382713E-2</v>
-      </c>
-      <c r="K39" s="10">
-        <f t="shared" ref="K39:K47" si="24">+K11/G11-1</f>
-        <v>0</v>
-      </c>
-      <c r="L39" s="10">
+        <v>-9.4594594594594628E-2</v>
+      </c>
+      <c r="N39" s="10">
+        <f>+N11/J11-1</f>
+        <v>-4.705882352941182E-2</v>
+      </c>
+      <c r="O39" s="10" t="e">
+        <f>+O11/K11-1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="10" t="e">
         <f t="shared" si="22"/>
-        <v>-8.8235294117647078E-2</v>
-      </c>
-      <c r="M39" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V39" s="10" t="e">
         <f t="shared" si="22"/>
-        <v>-9.4594594594594628E-2</v>
-      </c>
-      <c r="N39" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W39" s="10" t="e">
         <f t="shared" si="22"/>
-        <v>-4.705882352941182E-2</v>
-      </c>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="10" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R39" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S39" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T39" s="10">
-        <f t="shared" si="23"/>
+      <c r="X39" s="10">
+        <f t="shared" si="22"/>
         <v>0.20502092050209209</v>
       </c>
-      <c r="U39" s="10">
-        <f t="shared" si="23"/>
+      <c r="Y39" s="10">
+        <f t="shared" si="22"/>
         <v>3.125E-2</v>
       </c>
-      <c r="V39" s="10">
-        <f t="shared" ref="V39:V48" si="25">+V11/U11-1</f>
+      <c r="Z39" s="10">
+        <f t="shared" ref="Z39:Z48" si="24">+Z11/Y11-1</f>
         <v>-5.7239057239057201E-2</v>
       </c>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
@@ -4444,8 +4720,12 @@
       <c r="BG39" s="3"/>
       <c r="BH39" s="3"/>
       <c r="BI39" s="3"/>
-    </row>
-    <row r="40" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ39" s="3"/>
+      <c r="BK39" s="3"/>
+      <c r="BL39" s="3"/>
+      <c r="BM39" s="3"/>
+    </row>
+    <row r="40" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>47</v>
       </c>
@@ -4454,67 +4734,70 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="10">
+        <f t="shared" si="20"/>
+        <v>7.7419354838709653E-2</v>
+      </c>
+      <c r="H40" s="10">
+        <f t="shared" si="20"/>
+        <v>2.7027027027026973E-2</v>
+      </c>
+      <c r="I40" s="10">
+        <f t="shared" si="20"/>
+        <v>1.1834319526627279E-2</v>
+      </c>
+      <c r="J40" s="10">
+        <f t="shared" si="20"/>
+        <v>6.0773480662983381E-2</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="23"/>
+        <v>-2.39520958083832E-2</v>
+      </c>
+      <c r="L40" s="10">
         <f t="shared" si="21"/>
-        <v>7.7419354838709653E-2</v>
-      </c>
-      <c r="H40" s="10">
+        <v>-0.13157894736842102</v>
+      </c>
+      <c r="M40" s="10">
         <f t="shared" si="21"/>
-        <v>2.7027027027026973E-2</v>
-      </c>
-      <c r="I40" s="10">
-        <f t="shared" si="21"/>
-        <v>1.1834319526627279E-2</v>
-      </c>
-      <c r="J40" s="10">
-        <f t="shared" si="21"/>
-        <v>6.0773480662983381E-2</v>
-      </c>
-      <c r="K40" s="10">
+        <v>-7.6023391812865548E-2</v>
+      </c>
+      <c r="N40" s="10">
+        <f>+N12/J12-1</f>
+        <v>-5.2083333333333703E-3</v>
+      </c>
+      <c r="O40" s="10">
+        <f>+O12/K12-1</f>
+        <v>-0.23312883435582821</v>
+      </c>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V40" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W40" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X40" s="10">
+        <f t="shared" si="22"/>
+        <v>0.19816513761467891</v>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="22"/>
+        <v>4.4410413476263511E-2</v>
+      </c>
+      <c r="Z40" s="10">
         <f t="shared" si="24"/>
-        <v>-2.39520958083832E-2</v>
-      </c>
-      <c r="L40" s="10">
-        <f t="shared" si="22"/>
-        <v>-0.13157894736842102</v>
-      </c>
-      <c r="M40" s="10">
-        <f t="shared" si="22"/>
-        <v>-7.6023391812865548E-2</v>
-      </c>
-      <c r="N40" s="10">
-        <f t="shared" si="22"/>
-        <v>-5.2083333333333703E-3</v>
-      </c>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R40" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S40" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T40" s="10">
-        <f t="shared" si="23"/>
-        <v>0.19816513761467891</v>
-      </c>
-      <c r="U40" s="10">
-        <f t="shared" si="23"/>
-        <v>4.4410413476263511E-2</v>
-      </c>
-      <c r="V40" s="10">
-        <f t="shared" si="25"/>
         <v>-5.5718475073313734E-2</v>
       </c>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
@@ -4550,8 +4833,12 @@
       <c r="BG40" s="3"/>
       <c r="BH40" s="3"/>
       <c r="BI40" s="3"/>
-    </row>
-    <row r="41" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ40" s="3"/>
+      <c r="BK40" s="3"/>
+      <c r="BL40" s="3"/>
+      <c r="BM40" s="3"/>
+    </row>
+    <row r="41" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>48</v>
       </c>
@@ -4560,67 +4847,70 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="10">
+        <f t="shared" si="20"/>
+        <v>4.1050903119868698E-2</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" si="20"/>
+        <v>-2.5806451612903181E-2</v>
+      </c>
+      <c r="I41" s="10">
+        <f t="shared" si="20"/>
+        <v>1.3782542113323082E-2</v>
+      </c>
+      <c r="J41" s="10">
+        <f t="shared" si="20"/>
+        <v>6.6176470588235281E-2</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="23"/>
+        <v>-4.7318611987381409E-3</v>
+      </c>
+      <c r="L41" s="10">
         <f t="shared" si="21"/>
-        <v>4.1050903119868698E-2</v>
-      </c>
-      <c r="H41" s="10">
+        <v>2.3178807947019875E-2</v>
+      </c>
+      <c r="M41" s="10">
         <f t="shared" si="21"/>
-        <v>-2.5806451612903181E-2</v>
-      </c>
-      <c r="I41" s="10">
-        <f t="shared" si="21"/>
-        <v>1.3782542113323082E-2</v>
-      </c>
-      <c r="J41" s="10">
-        <f t="shared" si="21"/>
-        <v>6.6176470588235281E-2</v>
-      </c>
-      <c r="K41" s="10">
+        <v>-3.1722054380664666E-2</v>
+      </c>
+      <c r="N41" s="10">
+        <f>+N13/J13-1</f>
+        <v>0.21125793103448309</v>
+      </c>
+      <c r="O41" s="10">
+        <f>+O13/K13-1</f>
+        <v>-9.9841521394611776E-2</v>
+      </c>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V41" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W41" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X41" s="10">
+        <f t="shared" si="22"/>
+        <v>0.11246200607902734</v>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="22"/>
+        <v>2.4590163934426146E-2</v>
+      </c>
+      <c r="Z41" s="10">
         <f t="shared" si="24"/>
-        <v>-4.7318611987381409E-3</v>
-      </c>
-      <c r="L41" s="10">
-        <f t="shared" si="22"/>
-        <v>2.3178807947019875E-2</v>
-      </c>
-      <c r="M41" s="10">
-        <f t="shared" si="22"/>
-        <v>-3.1722054380664666E-2</v>
-      </c>
-      <c r="N41" s="10">
-        <f t="shared" si="22"/>
-        <v>0.21125793103448309</v>
-      </c>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R41" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S41" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T41" s="10">
-        <f t="shared" si="23"/>
-        <v>0.11246200607902734</v>
-      </c>
-      <c r="U41" s="10">
-        <f t="shared" si="23"/>
-        <v>2.4590163934426146E-2</v>
-      </c>
-      <c r="V41" s="10">
-        <f t="shared" si="25"/>
         <v>5.4537904761904787E-2</v>
       </c>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
@@ -4656,8 +4946,12 @@
       <c r="BG41" s="3"/>
       <c r="BH41" s="3"/>
       <c r="BI41" s="3"/>
-    </row>
-    <row r="42" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ41" s="3"/>
+      <c r="BK41" s="3"/>
+      <c r="BL41" s="3"/>
+      <c r="BM41" s="3"/>
+    </row>
+    <row r="42" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>49</v>
       </c>
@@ -4666,67 +4960,70 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="10">
+        <f t="shared" si="20"/>
+        <v>0.11794871794871797</v>
+      </c>
+      <c r="H42" s="10">
+        <f t="shared" si="20"/>
+        <v>5.9322033898305149E-2</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="20"/>
+        <v>9.4594594594594517E-2</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="23"/>
+        <v>-2.752293577981646E-2</v>
+      </c>
+      <c r="L42" s="10">
         <f t="shared" si="21"/>
-        <v>0.11794871794871797</v>
-      </c>
-      <c r="H42" s="10">
+        <v>-5.600000000000005E-2</v>
+      </c>
+      <c r="M42" s="10">
         <f t="shared" si="21"/>
-        <v>5.9322033898305149E-2</v>
-      </c>
-      <c r="I42" s="10">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="10">
-        <f t="shared" si="21"/>
-        <v>9.4594594594594517E-2</v>
-      </c>
-      <c r="K42" s="10">
+        <v>-2.1929824561403466E-2</v>
+      </c>
+      <c r="N42" s="10">
+        <f>+N14/J14-1</f>
+        <v>-7.0987654320986415E-3</v>
+      </c>
+      <c r="O42" s="10">
+        <f>+O14/K14-1</f>
+        <v>-0.1132075471698113</v>
+      </c>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V42" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W42" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X42" s="10">
+        <f t="shared" si="22"/>
+        <v>0.21039290240811148</v>
+      </c>
+      <c r="Y42" s="10">
+        <f t="shared" si="22"/>
+        <v>6.8062827225130906E-2</v>
+      </c>
+      <c r="Z42" s="10">
         <f t="shared" si="24"/>
-        <v>-2.752293577981646E-2</v>
-      </c>
-      <c r="L42" s="10">
-        <f t="shared" si="22"/>
-        <v>-5.600000000000005E-2</v>
-      </c>
-      <c r="M42" s="10">
-        <f t="shared" si="22"/>
-        <v>-2.1929824561403466E-2</v>
-      </c>
-      <c r="N42" s="10">
-        <f t="shared" si="22"/>
-        <v>-7.0987654320986415E-3</v>
-      </c>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R42" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S42" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T42" s="10">
-        <f t="shared" si="23"/>
-        <v>0.21039290240811148</v>
-      </c>
-      <c r="U42" s="10">
-        <f t="shared" si="23"/>
-        <v>6.8062827225130906E-2</v>
-      </c>
-      <c r="V42" s="10">
-        <f t="shared" si="25"/>
         <v>-2.6764705882352913E-2</v>
       </c>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
@@ -4762,8 +5059,12 @@
       <c r="BG42" s="3"/>
       <c r="BH42" s="3"/>
       <c r="BI42" s="3"/>
-    </row>
-    <row r="43" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ42" s="3"/>
+      <c r="BK42" s="3"/>
+      <c r="BL42" s="3"/>
+      <c r="BM42" s="3"/>
+    </row>
+    <row r="43" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>50</v>
       </c>
@@ -4772,67 +5073,70 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="10">
+        <f t="shared" si="20"/>
+        <v>-1.4184397163120588E-2</v>
+      </c>
+      <c r="H43" s="10">
+        <f t="shared" si="20"/>
+        <v>-6.944444444444442E-2</v>
+      </c>
+      <c r="I43" s="10">
+        <f t="shared" si="20"/>
+        <v>-8.333333333333337E-2</v>
+      </c>
+      <c r="J43" s="10">
+        <f t="shared" si="20"/>
+        <v>-5.8479532163743242E-3</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="23"/>
+        <v>-6.4748201438848962E-2</v>
+      </c>
+      <c r="L43" s="10">
         <f t="shared" si="21"/>
-        <v>-1.4184397163120588E-2</v>
-      </c>
-      <c r="H43" s="10">
+        <v>-7.4626865671641784E-2</v>
+      </c>
+      <c r="M43" s="10">
         <f t="shared" si="21"/>
-        <v>-6.944444444444442E-2</v>
-      </c>
-      <c r="I43" s="10">
-        <f t="shared" si="21"/>
-        <v>-8.333333333333337E-2</v>
-      </c>
-      <c r="J43" s="10">
-        <f t="shared" si="21"/>
-        <v>-5.8479532163743242E-3</v>
-      </c>
-      <c r="K43" s="10">
+        <v>-8.181818181818179E-2</v>
+      </c>
+      <c r="N43" s="10">
+        <f>+N15/J15-1</f>
+        <v>-9.4264705882352806E-2</v>
+      </c>
+      <c r="O43" s="10">
+        <f>+O15/K15-1</f>
+        <v>-5.3846153846153877E-2</v>
+      </c>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V43" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W43" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X43" s="10">
+        <f t="shared" si="22"/>
+        <v>0.23340471092077086</v>
+      </c>
+      <c r="Y43" s="10">
+        <f t="shared" si="22"/>
+        <v>-3.993055555555558E-2</v>
+      </c>
+      <c r="Z43" s="10">
         <f t="shared" si="24"/>
-        <v>-6.4748201438848962E-2</v>
-      </c>
-      <c r="L43" s="10">
-        <f t="shared" si="22"/>
-        <v>-7.4626865671641784E-2</v>
-      </c>
-      <c r="M43" s="10">
-        <f t="shared" si="22"/>
-        <v>-8.181818181818179E-2</v>
-      </c>
-      <c r="N43" s="10">
-        <f t="shared" si="22"/>
-        <v>-9.4264705882352806E-2</v>
-      </c>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R43" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S43" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T43" s="10">
-        <f t="shared" si="23"/>
-        <v>0.23340471092077086</v>
-      </c>
-      <c r="U43" s="10">
-        <f t="shared" si="23"/>
-        <v>-3.993055555555558E-2</v>
-      </c>
-      <c r="V43" s="10">
-        <f t="shared" si="25"/>
         <v>-7.9611211573236806E-2</v>
       </c>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
@@ -4868,8 +5172,12 @@
       <c r="BG43" s="3"/>
       <c r="BH43" s="3"/>
       <c r="BI43" s="3"/>
-    </row>
-    <row r="44" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ43" s="3"/>
+      <c r="BK43" s="3"/>
+      <c r="BL43" s="3"/>
+      <c r="BM43" s="3"/>
+    </row>
+    <row r="44" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>51</v>
       </c>
@@ -4878,67 +5186,70 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="10">
+        <f t="shared" si="20"/>
+        <v>1.4432989690721598E-2</v>
+      </c>
+      <c r="H44" s="10">
+        <f t="shared" si="20"/>
+        <v>-2.931034482758621E-2</v>
+      </c>
+      <c r="I44" s="10">
+        <f t="shared" si="20"/>
+        <v>-4.2226487523992273E-2</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="20"/>
+        <v>1.6751479289941029E-2</v>
+      </c>
+      <c r="K44" s="10">
+        <f t="shared" si="23"/>
+        <v>-3.8617886178861749E-2</v>
+      </c>
+      <c r="L44" s="10">
         <f t="shared" si="21"/>
-        <v>1.4432989690721598E-2</v>
-      </c>
-      <c r="H44" s="10">
+        <v>-3.730017761989346E-2</v>
+      </c>
+      <c r="M44" s="10">
         <f t="shared" si="21"/>
-        <v>-2.931034482758621E-2</v>
-      </c>
-      <c r="I44" s="10">
-        <f t="shared" si="21"/>
-        <v>-4.2226487523992273E-2</v>
-      </c>
-      <c r="J44" s="10">
-        <f t="shared" si="21"/>
-        <v>1.6751479289941029E-2</v>
-      </c>
-      <c r="K44" s="10">
+        <v>-3.2064128256513058E-2</v>
+      </c>
+      <c r="N44" s="10">
+        <f>+N16/J16-1</f>
+        <v>-2.6278727354202558E-2</v>
+      </c>
+      <c r="O44" s="10">
+        <f>+O16/K16-1</f>
+        <v>7.8224101479915431E-2</v>
+      </c>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V44" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W44" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X44" s="10">
+        <f t="shared" si="22"/>
+        <v>0.12202380952380953</v>
+      </c>
+      <c r="Y44" s="10">
+        <f t="shared" si="22"/>
+        <v>-9.1405835543766356E-3</v>
+      </c>
+      <c r="Z44" s="10">
         <f t="shared" si="24"/>
-        <v>-3.8617886178861749E-2</v>
-      </c>
-      <c r="L44" s="10">
-        <f t="shared" si="22"/>
-        <v>-3.730017761989346E-2</v>
-      </c>
-      <c r="M44" s="10">
-        <f t="shared" si="22"/>
-        <v>-3.2064128256513058E-2</v>
-      </c>
-      <c r="N44" s="10">
-        <f t="shared" si="22"/>
-        <v>-2.6278727354202558E-2</v>
-      </c>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R44" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S44" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T44" s="10">
-        <f t="shared" si="23"/>
-        <v>0.12202380952380953</v>
-      </c>
-      <c r="U44" s="10">
-        <f t="shared" si="23"/>
-        <v>-9.1405835543766356E-3</v>
-      </c>
-      <c r="V44" s="10">
-        <f t="shared" si="25"/>
         <v>-3.3043861574676314E-2</v>
       </c>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
@@ -4974,8 +5285,12 @@
       <c r="BG44" s="3"/>
       <c r="BH44" s="3"/>
       <c r="BI44" s="3"/>
-    </row>
-    <row r="45" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ44" s="3"/>
+      <c r="BK44" s="3"/>
+      <c r="BL44" s="3"/>
+      <c r="BM44" s="3"/>
+    </row>
+    <row r="45" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>52</v>
       </c>
@@ -4984,67 +5299,70 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="10">
+        <f t="shared" si="20"/>
+        <v>7.4468085106383031E-2</v>
+      </c>
+      <c r="H45" s="10">
+        <f t="shared" si="20"/>
+        <v>5.3571428571428603E-2</v>
+      </c>
+      <c r="I45" s="10">
+        <f t="shared" si="20"/>
+        <v>3.0716723549488067E-2</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="20"/>
+        <v>0.15387606837606871</v>
+      </c>
+      <c r="K45" s="10">
+        <f t="shared" si="23"/>
+        <v>-2.3102310231023049E-2</v>
+      </c>
+      <c r="L45" s="10">
         <f t="shared" si="21"/>
-        <v>7.4468085106383031E-2</v>
-      </c>
-      <c r="H45" s="10">
+        <v>4.237288135593209E-3</v>
+      </c>
+      <c r="M45" s="10">
         <f t="shared" si="21"/>
-        <v>5.3571428571428603E-2</v>
-      </c>
-      <c r="I45" s="10">
-        <f t="shared" si="21"/>
-        <v>3.0716723549488067E-2</v>
-      </c>
-      <c r="J45" s="10">
-        <f t="shared" si="21"/>
-        <v>0.15387606837606871</v>
-      </c>
-      <c r="K45" s="10">
+        <v>-6.9536423841059625E-2</v>
+      </c>
+      <c r="N45" s="10">
+        <f>+N17/J17-1</f>
+        <v>9.0268030088108908E-2</v>
+      </c>
+      <c r="O45" s="10">
+        <f>+O17/K17-1</f>
+        <v>0.24662162162162171</v>
+      </c>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V45" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W45" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X45" s="10">
+        <f t="shared" si="22"/>
+        <v>0.15418994413407816</v>
+      </c>
+      <c r="Y45" s="10">
+        <f t="shared" si="22"/>
+        <v>7.5515004840271072E-2</v>
+      </c>
+      <c r="Z45" s="10">
         <f t="shared" si="24"/>
-        <v>-2.3102310231023049E-2</v>
-      </c>
-      <c r="L45" s="10">
-        <f t="shared" si="22"/>
-        <v>4.237288135593209E-3</v>
-      </c>
-      <c r="M45" s="10">
-        <f t="shared" si="22"/>
-        <v>-6.9536423841059625E-2</v>
-      </c>
-      <c r="N45" s="10">
-        <f t="shared" si="22"/>
-        <v>9.0268030088108908E-2</v>
-      </c>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R45" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S45" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T45" s="10">
-        <f t="shared" si="23"/>
-        <v>0.15418994413407816</v>
-      </c>
-      <c r="U45" s="10">
-        <f t="shared" si="23"/>
-        <v>7.5515004840271072E-2</v>
-      </c>
-      <c r="V45" s="10">
-        <f t="shared" si="25"/>
         <v>-2.3645215556696852E-3</v>
       </c>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
@@ -5080,8 +5398,12 @@
       <c r="BG45" s="3"/>
       <c r="BH45" s="3"/>
       <c r="BI45" s="3"/>
-    </row>
-    <row r="46" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ45" s="3"/>
+      <c r="BK45" s="3"/>
+      <c r="BL45" s="3"/>
+      <c r="BM45" s="3"/>
+    </row>
+    <row r="46" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>53</v>
       </c>
@@ -5090,67 +5412,70 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="10">
+        <f t="shared" si="20"/>
+        <v>9.550561797752799E-2</v>
+      </c>
+      <c r="H46" s="10">
+        <f t="shared" si="20"/>
+        <v>-3.5714285714285698E-2</v>
+      </c>
+      <c r="I46" s="10">
+        <f t="shared" si="20"/>
+        <v>6.4171122994652441E-2</v>
+      </c>
+      <c r="J46" s="10">
+        <f t="shared" si="20"/>
+        <v>0.10950632911392399</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="23"/>
+        <v>4.6153846153846212E-2</v>
+      </c>
+      <c r="L46" s="10">
         <f t="shared" si="21"/>
-        <v>9.550561797752799E-2</v>
-      </c>
-      <c r="H46" s="10">
+        <v>5.2910052910053018E-2</v>
+      </c>
+      <c r="M46" s="10">
         <f t="shared" si="21"/>
-        <v>-3.5714285714285698E-2</v>
-      </c>
-      <c r="I46" s="10">
-        <f t="shared" si="21"/>
-        <v>6.4171122994652441E-2</v>
-      </c>
-      <c r="J46" s="10">
-        <f t="shared" si="21"/>
-        <v>0.10950632911392399</v>
-      </c>
-      <c r="K46" s="10">
+        <v>1.0050251256281451E-2</v>
+      </c>
+      <c r="N46" s="10">
+        <f>+N18/J18-1</f>
+        <v>9.0126372393545928E-2</v>
+      </c>
+      <c r="O46" s="10" t="e">
+        <f>+O18/K18-1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V46" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W46" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X46" s="10">
+        <f t="shared" si="22"/>
+        <v>0.2314814814814814</v>
+      </c>
+      <c r="Y46" s="10">
+        <f t="shared" si="22"/>
+        <v>6.0091478696741918E-2</v>
+      </c>
+      <c r="Z46" s="10">
         <f t="shared" si="24"/>
-        <v>4.6153846153846212E-2</v>
-      </c>
-      <c r="L46" s="10">
-        <f t="shared" si="22"/>
-        <v>5.2910052910053018E-2</v>
-      </c>
-      <c r="M46" s="10">
-        <f t="shared" si="22"/>
-        <v>1.0050251256281451E-2</v>
-      </c>
-      <c r="N46" s="10">
-        <f t="shared" si="22"/>
-        <v>9.0126372393545928E-2</v>
-      </c>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R46" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S46" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T46" s="10">
-        <f t="shared" si="23"/>
-        <v>0.2314814814814814</v>
-      </c>
-      <c r="U46" s="10">
-        <f t="shared" si="23"/>
-        <v>6.0091478696741918E-2</v>
-      </c>
-      <c r="V46" s="10">
-        <f t="shared" si="25"/>
         <v>5.2838632879131708E-2</v>
       </c>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
@@ -5186,8 +5511,12 @@
       <c r="BG46" s="3"/>
       <c r="BH46" s="3"/>
       <c r="BI46" s="3"/>
-    </row>
-    <row r="47" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ46" s="3"/>
+      <c r="BK46" s="3"/>
+      <c r="BL46" s="3"/>
+      <c r="BM46" s="3"/>
+    </row>
+    <row r="47" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>54</v>
       </c>
@@ -5196,67 +5525,70 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0.11538461538461542</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>7.1206896551724075E-2</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="24"/>
-        <v>0.13043478260869557</v>
-      </c>
-      <c r="L47" s="10">
-        <f t="shared" si="22"/>
-        <v>-7.6923076923076872E-2</v>
-      </c>
-      <c r="M47" s="10">
-        <f t="shared" si="22"/>
-        <v>-0.13793103448275867</v>
-      </c>
-      <c r="N47" s="10">
-        <f t="shared" si="22"/>
-        <v>-8.1152422340254327E-2</v>
-      </c>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R47" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S47" s="10" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T47" s="10">
         <f t="shared" si="23"/>
         <v>0.13043478260869557</v>
       </c>
-      <c r="U47" s="10">
-        <f t="shared" si="23"/>
+      <c r="L47" s="10">
+        <f t="shared" si="21"/>
+        <v>-7.6923076923076872E-2</v>
+      </c>
+      <c r="M47" s="10">
+        <f t="shared" si="21"/>
+        <v>-0.13793103448275867</v>
+      </c>
+      <c r="N47" s="10">
+        <f>+N19/J19-1</f>
+        <v>-8.1152422340254327E-2</v>
+      </c>
+      <c r="O47" s="10">
+        <f>+O19/K19-1</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V47" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W47" s="10" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X47" s="10">
+        <f t="shared" si="22"/>
+        <v>0.13043478260869557</v>
+      </c>
+      <c r="Y47" s="10">
+        <f t="shared" si="22"/>
         <v>4.8701923076923004E-2</v>
       </c>
-      <c r="V47" s="10">
-        <f t="shared" si="25"/>
+      <c r="Z47" s="10">
+        <f t="shared" si="24"/>
         <v>-5.0621189199101413E-2</v>
       </c>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
@@ -5292,8 +5624,12 @@
       <c r="BG47" s="3"/>
       <c r="BH47" s="3"/>
       <c r="BI47" s="3"/>
-    </row>
-    <row r="48" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ47" s="3"/>
+      <c r="BK47" s="3"/>
+      <c r="BL47" s="3"/>
+      <c r="BM47" s="3"/>
+    </row>
+    <row r="48" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
         <v>55</v>
       </c>
@@ -5302,11 +5638,11 @@
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="12">
-        <f t="shared" ref="G48:H48" si="26">+G20/C20-1</f>
+        <f t="shared" ref="G48:H48" si="25">+G20/C20-1</f>
         <v>4.7520661157024691E-2</v>
       </c>
       <c r="H48" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-1.0721247563352798E-2</v>
       </c>
       <c r="I48" s="12">
@@ -5314,56 +5650,59 @@
         <v>1.9474196689386325E-3</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" ref="J48:K48" si="27">+J20/F20-1</f>
+        <f t="shared" ref="J48:K48" si="26">+J20/F20-1</f>
         <v>6.2074829931972886E-2</v>
       </c>
       <c r="K48" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>-1.4792899408283988E-2</v>
       </c>
       <c r="L48" s="12">
+        <f t="shared" si="21"/>
+        <v>-1.2807881773398977E-2</v>
+      </c>
+      <c r="M48" s="12">
+        <f t="shared" si="21"/>
+        <v>-3.8872691933916403E-2</v>
+      </c>
+      <c r="N48" s="12">
+        <f>+N20/J20-1</f>
+        <v>2.4690152121697118E-2</v>
+      </c>
+      <c r="O48" s="12">
+        <f>+O20/K20-1</f>
+        <v>-9.4094094094094083E-2</v>
+      </c>
+      <c r="P48" s="12"/>
+      <c r="Q48" s="12"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="11"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>-1.2807881773398977E-2</v>
-      </c>
-      <c r="M48" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V48" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>-3.8872691933916403E-2</v>
-      </c>
-      <c r="N48" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W48" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>2.4690152121697118E-2</v>
-      </c>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="12" t="e">
-        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R48" s="12" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S48" s="12" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T48" s="12">
-        <f t="shared" si="23"/>
+      <c r="X48" s="12">
+        <f t="shared" si="22"/>
         <v>0.14954806902218576</v>
       </c>
-      <c r="U48" s="12">
-        <f t="shared" si="23"/>
+      <c r="Y48" s="12">
+        <f t="shared" si="22"/>
         <v>2.6209197045508725E-2</v>
       </c>
-      <c r="V48" s="12">
-        <f t="shared" si="25"/>
+      <c r="Z48" s="12">
+        <f t="shared" si="24"/>
         <v>-8.6282795449269534E-3</v>
       </c>
-      <c r="W48" s="11"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
+      <c r="AA48" s="11"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -5398,33 +5737,37 @@
       <c r="BG48" s="3"/>
       <c r="BH48" s="3"/>
       <c r="BI48" s="3"/>
-    </row>
-    <row r="49" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ48" s="3"/>
+      <c r="BK48" s="3"/>
+      <c r="BL48" s="3"/>
+      <c r="BM48" s="3"/>
+    </row>
+    <row r="49" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" ref="C49:H49" si="28">+C22/C20</f>
+        <f t="shared" ref="C49:H49" si="27">+C22/C20</f>
         <v>0.61363636363636365</v>
       </c>
       <c r="D49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.62378167641325533</v>
       </c>
       <c r="E49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.60662122687439146</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.61479591836734693</v>
       </c>
       <c r="G49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.61439842209072981</v>
       </c>
       <c r="H49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0.62857142857142856</v>
       </c>
       <c r="I49" s="10">
@@ -5440,50 +5783,53 @@
         <v>0.61361361361361366</v>
       </c>
       <c r="L49" s="10">
-        <f t="shared" ref="L49:N49" si="29">+L22/L20</f>
+        <f t="shared" ref="L49:N49" si="28">+L22/L20</f>
         <v>0.62874251497005984</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.61172901921132461</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.60818634858474263</v>
       </c>
-      <c r="O49" s="3"/>
-      <c r="P49" s="10" t="e">
-        <f t="shared" ref="P49:S49" si="30">+P22/P20</f>
+      <c r="O49" s="10">
+        <f t="shared" ref="O49" si="29">+O22/O20</f>
+        <v>0.62430939226519333</v>
+      </c>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="10" t="e">
+        <f t="shared" ref="T49:W49" si="30">+T22/T20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q49" s="10" t="e">
+      <c r="U49" s="10" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R49" s="10" t="e">
+      <c r="V49" s="10" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S49" s="10">
+      <c r="W49" s="10">
         <f t="shared" si="30"/>
         <v>0.61791290057518489</v>
       </c>
-      <c r="T49" s="10">
-        <f>+T22/T20</f>
+      <c r="X49" s="10">
+        <f>+X22/X20</f>
         <v>0.6147248034310222</v>
       </c>
-      <c r="U49" s="10">
-        <f>+U22/U20</f>
+      <c r="Y49" s="10">
+        <f>+Y22/Y20</f>
         <v>0.61736707685163683</v>
       </c>
-      <c r="V49" s="10">
-        <f>+V22/V20</f>
+      <c r="Z49" s="10">
+        <f>+Z22/Z20</f>
         <v>0.61510061974248198</v>
       </c>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
@@ -5519,8 +5865,12 @@
       <c r="BG49" s="3"/>
       <c r="BH49" s="3"/>
       <c r="BI49" s="3"/>
-    </row>
-    <row r="50" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ49" s="3"/>
+      <c r="BK49" s="3"/>
+      <c r="BL49" s="3"/>
+      <c r="BM49" s="3"/>
+    </row>
+    <row r="50" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>57</v>
       </c>
@@ -5572,39 +5922,42 @@
         <f t="shared" si="32"/>
         <v>0.11935338691303098</v>
       </c>
-      <c r="O50" s="3"/>
-      <c r="P50" s="10" t="e">
-        <f t="shared" ref="P50:S50" si="33">+P25/P20</f>
+      <c r="O50" s="10">
+        <f t="shared" ref="O50" si="33">+O25/O20</f>
+        <v>3.9779005524861875E-2</v>
+      </c>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="10" t="e">
+        <f t="shared" ref="T50:W50" si="34">+T25/T20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q50" s="10" t="e">
-        <f t="shared" si="33"/>
+      <c r="U50" s="10" t="e">
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R50" s="10" t="e">
-        <f t="shared" si="33"/>
+      <c r="V50" s="10" t="e">
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S50" s="10">
-        <f t="shared" si="33"/>
+      <c r="W50" s="10">
+        <f t="shared" si="34"/>
         <v>9.1755683374417973E-2</v>
       </c>
-      <c r="T50" s="10">
-        <f>+T25/T20</f>
+      <c r="X50" s="10">
+        <f>+X25/X20</f>
         <v>9.7450559923755065E-2</v>
       </c>
-      <c r="U50" s="10">
-        <f>+U25/U20</f>
+      <c r="Y50" s="10">
+        <f>+Y25/Y20</f>
         <v>8.3584861852797773E-2</v>
       </c>
-      <c r="V50" s="10">
-        <f>+V25/V20</f>
+      <c r="Z50" s="10">
+        <f>+Z25/Z20</f>
         <v>9.1514713204575854E-2</v>
       </c>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
@@ -5640,33 +5993,37 @@
       <c r="BG50" s="3"/>
       <c r="BH50" s="3"/>
       <c r="BI50" s="3"/>
-    </row>
-    <row r="51" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ50" s="3"/>
+      <c r="BK50" s="3"/>
+      <c r="BL50" s="3"/>
+      <c r="BM50" s="3"/>
+    </row>
+    <row r="51" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" ref="C51:H51" si="34">+C28/C27</f>
+        <f t="shared" ref="C51:H51" si="35">+C28/C27</f>
         <v>0.27777777777777779</v>
       </c>
       <c r="D51" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.28409090909090912</v>
       </c>
       <c r="F51" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.16346153846153846</v>
       </c>
       <c r="G51" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.2807017543859649</v>
       </c>
       <c r="H51" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="I51" s="10">
@@ -5682,50 +6039,53 @@
         <v>0.28301886792452829</v>
       </c>
       <c r="L51" s="10">
-        <f t="shared" ref="L51:N51" si="35">+L28/L27</f>
+        <f t="shared" ref="L51:N51" si="36">+L28/L27</f>
         <v>0.27536231884057971</v>
       </c>
       <c r="M51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.27710843373493976</v>
       </c>
       <c r="N51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.20426593827760817</v>
       </c>
-      <c r="O51" s="3"/>
-      <c r="P51" s="10" t="e">
-        <f t="shared" ref="P51:S51" si="36">+P28/P27</f>
+      <c r="O51" s="10">
+        <f t="shared" ref="O51" si="37">+O28/O27</f>
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="10" t="e">
+        <f t="shared" ref="T51:W51" si="38">+T28/T27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q51" s="10" t="e">
-        <f t="shared" si="36"/>
+      <c r="U51" s="10" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R51" s="10" t="e">
-        <f t="shared" si="36"/>
+      <c r="V51" s="10" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S51" s="10">
-        <f t="shared" si="36"/>
+      <c r="W51" s="10">
+        <f t="shared" si="38"/>
         <v>0.22105263157894736</v>
       </c>
-      <c r="T51" s="10">
-        <f>+T28/T27</f>
+      <c r="X51" s="10">
+        <f>+X28/X27</f>
         <v>0.2443820224719101</v>
       </c>
-      <c r="U51" s="10">
-        <f>+U28/U27</f>
+      <c r="Y51" s="10">
+        <f>+Y28/Y27</f>
         <v>0.25913621262458469</v>
       </c>
-      <c r="V51" s="10">
-        <f>+V28/V27</f>
+      <c r="Z51" s="10">
+        <f>+Z28/Z27</f>
         <v>0.24812673262733018</v>
       </c>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
       <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
@@ -5761,8 +6121,12 @@
       <c r="BG51" s="3"/>
       <c r="BH51" s="3"/>
       <c r="BI51" s="3"/>
-    </row>
-    <row r="52" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ51" s="3"/>
+      <c r="BK51" s="3"/>
+      <c r="BL51" s="3"/>
+      <c r="BM51" s="3"/>
+    </row>
+    <row r="52" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -5822,8 +6186,12 @@
       <c r="BG52" s="3"/>
       <c r="BH52" s="3"/>
       <c r="BI52" s="3"/>
-    </row>
-    <row r="53" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ52" s="3"/>
+      <c r="BK52" s="3"/>
+      <c r="BL52" s="3"/>
+      <c r="BM52" s="3"/>
+    </row>
+    <row r="53" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -5883,8 +6251,12 @@
       <c r="BG53" s="3"/>
       <c r="BH53" s="3"/>
       <c r="BI53" s="3"/>
-    </row>
-    <row r="54" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ53" s="3"/>
+      <c r="BK53" s="3"/>
+      <c r="BL53" s="3"/>
+      <c r="BM53" s="3"/>
+    </row>
+    <row r="54" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -5944,8 +6316,12 @@
       <c r="BG54" s="3"/>
       <c r="BH54" s="3"/>
       <c r="BI54" s="3"/>
-    </row>
-    <row r="55" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ54" s="3"/>
+      <c r="BK54" s="3"/>
+      <c r="BL54" s="3"/>
+      <c r="BM54" s="3"/>
+    </row>
+    <row r="55" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -6005,8 +6381,12 @@
       <c r="BG55" s="3"/>
       <c r="BH55" s="3"/>
       <c r="BI55" s="3"/>
-    </row>
-    <row r="56" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ55" s="3"/>
+      <c r="BK55" s="3"/>
+      <c r="BL55" s="3"/>
+      <c r="BM55" s="3"/>
+    </row>
+    <row r="56" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -6066,8 +6446,12 @@
       <c r="BG56" s="3"/>
       <c r="BH56" s="3"/>
       <c r="BI56" s="3"/>
-    </row>
-    <row r="57" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ56" s="3"/>
+      <c r="BK56" s="3"/>
+      <c r="BL56" s="3"/>
+      <c r="BM56" s="3"/>
+    </row>
+    <row r="57" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -6127,8 +6511,12 @@
       <c r="BG57" s="3"/>
       <c r="BH57" s="3"/>
       <c r="BI57" s="3"/>
-    </row>
-    <row r="58" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ57" s="3"/>
+      <c r="BK57" s="3"/>
+      <c r="BL57" s="3"/>
+      <c r="BM57" s="3"/>
+    </row>
+    <row r="58" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -6188,8 +6576,12 @@
       <c r="BG58" s="3"/>
       <c r="BH58" s="3"/>
       <c r="BI58" s="3"/>
-    </row>
-    <row r="59" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ58" s="3"/>
+      <c r="BK58" s="3"/>
+      <c r="BL58" s="3"/>
+      <c r="BM58" s="3"/>
+    </row>
+    <row r="59" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -6249,8 +6641,12 @@
       <c r="BG59" s="3"/>
       <c r="BH59" s="3"/>
       <c r="BI59" s="3"/>
-    </row>
-    <row r="60" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ59" s="3"/>
+      <c r="BK59" s="3"/>
+      <c r="BL59" s="3"/>
+      <c r="BM59" s="3"/>
+    </row>
+    <row r="60" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -6310,8 +6706,12 @@
       <c r="BG60" s="3"/>
       <c r="BH60" s="3"/>
       <c r="BI60" s="3"/>
-    </row>
-    <row r="61" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ60" s="3"/>
+      <c r="BK60" s="3"/>
+      <c r="BL60" s="3"/>
+      <c r="BM60" s="3"/>
+    </row>
+    <row r="61" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -6371,8 +6771,12 @@
       <c r="BG61" s="3"/>
       <c r="BH61" s="3"/>
       <c r="BI61" s="3"/>
-    </row>
-    <row r="62" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ61" s="3"/>
+      <c r="BK61" s="3"/>
+      <c r="BL61" s="3"/>
+      <c r="BM61" s="3"/>
+    </row>
+    <row r="62" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -6432,8 +6836,12 @@
       <c r="BG62" s="3"/>
       <c r="BH62" s="3"/>
       <c r="BI62" s="3"/>
-    </row>
-    <row r="63" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ62" s="3"/>
+      <c r="BK62" s="3"/>
+      <c r="BL62" s="3"/>
+      <c r="BM62" s="3"/>
+    </row>
+    <row r="63" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -6493,8 +6901,12 @@
       <c r="BG63" s="3"/>
       <c r="BH63" s="3"/>
       <c r="BI63" s="3"/>
-    </row>
-    <row r="64" spans="2:61" x14ac:dyDescent="0.2">
+      <c r="BJ63" s="3"/>
+      <c r="BK63" s="3"/>
+      <c r="BL63" s="3"/>
+      <c r="BM63" s="3"/>
+    </row>
+    <row r="64" spans="2:65" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -6554,8 +6966,12 @@
       <c r="BG64" s="3"/>
       <c r="BH64" s="3"/>
       <c r="BI64" s="3"/>
-    </row>
-    <row r="65" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ64" s="3"/>
+      <c r="BK64" s="3"/>
+      <c r="BL64" s="3"/>
+      <c r="BM64" s="3"/>
+    </row>
+    <row r="65" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -6615,8 +7031,12 @@
       <c r="BG65" s="3"/>
       <c r="BH65" s="3"/>
       <c r="BI65" s="3"/>
-    </row>
-    <row r="66" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ65" s="3"/>
+      <c r="BK65" s="3"/>
+      <c r="BL65" s="3"/>
+      <c r="BM65" s="3"/>
+    </row>
+    <row r="66" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -6676,8 +7096,12 @@
       <c r="BG66" s="3"/>
       <c r="BH66" s="3"/>
       <c r="BI66" s="3"/>
-    </row>
-    <row r="67" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ66" s="3"/>
+      <c r="BK66" s="3"/>
+      <c r="BL66" s="3"/>
+      <c r="BM66" s="3"/>
+    </row>
+    <row r="67" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -6737,8 +7161,12 @@
       <c r="BG67" s="3"/>
       <c r="BH67" s="3"/>
       <c r="BI67" s="3"/>
-    </row>
-    <row r="68" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ67" s="3"/>
+      <c r="BK67" s="3"/>
+      <c r="BL67" s="3"/>
+      <c r="BM67" s="3"/>
+    </row>
+    <row r="68" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -6798,8 +7226,12 @@
       <c r="BG68" s="3"/>
       <c r="BH68" s="3"/>
       <c r="BI68" s="3"/>
-    </row>
-    <row r="69" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ68" s="3"/>
+      <c r="BK68" s="3"/>
+      <c r="BL68" s="3"/>
+      <c r="BM68" s="3"/>
+    </row>
+    <row r="69" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -6859,8 +7291,12 @@
       <c r="BG69" s="3"/>
       <c r="BH69" s="3"/>
       <c r="BI69" s="3"/>
-    </row>
-    <row r="70" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ69" s="3"/>
+      <c r="BK69" s="3"/>
+      <c r="BL69" s="3"/>
+      <c r="BM69" s="3"/>
+    </row>
+    <row r="70" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -6920,8 +7356,12 @@
       <c r="BG70" s="3"/>
       <c r="BH70" s="3"/>
       <c r="BI70" s="3"/>
-    </row>
-    <row r="71" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ70" s="3"/>
+      <c r="BK70" s="3"/>
+      <c r="BL70" s="3"/>
+      <c r="BM70" s="3"/>
+    </row>
+    <row r="71" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -6981,8 +7421,12 @@
       <c r="BG71" s="3"/>
       <c r="BH71" s="3"/>
       <c r="BI71" s="3"/>
-    </row>
-    <row r="72" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ71" s="3"/>
+      <c r="BK71" s="3"/>
+      <c r="BL71" s="3"/>
+      <c r="BM71" s="3"/>
+    </row>
+    <row r="72" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -7042,8 +7486,12 @@
       <c r="BG72" s="3"/>
       <c r="BH72" s="3"/>
       <c r="BI72" s="3"/>
-    </row>
-    <row r="73" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ72" s="3"/>
+      <c r="BK72" s="3"/>
+      <c r="BL72" s="3"/>
+      <c r="BM72" s="3"/>
+    </row>
+    <row r="73" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -7103,8 +7551,12 @@
       <c r="BG73" s="3"/>
       <c r="BH73" s="3"/>
       <c r="BI73" s="3"/>
-    </row>
-    <row r="74" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ73" s="3"/>
+      <c r="BK73" s="3"/>
+      <c r="BL73" s="3"/>
+      <c r="BM73" s="3"/>
+    </row>
+    <row r="74" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -7164,8 +7616,12 @@
       <c r="BG74" s="3"/>
       <c r="BH74" s="3"/>
       <c r="BI74" s="3"/>
-    </row>
-    <row r="75" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ74" s="3"/>
+      <c r="BK74" s="3"/>
+      <c r="BL74" s="3"/>
+      <c r="BM74" s="3"/>
+    </row>
+    <row r="75" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -7225,8 +7681,12 @@
       <c r="BG75" s="3"/>
       <c r="BH75" s="3"/>
       <c r="BI75" s="3"/>
-    </row>
-    <row r="76" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ75" s="3"/>
+      <c r="BK75" s="3"/>
+      <c r="BL75" s="3"/>
+      <c r="BM75" s="3"/>
+    </row>
+    <row r="76" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -7286,8 +7746,12 @@
       <c r="BG76" s="3"/>
       <c r="BH76" s="3"/>
       <c r="BI76" s="3"/>
-    </row>
-    <row r="77" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ76" s="3"/>
+      <c r="BK76" s="3"/>
+      <c r="BL76" s="3"/>
+      <c r="BM76" s="3"/>
+    </row>
+    <row r="77" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -7347,8 +7811,12 @@
       <c r="BG77" s="3"/>
       <c r="BH77" s="3"/>
       <c r="BI77" s="3"/>
-    </row>
-    <row r="78" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ77" s="3"/>
+      <c r="BK77" s="3"/>
+      <c r="BL77" s="3"/>
+      <c r="BM77" s="3"/>
+    </row>
+    <row r="78" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -7408,8 +7876,12 @@
       <c r="BG78" s="3"/>
       <c r="BH78" s="3"/>
       <c r="BI78" s="3"/>
-    </row>
-    <row r="79" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ78" s="3"/>
+      <c r="BK78" s="3"/>
+      <c r="BL78" s="3"/>
+      <c r="BM78" s="3"/>
+    </row>
+    <row r="79" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -7469,8 +7941,12 @@
       <c r="BG79" s="3"/>
       <c r="BH79" s="3"/>
       <c r="BI79" s="3"/>
-    </row>
-    <row r="80" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ79" s="3"/>
+      <c r="BK79" s="3"/>
+      <c r="BL79" s="3"/>
+      <c r="BM79" s="3"/>
+    </row>
+    <row r="80" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7530,8 +8006,12 @@
       <c r="BG80" s="3"/>
       <c r="BH80" s="3"/>
       <c r="BI80" s="3"/>
-    </row>
-    <row r="81" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ80" s="3"/>
+      <c r="BK80" s="3"/>
+      <c r="BL80" s="3"/>
+      <c r="BM80" s="3"/>
+    </row>
+    <row r="81" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7591,8 +8071,12 @@
       <c r="BG81" s="3"/>
       <c r="BH81" s="3"/>
       <c r="BI81" s="3"/>
-    </row>
-    <row r="82" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ81" s="3"/>
+      <c r="BK81" s="3"/>
+      <c r="BL81" s="3"/>
+      <c r="BM81" s="3"/>
+    </row>
+    <row r="82" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7652,8 +8136,12 @@
       <c r="BG82" s="3"/>
       <c r="BH82" s="3"/>
       <c r="BI82" s="3"/>
-    </row>
-    <row r="83" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ82" s="3"/>
+      <c r="BK82" s="3"/>
+      <c r="BL82" s="3"/>
+      <c r="BM82" s="3"/>
+    </row>
+    <row r="83" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7713,8 +8201,12 @@
       <c r="BG83" s="3"/>
       <c r="BH83" s="3"/>
       <c r="BI83" s="3"/>
-    </row>
-    <row r="84" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ83" s="3"/>
+      <c r="BK83" s="3"/>
+      <c r="BL83" s="3"/>
+      <c r="BM83" s="3"/>
+    </row>
+    <row r="84" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -7774,8 +8266,12 @@
       <c r="BG84" s="3"/>
       <c r="BH84" s="3"/>
       <c r="BI84" s="3"/>
-    </row>
-    <row r="85" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ84" s="3"/>
+      <c r="BK84" s="3"/>
+      <c r="BL84" s="3"/>
+      <c r="BM84" s="3"/>
+    </row>
+    <row r="85" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -7835,8 +8331,12 @@
       <c r="BG85" s="3"/>
       <c r="BH85" s="3"/>
       <c r="BI85" s="3"/>
-    </row>
-    <row r="86" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ85" s="3"/>
+      <c r="BK85" s="3"/>
+      <c r="BL85" s="3"/>
+      <c r="BM85" s="3"/>
+    </row>
+    <row r="86" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -7896,8 +8396,12 @@
       <c r="BG86" s="3"/>
       <c r="BH86" s="3"/>
       <c r="BI86" s="3"/>
-    </row>
-    <row r="87" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ86" s="3"/>
+      <c r="BK86" s="3"/>
+      <c r="BL86" s="3"/>
+      <c r="BM86" s="3"/>
+    </row>
+    <row r="87" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -7957,8 +8461,12 @@
       <c r="BG87" s="3"/>
       <c r="BH87" s="3"/>
       <c r="BI87" s="3"/>
-    </row>
-    <row r="88" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ87" s="3"/>
+      <c r="BK87" s="3"/>
+      <c r="BL87" s="3"/>
+      <c r="BM87" s="3"/>
+    </row>
+    <row r="88" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -8018,8 +8526,12 @@
       <c r="BG88" s="3"/>
       <c r="BH88" s="3"/>
       <c r="BI88" s="3"/>
-    </row>
-    <row r="89" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ88" s="3"/>
+      <c r="BK88" s="3"/>
+      <c r="BL88" s="3"/>
+      <c r="BM88" s="3"/>
+    </row>
+    <row r="89" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -8079,8 +8591,12 @@
       <c r="BG89" s="3"/>
       <c r="BH89" s="3"/>
       <c r="BI89" s="3"/>
-    </row>
-    <row r="90" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ89" s="3"/>
+      <c r="BK89" s="3"/>
+      <c r="BL89" s="3"/>
+      <c r="BM89" s="3"/>
+    </row>
+    <row r="90" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -8140,8 +8656,12 @@
       <c r="BG90" s="3"/>
       <c r="BH90" s="3"/>
       <c r="BI90" s="3"/>
-    </row>
-    <row r="91" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ90" s="3"/>
+      <c r="BK90" s="3"/>
+      <c r="BL90" s="3"/>
+      <c r="BM90" s="3"/>
+    </row>
+    <row r="91" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -8201,8 +8721,12 @@
       <c r="BG91" s="3"/>
       <c r="BH91" s="3"/>
       <c r="BI91" s="3"/>
-    </row>
-    <row r="92" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ91" s="3"/>
+      <c r="BK91" s="3"/>
+      <c r="BL91" s="3"/>
+      <c r="BM91" s="3"/>
+    </row>
+    <row r="92" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -8262,8 +8786,12 @@
       <c r="BG92" s="3"/>
       <c r="BH92" s="3"/>
       <c r="BI92" s="3"/>
-    </row>
-    <row r="93" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ92" s="3"/>
+      <c r="BK92" s="3"/>
+      <c r="BL92" s="3"/>
+      <c r="BM92" s="3"/>
+    </row>
+    <row r="93" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -8323,8 +8851,12 @@
       <c r="BG93" s="3"/>
       <c r="BH93" s="3"/>
       <c r="BI93" s="3"/>
-    </row>
-    <row r="94" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ93" s="3"/>
+      <c r="BK93" s="3"/>
+      <c r="BL93" s="3"/>
+      <c r="BM93" s="3"/>
+    </row>
+    <row r="94" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -8384,8 +8916,12 @@
       <c r="BG94" s="3"/>
       <c r="BH94" s="3"/>
       <c r="BI94" s="3"/>
-    </row>
-    <row r="95" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ94" s="3"/>
+      <c r="BK94" s="3"/>
+      <c r="BL94" s="3"/>
+      <c r="BM94" s="3"/>
+    </row>
+    <row r="95" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -8445,8 +8981,12 @@
       <c r="BG95" s="3"/>
       <c r="BH95" s="3"/>
       <c r="BI95" s="3"/>
-    </row>
-    <row r="96" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ95" s="3"/>
+      <c r="BK95" s="3"/>
+      <c r="BL95" s="3"/>
+      <c r="BM95" s="3"/>
+    </row>
+    <row r="96" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -8506,8 +9046,12 @@
       <c r="BG96" s="3"/>
       <c r="BH96" s="3"/>
       <c r="BI96" s="3"/>
-    </row>
-    <row r="97" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ96" s="3"/>
+      <c r="BK96" s="3"/>
+      <c r="BL96" s="3"/>
+      <c r="BM96" s="3"/>
+    </row>
+    <row r="97" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -8567,8 +9111,12 @@
       <c r="BG97" s="3"/>
       <c r="BH97" s="3"/>
       <c r="BI97" s="3"/>
-    </row>
-    <row r="98" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ97" s="3"/>
+      <c r="BK97" s="3"/>
+      <c r="BL97" s="3"/>
+      <c r="BM97" s="3"/>
+    </row>
+    <row r="98" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -8628,8 +9176,12 @@
       <c r="BG98" s="3"/>
       <c r="BH98" s="3"/>
       <c r="BI98" s="3"/>
-    </row>
-    <row r="99" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ98" s="3"/>
+      <c r="BK98" s="3"/>
+      <c r="BL98" s="3"/>
+      <c r="BM98" s="3"/>
+    </row>
+    <row r="99" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -8689,8 +9241,12 @@
       <c r="BG99" s="3"/>
       <c r="BH99" s="3"/>
       <c r="BI99" s="3"/>
-    </row>
-    <row r="100" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ99" s="3"/>
+      <c r="BK99" s="3"/>
+      <c r="BL99" s="3"/>
+      <c r="BM99" s="3"/>
+    </row>
+    <row r="100" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -8750,8 +9306,12 @@
       <c r="BG100" s="3"/>
       <c r="BH100" s="3"/>
       <c r="BI100" s="3"/>
-    </row>
-    <row r="101" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ100" s="3"/>
+      <c r="BK100" s="3"/>
+      <c r="BL100" s="3"/>
+      <c r="BM100" s="3"/>
+    </row>
+    <row r="101" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -8811,8 +9371,12 @@
       <c r="BG101" s="3"/>
       <c r="BH101" s="3"/>
       <c r="BI101" s="3"/>
-    </row>
-    <row r="102" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ101" s="3"/>
+      <c r="BK101" s="3"/>
+      <c r="BL101" s="3"/>
+      <c r="BM101" s="3"/>
+    </row>
+    <row r="102" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -8872,8 +9436,12 @@
       <c r="BG102" s="3"/>
       <c r="BH102" s="3"/>
       <c r="BI102" s="3"/>
-    </row>
-    <row r="103" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ102" s="3"/>
+      <c r="BK102" s="3"/>
+      <c r="BL102" s="3"/>
+      <c r="BM102" s="3"/>
+    </row>
+    <row r="103" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -8933,8 +9501,12 @@
       <c r="BG103" s="3"/>
       <c r="BH103" s="3"/>
       <c r="BI103" s="3"/>
-    </row>
-    <row r="104" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ103" s="3"/>
+      <c r="BK103" s="3"/>
+      <c r="BL103" s="3"/>
+      <c r="BM103" s="3"/>
+    </row>
+    <row r="104" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -8994,8 +9566,12 @@
       <c r="BG104" s="3"/>
       <c r="BH104" s="3"/>
       <c r="BI104" s="3"/>
-    </row>
-    <row r="105" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ104" s="3"/>
+      <c r="BK104" s="3"/>
+      <c r="BL104" s="3"/>
+      <c r="BM104" s="3"/>
+    </row>
+    <row r="105" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -9055,8 +9631,12 @@
       <c r="BG105" s="3"/>
       <c r="BH105" s="3"/>
       <c r="BI105" s="3"/>
-    </row>
-    <row r="106" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ105" s="3"/>
+      <c r="BK105" s="3"/>
+      <c r="BL105" s="3"/>
+      <c r="BM105" s="3"/>
+    </row>
+    <row r="106" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -9116,8 +9696,12 @@
       <c r="BG106" s="3"/>
       <c r="BH106" s="3"/>
       <c r="BI106" s="3"/>
-    </row>
-    <row r="107" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ106" s="3"/>
+      <c r="BK106" s="3"/>
+      <c r="BL106" s="3"/>
+      <c r="BM106" s="3"/>
+    </row>
+    <row r="107" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -9177,8 +9761,12 @@
       <c r="BG107" s="3"/>
       <c r="BH107" s="3"/>
       <c r="BI107" s="3"/>
-    </row>
-    <row r="108" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ107" s="3"/>
+      <c r="BK107" s="3"/>
+      <c r="BL107" s="3"/>
+      <c r="BM107" s="3"/>
+    </row>
+    <row r="108" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -9238,8 +9826,12 @@
       <c r="BG108" s="3"/>
       <c r="BH108" s="3"/>
       <c r="BI108" s="3"/>
-    </row>
-    <row r="109" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ108" s="3"/>
+      <c r="BK108" s="3"/>
+      <c r="BL108" s="3"/>
+      <c r="BM108" s="3"/>
+    </row>
+    <row r="109" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -9299,8 +9891,12 @@
       <c r="BG109" s="3"/>
       <c r="BH109" s="3"/>
       <c r="BI109" s="3"/>
-    </row>
-    <row r="110" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ109" s="3"/>
+      <c r="BK109" s="3"/>
+      <c r="BL109" s="3"/>
+      <c r="BM109" s="3"/>
+    </row>
+    <row r="110" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -9360,8 +9956,12 @@
       <c r="BG110" s="3"/>
       <c r="BH110" s="3"/>
       <c r="BI110" s="3"/>
-    </row>
-    <row r="111" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ110" s="3"/>
+      <c r="BK110" s="3"/>
+      <c r="BL110" s="3"/>
+      <c r="BM110" s="3"/>
+    </row>
+    <row r="111" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -9421,8 +10021,12 @@
       <c r="BG111" s="3"/>
       <c r="BH111" s="3"/>
       <c r="BI111" s="3"/>
-    </row>
-    <row r="112" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ111" s="3"/>
+      <c r="BK111" s="3"/>
+      <c r="BL111" s="3"/>
+      <c r="BM111" s="3"/>
+    </row>
+    <row r="112" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -9482,8 +10086,12 @@
       <c r="BG112" s="3"/>
       <c r="BH112" s="3"/>
       <c r="BI112" s="3"/>
-    </row>
-    <row r="113" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ112" s="3"/>
+      <c r="BK112" s="3"/>
+      <c r="BL112" s="3"/>
+      <c r="BM112" s="3"/>
+    </row>
+    <row r="113" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -9543,8 +10151,12 @@
       <c r="BG113" s="3"/>
       <c r="BH113" s="3"/>
       <c r="BI113" s="3"/>
-    </row>
-    <row r="114" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ113" s="3"/>
+      <c r="BK113" s="3"/>
+      <c r="BL113" s="3"/>
+      <c r="BM113" s="3"/>
+    </row>
+    <row r="114" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -9604,8 +10216,12 @@
       <c r="BG114" s="3"/>
       <c r="BH114" s="3"/>
       <c r="BI114" s="3"/>
-    </row>
-    <row r="115" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ114" s="3"/>
+      <c r="BK114" s="3"/>
+      <c r="BL114" s="3"/>
+      <c r="BM114" s="3"/>
+    </row>
+    <row r="115" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -9665,8 +10281,12 @@
       <c r="BG115" s="3"/>
       <c r="BH115" s="3"/>
       <c r="BI115" s="3"/>
-    </row>
-    <row r="116" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ115" s="3"/>
+      <c r="BK115" s="3"/>
+      <c r="BL115" s="3"/>
+      <c r="BM115" s="3"/>
+    </row>
+    <row r="116" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -9726,8 +10346,12 @@
       <c r="BG116" s="3"/>
       <c r="BH116" s="3"/>
       <c r="BI116" s="3"/>
-    </row>
-    <row r="117" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ116" s="3"/>
+      <c r="BK116" s="3"/>
+      <c r="BL116" s="3"/>
+      <c r="BM116" s="3"/>
+    </row>
+    <row r="117" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -9787,8 +10411,12 @@
       <c r="BG117" s="3"/>
       <c r="BH117" s="3"/>
       <c r="BI117" s="3"/>
-    </row>
-    <row r="118" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ117" s="3"/>
+      <c r="BK117" s="3"/>
+      <c r="BL117" s="3"/>
+      <c r="BM117" s="3"/>
+    </row>
+    <row r="118" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -9848,8 +10476,12 @@
       <c r="BG118" s="3"/>
       <c r="BH118" s="3"/>
       <c r="BI118" s="3"/>
-    </row>
-    <row r="119" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ118" s="3"/>
+      <c r="BK118" s="3"/>
+      <c r="BL118" s="3"/>
+      <c r="BM118" s="3"/>
+    </row>
+    <row r="119" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -9909,8 +10541,12 @@
       <c r="BG119" s="3"/>
       <c r="BH119" s="3"/>
       <c r="BI119" s="3"/>
-    </row>
-    <row r="120" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ119" s="3"/>
+      <c r="BK119" s="3"/>
+      <c r="BL119" s="3"/>
+      <c r="BM119" s="3"/>
+    </row>
+    <row r="120" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -9970,8 +10606,12 @@
       <c r="BG120" s="3"/>
       <c r="BH120" s="3"/>
       <c r="BI120" s="3"/>
-    </row>
-    <row r="121" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ120" s="3"/>
+      <c r="BK120" s="3"/>
+      <c r="BL120" s="3"/>
+      <c r="BM120" s="3"/>
+    </row>
+    <row r="121" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -10031,8 +10671,12 @@
       <c r="BG121" s="3"/>
       <c r="BH121" s="3"/>
       <c r="BI121" s="3"/>
-    </row>
-    <row r="122" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ121" s="3"/>
+      <c r="BK121" s="3"/>
+      <c r="BL121" s="3"/>
+      <c r="BM121" s="3"/>
+    </row>
+    <row r="122" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -10092,8 +10736,12 @@
       <c r="BG122" s="3"/>
       <c r="BH122" s="3"/>
       <c r="BI122" s="3"/>
-    </row>
-    <row r="123" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ122" s="3"/>
+      <c r="BK122" s="3"/>
+      <c r="BL122" s="3"/>
+      <c r="BM122" s="3"/>
+    </row>
+    <row r="123" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -10153,8 +10801,12 @@
       <c r="BG123" s="3"/>
       <c r="BH123" s="3"/>
       <c r="BI123" s="3"/>
-    </row>
-    <row r="124" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ123" s="3"/>
+      <c r="BK123" s="3"/>
+      <c r="BL123" s="3"/>
+      <c r="BM123" s="3"/>
+    </row>
+    <row r="124" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -10214,8 +10866,12 @@
       <c r="BG124" s="3"/>
       <c r="BH124" s="3"/>
       <c r="BI124" s="3"/>
-    </row>
-    <row r="125" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ124" s="3"/>
+      <c r="BK124" s="3"/>
+      <c r="BL124" s="3"/>
+      <c r="BM124" s="3"/>
+    </row>
+    <row r="125" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -10275,8 +10931,12 @@
       <c r="BG125" s="3"/>
       <c r="BH125" s="3"/>
       <c r="BI125" s="3"/>
-    </row>
-    <row r="126" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ125" s="3"/>
+      <c r="BK125" s="3"/>
+      <c r="BL125" s="3"/>
+      <c r="BM125" s="3"/>
+    </row>
+    <row r="126" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -10336,8 +10996,12 @@
       <c r="BG126" s="3"/>
       <c r="BH126" s="3"/>
       <c r="BI126" s="3"/>
-    </row>
-    <row r="127" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ126" s="3"/>
+      <c r="BK126" s="3"/>
+      <c r="BL126" s="3"/>
+      <c r="BM126" s="3"/>
+    </row>
+    <row r="127" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -10397,8 +11061,12 @@
       <c r="BG127" s="3"/>
       <c r="BH127" s="3"/>
       <c r="BI127" s="3"/>
-    </row>
-    <row r="128" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ127" s="3"/>
+      <c r="BK127" s="3"/>
+      <c r="BL127" s="3"/>
+      <c r="BM127" s="3"/>
+    </row>
+    <row r="128" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -10458,8 +11126,12 @@
       <c r="BG128" s="3"/>
       <c r="BH128" s="3"/>
       <c r="BI128" s="3"/>
-    </row>
-    <row r="129" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ128" s="3"/>
+      <c r="BK128" s="3"/>
+      <c r="BL128" s="3"/>
+      <c r="BM128" s="3"/>
+    </row>
+    <row r="129" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -10519,8 +11191,12 @@
       <c r="BG129" s="3"/>
       <c r="BH129" s="3"/>
       <c r="BI129" s="3"/>
-    </row>
-    <row r="130" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ129" s="3"/>
+      <c r="BK129" s="3"/>
+      <c r="BL129" s="3"/>
+      <c r="BM129" s="3"/>
+    </row>
+    <row r="130" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -10580,8 +11256,12 @@
       <c r="BG130" s="3"/>
       <c r="BH130" s="3"/>
       <c r="BI130" s="3"/>
-    </row>
-    <row r="131" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ130" s="3"/>
+      <c r="BK130" s="3"/>
+      <c r="BL130" s="3"/>
+      <c r="BM130" s="3"/>
+    </row>
+    <row r="131" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -10641,8 +11321,12 @@
       <c r="BG131" s="3"/>
       <c r="BH131" s="3"/>
       <c r="BI131" s="3"/>
-    </row>
-    <row r="132" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ131" s="3"/>
+      <c r="BK131" s="3"/>
+      <c r="BL131" s="3"/>
+      <c r="BM131" s="3"/>
+    </row>
+    <row r="132" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -10702,8 +11386,12 @@
       <c r="BG132" s="3"/>
       <c r="BH132" s="3"/>
       <c r="BI132" s="3"/>
-    </row>
-    <row r="133" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ132" s="3"/>
+      <c r="BK132" s="3"/>
+      <c r="BL132" s="3"/>
+      <c r="BM132" s="3"/>
+    </row>
+    <row r="133" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -10763,8 +11451,12 @@
       <c r="BG133" s="3"/>
       <c r="BH133" s="3"/>
       <c r="BI133" s="3"/>
-    </row>
-    <row r="134" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ133" s="3"/>
+      <c r="BK133" s="3"/>
+      <c r="BL133" s="3"/>
+      <c r="BM133" s="3"/>
+    </row>
+    <row r="134" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -10824,8 +11516,12 @@
       <c r="BG134" s="3"/>
       <c r="BH134" s="3"/>
       <c r="BI134" s="3"/>
-    </row>
-    <row r="135" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ134" s="3"/>
+      <c r="BK134" s="3"/>
+      <c r="BL134" s="3"/>
+      <c r="BM134" s="3"/>
+    </row>
+    <row r="135" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -10885,8 +11581,12 @@
       <c r="BG135" s="3"/>
       <c r="BH135" s="3"/>
       <c r="BI135" s="3"/>
-    </row>
-    <row r="136" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ135" s="3"/>
+      <c r="BK135" s="3"/>
+      <c r="BL135" s="3"/>
+      <c r="BM135" s="3"/>
+    </row>
+    <row r="136" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -10946,8 +11646,12 @@
       <c r="BG136" s="3"/>
       <c r="BH136" s="3"/>
       <c r="BI136" s="3"/>
-    </row>
-    <row r="137" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ136" s="3"/>
+      <c r="BK136" s="3"/>
+      <c r="BL136" s="3"/>
+      <c r="BM136" s="3"/>
+    </row>
+    <row r="137" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -11007,8 +11711,12 @@
       <c r="BG137" s="3"/>
       <c r="BH137" s="3"/>
       <c r="BI137" s="3"/>
-    </row>
-    <row r="138" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ137" s="3"/>
+      <c r="BK137" s="3"/>
+      <c r="BL137" s="3"/>
+      <c r="BM137" s="3"/>
+    </row>
+    <row r="138" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -11068,8 +11776,12 @@
       <c r="BG138" s="3"/>
       <c r="BH138" s="3"/>
       <c r="BI138" s="3"/>
-    </row>
-    <row r="139" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ138" s="3"/>
+      <c r="BK138" s="3"/>
+      <c r="BL138" s="3"/>
+      <c r="BM138" s="3"/>
+    </row>
+    <row r="139" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -11129,8 +11841,12 @@
       <c r="BG139" s="3"/>
       <c r="BH139" s="3"/>
       <c r="BI139" s="3"/>
-    </row>
-    <row r="140" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ139" s="3"/>
+      <c r="BK139" s="3"/>
+      <c r="BL139" s="3"/>
+      <c r="BM139" s="3"/>
+    </row>
+    <row r="140" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -11190,8 +11906,12 @@
       <c r="BG140" s="3"/>
       <c r="BH140" s="3"/>
       <c r="BI140" s="3"/>
-    </row>
-    <row r="141" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ140" s="3"/>
+      <c r="BK140" s="3"/>
+      <c r="BL140" s="3"/>
+      <c r="BM140" s="3"/>
+    </row>
+    <row r="141" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -11251,8 +11971,12 @@
       <c r="BG141" s="3"/>
       <c r="BH141" s="3"/>
       <c r="BI141" s="3"/>
-    </row>
-    <row r="142" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ141" s="3"/>
+      <c r="BK141" s="3"/>
+      <c r="BL141" s="3"/>
+      <c r="BM141" s="3"/>
+    </row>
+    <row r="142" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -11312,8 +12036,12 @@
       <c r="BG142" s="3"/>
       <c r="BH142" s="3"/>
       <c r="BI142" s="3"/>
-    </row>
-    <row r="143" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ142" s="3"/>
+      <c r="BK142" s="3"/>
+      <c r="BL142" s="3"/>
+      <c r="BM142" s="3"/>
+    </row>
+    <row r="143" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -11373,8 +12101,12 @@
       <c r="BG143" s="3"/>
       <c r="BH143" s="3"/>
       <c r="BI143" s="3"/>
-    </row>
-    <row r="144" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ143" s="3"/>
+      <c r="BK143" s="3"/>
+      <c r="BL143" s="3"/>
+      <c r="BM143" s="3"/>
+    </row>
+    <row r="144" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -11434,8 +12166,12 @@
       <c r="BG144" s="3"/>
       <c r="BH144" s="3"/>
       <c r="BI144" s="3"/>
-    </row>
-    <row r="145" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ144" s="3"/>
+      <c r="BK144" s="3"/>
+      <c r="BL144" s="3"/>
+      <c r="BM144" s="3"/>
+    </row>
+    <row r="145" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -11495,8 +12231,12 @@
       <c r="BG145" s="3"/>
       <c r="BH145" s="3"/>
       <c r="BI145" s="3"/>
-    </row>
-    <row r="146" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ145" s="3"/>
+      <c r="BK145" s="3"/>
+      <c r="BL145" s="3"/>
+      <c r="BM145" s="3"/>
+    </row>
+    <row r="146" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -11556,8 +12296,12 @@
       <c r="BG146" s="3"/>
       <c r="BH146" s="3"/>
       <c r="BI146" s="3"/>
-    </row>
-    <row r="147" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ146" s="3"/>
+      <c r="BK146" s="3"/>
+      <c r="BL146" s="3"/>
+      <c r="BM146" s="3"/>
+    </row>
+    <row r="147" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -11617,8 +12361,12 @@
       <c r="BG147" s="3"/>
       <c r="BH147" s="3"/>
       <c r="BI147" s="3"/>
-    </row>
-    <row r="148" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ147" s="3"/>
+      <c r="BK147" s="3"/>
+      <c r="BL147" s="3"/>
+      <c r="BM147" s="3"/>
+    </row>
+    <row r="148" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -11678,8 +12426,12 @@
       <c r="BG148" s="3"/>
       <c r="BH148" s="3"/>
       <c r="BI148" s="3"/>
-    </row>
-    <row r="149" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ148" s="3"/>
+      <c r="BK148" s="3"/>
+      <c r="BL148" s="3"/>
+      <c r="BM148" s="3"/>
+    </row>
+    <row r="149" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -11739,8 +12491,12 @@
       <c r="BG149" s="3"/>
       <c r="BH149" s="3"/>
       <c r="BI149" s="3"/>
-    </row>
-    <row r="150" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ149" s="3"/>
+      <c r="BK149" s="3"/>
+      <c r="BL149" s="3"/>
+      <c r="BM149" s="3"/>
+    </row>
+    <row r="150" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -11800,8 +12556,12 @@
       <c r="BG150" s="3"/>
       <c r="BH150" s="3"/>
       <c r="BI150" s="3"/>
-    </row>
-    <row r="151" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ150" s="3"/>
+      <c r="BK150" s="3"/>
+      <c r="BL150" s="3"/>
+      <c r="BM150" s="3"/>
+    </row>
+    <row r="151" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -11861,8 +12621,12 @@
       <c r="BG151" s="3"/>
       <c r="BH151" s="3"/>
       <c r="BI151" s="3"/>
-    </row>
-    <row r="152" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ151" s="3"/>
+      <c r="BK151" s="3"/>
+      <c r="BL151" s="3"/>
+      <c r="BM151" s="3"/>
+    </row>
+    <row r="152" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -11922,8 +12686,12 @@
       <c r="BG152" s="3"/>
       <c r="BH152" s="3"/>
       <c r="BI152" s="3"/>
-    </row>
-    <row r="153" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ152" s="3"/>
+      <c r="BK152" s="3"/>
+      <c r="BL152" s="3"/>
+      <c r="BM152" s="3"/>
+    </row>
+    <row r="153" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -11983,8 +12751,12 @@
       <c r="BG153" s="3"/>
       <c r="BH153" s="3"/>
       <c r="BI153" s="3"/>
-    </row>
-    <row r="154" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ153" s="3"/>
+      <c r="BK153" s="3"/>
+      <c r="BL153" s="3"/>
+      <c r="BM153" s="3"/>
+    </row>
+    <row r="154" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -12044,8 +12816,12 @@
       <c r="BG154" s="3"/>
       <c r="BH154" s="3"/>
       <c r="BI154" s="3"/>
-    </row>
-    <row r="155" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ154" s="3"/>
+      <c r="BK154" s="3"/>
+      <c r="BL154" s="3"/>
+      <c r="BM154" s="3"/>
+    </row>
+    <row r="155" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -12105,8 +12881,12 @@
       <c r="BG155" s="3"/>
       <c r="BH155" s="3"/>
       <c r="BI155" s="3"/>
-    </row>
-    <row r="156" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ155" s="3"/>
+      <c r="BK155" s="3"/>
+      <c r="BL155" s="3"/>
+      <c r="BM155" s="3"/>
+    </row>
+    <row r="156" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -12166,8 +12946,12 @@
       <c r="BG156" s="3"/>
       <c r="BH156" s="3"/>
       <c r="BI156" s="3"/>
-    </row>
-    <row r="157" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ156" s="3"/>
+      <c r="BK156" s="3"/>
+      <c r="BL156" s="3"/>
+      <c r="BM156" s="3"/>
+    </row>
+    <row r="157" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -12227,8 +13011,12 @@
       <c r="BG157" s="3"/>
       <c r="BH157" s="3"/>
       <c r="BI157" s="3"/>
-    </row>
-    <row r="158" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ157" s="3"/>
+      <c r="BK157" s="3"/>
+      <c r="BL157" s="3"/>
+      <c r="BM157" s="3"/>
+    </row>
+    <row r="158" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -12288,8 +13076,12 @@
       <c r="BG158" s="3"/>
       <c r="BH158" s="3"/>
       <c r="BI158" s="3"/>
-    </row>
-    <row r="159" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ158" s="3"/>
+      <c r="BK158" s="3"/>
+      <c r="BL158" s="3"/>
+      <c r="BM158" s="3"/>
+    </row>
+    <row r="159" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -12349,8 +13141,12 @@
       <c r="BG159" s="3"/>
       <c r="BH159" s="3"/>
       <c r="BI159" s="3"/>
-    </row>
-    <row r="160" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ159" s="3"/>
+      <c r="BK159" s="3"/>
+      <c r="BL159" s="3"/>
+      <c r="BM159" s="3"/>
+    </row>
+    <row r="160" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -12410,8 +13206,12 @@
       <c r="BG160" s="3"/>
       <c r="BH160" s="3"/>
       <c r="BI160" s="3"/>
-    </row>
-    <row r="161" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ160" s="3"/>
+      <c r="BK160" s="3"/>
+      <c r="BL160" s="3"/>
+      <c r="BM160" s="3"/>
+    </row>
+    <row r="161" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -12471,8 +13271,12 @@
       <c r="BG161" s="3"/>
       <c r="BH161" s="3"/>
       <c r="BI161" s="3"/>
-    </row>
-    <row r="162" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ161" s="3"/>
+      <c r="BK161" s="3"/>
+      <c r="BL161" s="3"/>
+      <c r="BM161" s="3"/>
+    </row>
+    <row r="162" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -12532,8 +13336,12 @@
       <c r="BG162" s="3"/>
       <c r="BH162" s="3"/>
       <c r="BI162" s="3"/>
-    </row>
-    <row r="163" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ162" s="3"/>
+      <c r="BK162" s="3"/>
+      <c r="BL162" s="3"/>
+      <c r="BM162" s="3"/>
+    </row>
+    <row r="163" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -12593,8 +13401,12 @@
       <c r="BG163" s="3"/>
       <c r="BH163" s="3"/>
       <c r="BI163" s="3"/>
-    </row>
-    <row r="164" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ163" s="3"/>
+      <c r="BK163" s="3"/>
+      <c r="BL163" s="3"/>
+      <c r="BM163" s="3"/>
+    </row>
+    <row r="164" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -12654,8 +13466,12 @@
       <c r="BG164" s="3"/>
       <c r="BH164" s="3"/>
       <c r="BI164" s="3"/>
-    </row>
-    <row r="165" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ164" s="3"/>
+      <c r="BK164" s="3"/>
+      <c r="BL164" s="3"/>
+      <c r="BM164" s="3"/>
+    </row>
+    <row r="165" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -12715,8 +13531,12 @@
       <c r="BG165" s="3"/>
       <c r="BH165" s="3"/>
       <c r="BI165" s="3"/>
-    </row>
-    <row r="166" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ165" s="3"/>
+      <c r="BK165" s="3"/>
+      <c r="BL165" s="3"/>
+      <c r="BM165" s="3"/>
+    </row>
+    <row r="166" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -12776,8 +13596,12 @@
       <c r="BG166" s="3"/>
       <c r="BH166" s="3"/>
       <c r="BI166" s="3"/>
-    </row>
-    <row r="167" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ166" s="3"/>
+      <c r="BK166" s="3"/>
+      <c r="BL166" s="3"/>
+      <c r="BM166" s="3"/>
+    </row>
+    <row r="167" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -12837,8 +13661,12 @@
       <c r="BG167" s="3"/>
       <c r="BH167" s="3"/>
       <c r="BI167" s="3"/>
-    </row>
-    <row r="168" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ167" s="3"/>
+      <c r="BK167" s="3"/>
+      <c r="BL167" s="3"/>
+      <c r="BM167" s="3"/>
+    </row>
+    <row r="168" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -12898,8 +13726,12 @@
       <c r="BG168" s="3"/>
       <c r="BH168" s="3"/>
       <c r="BI168" s="3"/>
-    </row>
-    <row r="169" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ168" s="3"/>
+      <c r="BK168" s="3"/>
+      <c r="BL168" s="3"/>
+      <c r="BM168" s="3"/>
+    </row>
+    <row r="169" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -12959,8 +13791,12 @@
       <c r="BG169" s="3"/>
       <c r="BH169" s="3"/>
       <c r="BI169" s="3"/>
-    </row>
-    <row r="170" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ169" s="3"/>
+      <c r="BK169" s="3"/>
+      <c r="BL169" s="3"/>
+      <c r="BM169" s="3"/>
+    </row>
+    <row r="170" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -13020,8 +13856,12 @@
       <c r="BG170" s="3"/>
       <c r="BH170" s="3"/>
       <c r="BI170" s="3"/>
-    </row>
-    <row r="171" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ170" s="3"/>
+      <c r="BK170" s="3"/>
+      <c r="BL170" s="3"/>
+      <c r="BM170" s="3"/>
+    </row>
+    <row r="171" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -13081,8 +13921,12 @@
       <c r="BG171" s="3"/>
       <c r="BH171" s="3"/>
       <c r="BI171" s="3"/>
-    </row>
-    <row r="172" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ171" s="3"/>
+      <c r="BK171" s="3"/>
+      <c r="BL171" s="3"/>
+      <c r="BM171" s="3"/>
+    </row>
+    <row r="172" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -13142,8 +13986,12 @@
       <c r="BG172" s="3"/>
       <c r="BH172" s="3"/>
       <c r="BI172" s="3"/>
-    </row>
-    <row r="173" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ172" s="3"/>
+      <c r="BK172" s="3"/>
+      <c r="BL172" s="3"/>
+      <c r="BM172" s="3"/>
+    </row>
+    <row r="173" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -13203,8 +14051,12 @@
       <c r="BG173" s="3"/>
       <c r="BH173" s="3"/>
       <c r="BI173" s="3"/>
-    </row>
-    <row r="174" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ173" s="3"/>
+      <c r="BK173" s="3"/>
+      <c r="BL173" s="3"/>
+      <c r="BM173" s="3"/>
+    </row>
+    <row r="174" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -13264,8 +14116,12 @@
       <c r="BG174" s="3"/>
       <c r="BH174" s="3"/>
       <c r="BI174" s="3"/>
-    </row>
-    <row r="175" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ174" s="3"/>
+      <c r="BK174" s="3"/>
+      <c r="BL174" s="3"/>
+      <c r="BM174" s="3"/>
+    </row>
+    <row r="175" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -13325,8 +14181,12 @@
       <c r="BG175" s="3"/>
       <c r="BH175" s="3"/>
       <c r="BI175" s="3"/>
-    </row>
-    <row r="176" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ175" s="3"/>
+      <c r="BK175" s="3"/>
+      <c r="BL175" s="3"/>
+      <c r="BM175" s="3"/>
+    </row>
+    <row r="176" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -13386,8 +14246,12 @@
       <c r="BG176" s="3"/>
       <c r="BH176" s="3"/>
       <c r="BI176" s="3"/>
-    </row>
-    <row r="177" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ176" s="3"/>
+      <c r="BK176" s="3"/>
+      <c r="BL176" s="3"/>
+      <c r="BM176" s="3"/>
+    </row>
+    <row r="177" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -13447,8 +14311,12 @@
       <c r="BG177" s="3"/>
       <c r="BH177" s="3"/>
       <c r="BI177" s="3"/>
-    </row>
-    <row r="178" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ177" s="3"/>
+      <c r="BK177" s="3"/>
+      <c r="BL177" s="3"/>
+      <c r="BM177" s="3"/>
+    </row>
+    <row r="178" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -13508,8 +14376,12 @@
       <c r="BG178" s="3"/>
       <c r="BH178" s="3"/>
       <c r="BI178" s="3"/>
-    </row>
-    <row r="179" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ178" s="3"/>
+      <c r="BK178" s="3"/>
+      <c r="BL178" s="3"/>
+      <c r="BM178" s="3"/>
+    </row>
+    <row r="179" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -13569,8 +14441,12 @@
       <c r="BG179" s="3"/>
       <c r="BH179" s="3"/>
       <c r="BI179" s="3"/>
-    </row>
-    <row r="180" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ179" s="3"/>
+      <c r="BK179" s="3"/>
+      <c r="BL179" s="3"/>
+      <c r="BM179" s="3"/>
+    </row>
+    <row r="180" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -13630,8 +14506,12 @@
       <c r="BG180" s="3"/>
       <c r="BH180" s="3"/>
       <c r="BI180" s="3"/>
-    </row>
-    <row r="181" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ180" s="3"/>
+      <c r="BK180" s="3"/>
+      <c r="BL180" s="3"/>
+      <c r="BM180" s="3"/>
+    </row>
+    <row r="181" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -13691,8 +14571,12 @@
       <c r="BG181" s="3"/>
       <c r="BH181" s="3"/>
       <c r="BI181" s="3"/>
-    </row>
-    <row r="182" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ181" s="3"/>
+      <c r="BK181" s="3"/>
+      <c r="BL181" s="3"/>
+      <c r="BM181" s="3"/>
+    </row>
+    <row r="182" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -13752,8 +14636,12 @@
       <c r="BG182" s="3"/>
       <c r="BH182" s="3"/>
       <c r="BI182" s="3"/>
-    </row>
-    <row r="183" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ182" s="3"/>
+      <c r="BK182" s="3"/>
+      <c r="BL182" s="3"/>
+      <c r="BM182" s="3"/>
+    </row>
+    <row r="183" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -13813,8 +14701,12 @@
       <c r="BG183" s="3"/>
       <c r="BH183" s="3"/>
       <c r="BI183" s="3"/>
-    </row>
-    <row r="184" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ183" s="3"/>
+      <c r="BK183" s="3"/>
+      <c r="BL183" s="3"/>
+      <c r="BM183" s="3"/>
+    </row>
+    <row r="184" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -13874,8 +14766,12 @@
       <c r="BG184" s="3"/>
       <c r="BH184" s="3"/>
       <c r="BI184" s="3"/>
-    </row>
-    <row r="185" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ184" s="3"/>
+      <c r="BK184" s="3"/>
+      <c r="BL184" s="3"/>
+      <c r="BM184" s="3"/>
+    </row>
+    <row r="185" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -13935,8 +14831,12 @@
       <c r="BG185" s="3"/>
       <c r="BH185" s="3"/>
       <c r="BI185" s="3"/>
-    </row>
-    <row r="186" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ185" s="3"/>
+      <c r="BK185" s="3"/>
+      <c r="BL185" s="3"/>
+      <c r="BM185" s="3"/>
+    </row>
+    <row r="186" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -13996,8 +14896,12 @@
       <c r="BG186" s="3"/>
       <c r="BH186" s="3"/>
       <c r="BI186" s="3"/>
-    </row>
-    <row r="187" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ186" s="3"/>
+      <c r="BK186" s="3"/>
+      <c r="BL186" s="3"/>
+      <c r="BM186" s="3"/>
+    </row>
+    <row r="187" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -14057,8 +14961,12 @@
       <c r="BG187" s="3"/>
       <c r="BH187" s="3"/>
       <c r="BI187" s="3"/>
-    </row>
-    <row r="188" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ187" s="3"/>
+      <c r="BK187" s="3"/>
+      <c r="BL187" s="3"/>
+      <c r="BM187" s="3"/>
+    </row>
+    <row r="188" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -14118,8 +15026,12 @@
       <c r="BG188" s="3"/>
       <c r="BH188" s="3"/>
       <c r="BI188" s="3"/>
-    </row>
-    <row r="189" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ188" s="3"/>
+      <c r="BK188" s="3"/>
+      <c r="BL188" s="3"/>
+      <c r="BM188" s="3"/>
+    </row>
+    <row r="189" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -14179,8 +15091,12 @@
       <c r="BG189" s="3"/>
       <c r="BH189" s="3"/>
       <c r="BI189" s="3"/>
-    </row>
-    <row r="190" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ189" s="3"/>
+      <c r="BK189" s="3"/>
+      <c r="BL189" s="3"/>
+      <c r="BM189" s="3"/>
+    </row>
+    <row r="190" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -14240,8 +15156,12 @@
       <c r="BG190" s="3"/>
       <c r="BH190" s="3"/>
       <c r="BI190" s="3"/>
-    </row>
-    <row r="191" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ190" s="3"/>
+      <c r="BK190" s="3"/>
+      <c r="BL190" s="3"/>
+      <c r="BM190" s="3"/>
+    </row>
+    <row r="191" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -14301,8 +15221,12 @@
       <c r="BG191" s="3"/>
       <c r="BH191" s="3"/>
       <c r="BI191" s="3"/>
-    </row>
-    <row r="192" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ191" s="3"/>
+      <c r="BK191" s="3"/>
+      <c r="BL191" s="3"/>
+      <c r="BM191" s="3"/>
+    </row>
+    <row r="192" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -14362,8 +15286,12 @@
       <c r="BG192" s="3"/>
       <c r="BH192" s="3"/>
       <c r="BI192" s="3"/>
-    </row>
-    <row r="193" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ192" s="3"/>
+      <c r="BK192" s="3"/>
+      <c r="BL192" s="3"/>
+      <c r="BM192" s="3"/>
+    </row>
+    <row r="193" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -14423,8 +15351,12 @@
       <c r="BG193" s="3"/>
       <c r="BH193" s="3"/>
       <c r="BI193" s="3"/>
-    </row>
-    <row r="194" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ193" s="3"/>
+      <c r="BK193" s="3"/>
+      <c r="BL193" s="3"/>
+      <c r="BM193" s="3"/>
+    </row>
+    <row r="194" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -14484,8 +15416,12 @@
       <c r="BG194" s="3"/>
       <c r="BH194" s="3"/>
       <c r="BI194" s="3"/>
-    </row>
-    <row r="195" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ194" s="3"/>
+      <c r="BK194" s="3"/>
+      <c r="BL194" s="3"/>
+      <c r="BM194" s="3"/>
+    </row>
+    <row r="195" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -14545,8 +15481,12 @@
       <c r="BG195" s="3"/>
       <c r="BH195" s="3"/>
       <c r="BI195" s="3"/>
-    </row>
-    <row r="196" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ195" s="3"/>
+      <c r="BK195" s="3"/>
+      <c r="BL195" s="3"/>
+      <c r="BM195" s="3"/>
+    </row>
+    <row r="196" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -14606,8 +15546,12 @@
       <c r="BG196" s="3"/>
       <c r="BH196" s="3"/>
       <c r="BI196" s="3"/>
-    </row>
-    <row r="197" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ196" s="3"/>
+      <c r="BK196" s="3"/>
+      <c r="BL196" s="3"/>
+      <c r="BM196" s="3"/>
+    </row>
+    <row r="197" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -14667,8 +15611,12 @@
       <c r="BG197" s="3"/>
       <c r="BH197" s="3"/>
       <c r="BI197" s="3"/>
-    </row>
-    <row r="198" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ197" s="3"/>
+      <c r="BK197" s="3"/>
+      <c r="BL197" s="3"/>
+      <c r="BM197" s="3"/>
+    </row>
+    <row r="198" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -14728,8 +15676,12 @@
       <c r="BG198" s="3"/>
       <c r="BH198" s="3"/>
       <c r="BI198" s="3"/>
-    </row>
-    <row r="199" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ198" s="3"/>
+      <c r="BK198" s="3"/>
+      <c r="BL198" s="3"/>
+      <c r="BM198" s="3"/>
+    </row>
+    <row r="199" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -14789,8 +15741,12 @@
       <c r="BG199" s="3"/>
       <c r="BH199" s="3"/>
       <c r="BI199" s="3"/>
-    </row>
-    <row r="200" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ199" s="3"/>
+      <c r="BK199" s="3"/>
+      <c r="BL199" s="3"/>
+      <c r="BM199" s="3"/>
+    </row>
+    <row r="200" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -14850,8 +15806,12 @@
       <c r="BG200" s="3"/>
       <c r="BH200" s="3"/>
       <c r="BI200" s="3"/>
-    </row>
-    <row r="201" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ200" s="3"/>
+      <c r="BK200" s="3"/>
+      <c r="BL200" s="3"/>
+      <c r="BM200" s="3"/>
+    </row>
+    <row r="201" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -14911,8 +15871,12 @@
       <c r="BG201" s="3"/>
       <c r="BH201" s="3"/>
       <c r="BI201" s="3"/>
-    </row>
-    <row r="202" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ201" s="3"/>
+      <c r="BK201" s="3"/>
+      <c r="BL201" s="3"/>
+      <c r="BM201" s="3"/>
+    </row>
+    <row r="202" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -14972,8 +15936,12 @@
       <c r="BG202" s="3"/>
       <c r="BH202" s="3"/>
       <c r="BI202" s="3"/>
-    </row>
-    <row r="203" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ202" s="3"/>
+      <c r="BK202" s="3"/>
+      <c r="BL202" s="3"/>
+      <c r="BM202" s="3"/>
+    </row>
+    <row r="203" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -15033,8 +16001,12 @@
       <c r="BG203" s="3"/>
       <c r="BH203" s="3"/>
       <c r="BI203" s="3"/>
-    </row>
-    <row r="204" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ203" s="3"/>
+      <c r="BK203" s="3"/>
+      <c r="BL203" s="3"/>
+      <c r="BM203" s="3"/>
+    </row>
+    <row r="204" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -15094,8 +16066,12 @@
       <c r="BG204" s="3"/>
       <c r="BH204" s="3"/>
       <c r="BI204" s="3"/>
-    </row>
-    <row r="205" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ204" s="3"/>
+      <c r="BK204" s="3"/>
+      <c r="BL204" s="3"/>
+      <c r="BM204" s="3"/>
+    </row>
+    <row r="205" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -15155,8 +16131,12 @@
       <c r="BG205" s="3"/>
       <c r="BH205" s="3"/>
       <c r="BI205" s="3"/>
-    </row>
-    <row r="206" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ205" s="3"/>
+      <c r="BK205" s="3"/>
+      <c r="BL205" s="3"/>
+      <c r="BM205" s="3"/>
+    </row>
+    <row r="206" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -15216,8 +16196,12 @@
       <c r="BG206" s="3"/>
       <c r="BH206" s="3"/>
       <c r="BI206" s="3"/>
-    </row>
-    <row r="207" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ206" s="3"/>
+      <c r="BK206" s="3"/>
+      <c r="BL206" s="3"/>
+      <c r="BM206" s="3"/>
+    </row>
+    <row r="207" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -15277,8 +16261,12 @@
       <c r="BG207" s="3"/>
       <c r="BH207" s="3"/>
       <c r="BI207" s="3"/>
-    </row>
-    <row r="208" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ207" s="3"/>
+      <c r="BK207" s="3"/>
+      <c r="BL207" s="3"/>
+      <c r="BM207" s="3"/>
+    </row>
+    <row r="208" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -15338,8 +16326,12 @@
       <c r="BG208" s="3"/>
       <c r="BH208" s="3"/>
       <c r="BI208" s="3"/>
-    </row>
-    <row r="209" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ208" s="3"/>
+      <c r="BK208" s="3"/>
+      <c r="BL208" s="3"/>
+      <c r="BM208" s="3"/>
+    </row>
+    <row r="209" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -15399,8 +16391,12 @@
       <c r="BG209" s="3"/>
       <c r="BH209" s="3"/>
       <c r="BI209" s="3"/>
-    </row>
-    <row r="210" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ209" s="3"/>
+      <c r="BK209" s="3"/>
+      <c r="BL209" s="3"/>
+      <c r="BM209" s="3"/>
+    </row>
+    <row r="210" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -15460,8 +16456,12 @@
       <c r="BG210" s="3"/>
       <c r="BH210" s="3"/>
       <c r="BI210" s="3"/>
-    </row>
-    <row r="211" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ210" s="3"/>
+      <c r="BK210" s="3"/>
+      <c r="BL210" s="3"/>
+      <c r="BM210" s="3"/>
+    </row>
+    <row r="211" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -15521,8 +16521,12 @@
       <c r="BG211" s="3"/>
       <c r="BH211" s="3"/>
       <c r="BI211" s="3"/>
-    </row>
-    <row r="212" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ211" s="3"/>
+      <c r="BK211" s="3"/>
+      <c r="BL211" s="3"/>
+      <c r="BM211" s="3"/>
+    </row>
+    <row r="212" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -15582,8 +16586,12 @@
       <c r="BG212" s="3"/>
       <c r="BH212" s="3"/>
       <c r="BI212" s="3"/>
-    </row>
-    <row r="213" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ212" s="3"/>
+      <c r="BK212" s="3"/>
+      <c r="BL212" s="3"/>
+      <c r="BM212" s="3"/>
+    </row>
+    <row r="213" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -15643,8 +16651,12 @@
       <c r="BG213" s="3"/>
       <c r="BH213" s="3"/>
       <c r="BI213" s="3"/>
-    </row>
-    <row r="214" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ213" s="3"/>
+      <c r="BK213" s="3"/>
+      <c r="BL213" s="3"/>
+      <c r="BM213" s="3"/>
+    </row>
+    <row r="214" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -15704,8 +16716,12 @@
       <c r="BG214" s="3"/>
       <c r="BH214" s="3"/>
       <c r="BI214" s="3"/>
-    </row>
-    <row r="215" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ214" s="3"/>
+      <c r="BK214" s="3"/>
+      <c r="BL214" s="3"/>
+      <c r="BM214" s="3"/>
+    </row>
+    <row r="215" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -15765,8 +16781,12 @@
       <c r="BG215" s="3"/>
       <c r="BH215" s="3"/>
       <c r="BI215" s="3"/>
-    </row>
-    <row r="216" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ215" s="3"/>
+      <c r="BK215" s="3"/>
+      <c r="BL215" s="3"/>
+      <c r="BM215" s="3"/>
+    </row>
+    <row r="216" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -15826,8 +16846,12 @@
       <c r="BG216" s="3"/>
       <c r="BH216" s="3"/>
       <c r="BI216" s="3"/>
-    </row>
-    <row r="217" spans="3:61" x14ac:dyDescent="0.2">
+      <c r="BJ216" s="3"/>
+      <c r="BK216" s="3"/>
+      <c r="BL216" s="3"/>
+      <c r="BM216" s="3"/>
+    </row>
+    <row r="217" spans="3:65" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -15887,6 +16911,10 @@
       <c r="BG217" s="3"/>
       <c r="BH217" s="3"/>
       <c r="BI217" s="3"/>
+      <c r="BJ217" s="3"/>
+      <c r="BK217" s="3"/>
+      <c r="BL217" s="3"/>
+      <c r="BM217" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/BOSS.DE.xlsx
+++ b/BOSS.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0933E8-840F-45A4-A0F5-165ACB6F5D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCE706E-395A-4920-8BB5-82D17064A171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{09B18DE7-4EEF-4A72-AC57-80486CCDDA74}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{09B18DE7-4EEF-4A72-AC57-80486CCDDA74}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
   <si>
     <t>Hugo Boss</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>Asia Pacific Stores</t>
-  </si>
-  <si>
-    <t>Boss Meanswear</t>
   </si>
   <si>
     <t>Boss Womenswear</t>
@@ -323,6 +320,9 @@
   <si>
     <t>n.a.</t>
   </si>
+  <si>
+    <t>BOSS</t>
+  </si>
 </sst>
 </file>
 
@@ -331,13 +331,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -394,12 +406,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -420,34 +426,44 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -473,16 +489,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>42862</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -497,7 +513,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10463212" y="0"/>
+          <a:off x="11110912" y="47625"/>
           <a:ext cx="14287" cy="8201025"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -878,7 +894,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>35.700000000000003</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -886,9 +902,9 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>69.016170000000002</v>
-      </c>
-      <c r="K3" s="15" t="s">
+        <v>69.016166999999996</v>
+      </c>
+      <c r="K3" s="21" t="s">
         <v>81</v>
       </c>
     </row>
@@ -901,7 +917,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>2463.8772690000001</v>
+        <v>2618.4733759799997</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -912,9 +928,9 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>314</v>
-      </c>
-      <c r="K5" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="K5" s="21" t="s">
         <v>81</v>
       </c>
     </row>
@@ -923,9 +939,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>297</v>
-      </c>
-      <c r="K6" s="15" t="s">
+        <f>34+145</f>
+        <v>179</v>
+      </c>
+      <c r="K6" s="21" t="s">
         <v>81</v>
       </c>
     </row>
@@ -935,12 +952,12 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>2446.8772690000001</v>
+        <v>2566.4733759799997</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J9" s="2">
         <v>1924</v>
@@ -948,7 +965,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3">
         <v>18376</v>
@@ -956,21 +973,21 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1022,49 +1039,49 @@
         <v>18</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="O2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="Q2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="R2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="R2" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="T2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="Y2" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="Z2" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.2">
@@ -1120,7 +1137,9 @@
       <c r="O3" s="7">
         <v>522</v>
       </c>
-      <c r="P3" s="7"/>
+      <c r="P3" s="7">
+        <v>517</v>
+      </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
@@ -1214,13 +1233,15 @@
         <v>559</v>
       </c>
       <c r="N4" s="7">
-        <f t="shared" ref="N4:O7" si="1">+Z4</f>
+        <f t="shared" ref="N4:N7" si="1">+Z4</f>
         <v>558</v>
       </c>
       <c r="O4" s="7">
         <v>531</v>
       </c>
-      <c r="P4" s="7"/>
+      <c r="P4" s="7">
+        <v>532</v>
+      </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -1320,7 +1341,9 @@
       <c r="O5" s="7">
         <v>353</v>
       </c>
-      <c r="P5" s="7"/>
+      <c r="P5" s="7">
+        <v>346</v>
+      </c>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -1370,7 +1393,7 @@
     <row r="6" spans="1:51" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="8">
         <v>1418</v>
@@ -1416,7 +1439,10 @@
         <f>+SUM(O3:O5)</f>
         <v>1406</v>
       </c>
-      <c r="P6" s="8"/>
+      <c r="P6" s="8">
+        <f>+SUM(P3:P5)</f>
+        <v>1395</v>
+      </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
@@ -1464,7 +1490,7 @@
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B7" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="7">
         <v>489</v>
@@ -1507,7 +1533,9 @@
       <c r="O7" s="7">
         <v>470</v>
       </c>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7">
+        <v>464</v>
+      </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -1655,8 +1683,8 @@
       <c r="AY9" s="7"/>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="B10" s="2" t="s">
-        <v>35</v>
+      <c r="B10" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="C10" s="7">
         <v>746</v>
@@ -1668,7 +1696,7 @@
         <v>786</v>
       </c>
       <c r="F10" s="7">
-        <f>+X10-SUM(C10:E10)</f>
+        <f t="shared" ref="F10:F21" si="2">+X10-SUM(C10:E10)</f>
         <v>914</v>
       </c>
       <c r="G10" s="7">
@@ -1681,7 +1709,7 @@
         <v>785</v>
       </c>
       <c r="J10" s="7">
-        <f>+Y10-SUM(G10:I10)</f>
+        <f t="shared" ref="J10:J21" si="3">+Y10-SUM(G10:I10)</f>
         <v>973</v>
       </c>
       <c r="K10" s="7">
@@ -1694,13 +1722,15 @@
         <v>764</v>
       </c>
       <c r="N10" s="7">
-        <f>+Z10-SUM(K10:M10)</f>
+        <f t="shared" ref="N10:N21" si="4">+Z10-SUM(K10:M10)</f>
         <v>1008</v>
       </c>
       <c r="O10" s="7">
         <v>779</v>
       </c>
-      <c r="P10" s="7"/>
+      <c r="P10" s="7">
+        <v>792</v>
+      </c>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
@@ -1747,7 +1777,7 @@
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="7">
         <v>67</v>
@@ -1759,7 +1789,7 @@
         <v>73</v>
       </c>
       <c r="F11" s="7">
-        <f>+X11-SUM(C11:E11)</f>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="G11" s="7">
@@ -1772,7 +1802,7 @@
         <v>74</v>
       </c>
       <c r="J11" s="7">
-        <f>+Y11-SUM(G11:I11)</f>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="K11" s="7">
@@ -1785,13 +1815,15 @@
         <v>67</v>
       </c>
       <c r="N11" s="7">
-        <f>+Z11-SUM(K11:M11)</f>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="7"/>
+        <v>84</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>84</v>
+      </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
@@ -1838,7 +1870,7 @@
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7">
         <v>155</v>
@@ -1850,7 +1882,7 @@
         <v>169</v>
       </c>
       <c r="F12" s="7">
-        <f>+X12-SUM(C12:E12)</f>
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
       <c r="G12" s="7">
@@ -1863,7 +1895,7 @@
         <v>171</v>
       </c>
       <c r="J12" s="7">
-        <f>+Y12-SUM(G12:I12)</f>
+        <f t="shared" si="3"/>
         <v>192</v>
       </c>
       <c r="K12" s="7">
@@ -1876,13 +1908,15 @@
         <v>158</v>
       </c>
       <c r="N12" s="7">
-        <f>+Z12-SUM(K12:M12)</f>
+        <f t="shared" si="4"/>
         <v>191</v>
       </c>
       <c r="O12" s="7">
         <v>125</v>
       </c>
-      <c r="P12" s="7"/>
+      <c r="P12" s="7">
+        <v>113</v>
+      </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
@@ -1929,7 +1963,7 @@
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="7">
         <v>609</v>
@@ -1941,7 +1975,7 @@
         <v>653</v>
       </c>
       <c r="F13" s="7">
-        <f>+X13-SUM(C13:E13)</f>
+        <f t="shared" si="2"/>
         <v>680</v>
       </c>
       <c r="G13" s="7">
@@ -1954,7 +1988,7 @@
         <v>662</v>
       </c>
       <c r="J13" s="7">
-        <f>+Y13-SUM(G13:I13)</f>
+        <f t="shared" si="3"/>
         <v>725</v>
       </c>
       <c r="K13" s="7">
@@ -1967,13 +2001,15 @@
         <v>641</v>
       </c>
       <c r="N13" s="7">
-        <f>+Z13-SUM(K13:M13)</f>
+        <f t="shared" si="4"/>
         <v>878.16200000000026</v>
       </c>
       <c r="O13" s="7">
         <v>568</v>
       </c>
-      <c r="P13" s="7"/>
+      <c r="P13" s="7">
+        <v>532</v>
+      </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
@@ -2021,7 +2057,7 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="7">
         <v>195</v>
@@ -2033,7 +2069,7 @@
         <v>228</v>
       </c>
       <c r="F14" s="7">
-        <f>+X14-SUM(C14:E14)</f>
+        <f t="shared" si="2"/>
         <v>296</v>
       </c>
       <c r="G14" s="7">
@@ -2046,7 +2082,7 @@
         <v>228</v>
       </c>
       <c r="J14" s="7">
-        <f>+Y14-SUM(G14:I14)</f>
+        <f t="shared" si="3"/>
         <v>324</v>
       </c>
       <c r="K14" s="7">
@@ -2059,13 +2095,15 @@
         <v>223</v>
       </c>
       <c r="N14" s="7">
-        <f>+Z14-SUM(K14:M14)</f>
+        <f t="shared" si="4"/>
         <v>321.70000000000005</v>
       </c>
       <c r="O14" s="7">
         <v>188</v>
       </c>
-      <c r="P14" s="7"/>
+      <c r="P14" s="7">
+        <v>236</v>
+      </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
@@ -2113,7 +2151,7 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="7">
         <v>141</v>
@@ -2125,7 +2163,7 @@
         <v>120</v>
       </c>
       <c r="F15" s="7">
-        <f>+X15-SUM(C15:E15)</f>
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="G15" s="7">
@@ -2138,7 +2176,7 @@
         <v>110</v>
       </c>
       <c r="J15" s="7">
-        <f>+Y15-SUM(G15:I15)</f>
+        <f t="shared" si="3"/>
         <v>170</v>
       </c>
       <c r="K15" s="7">
@@ -2151,13 +2189,15 @@
         <v>101</v>
       </c>
       <c r="N15" s="7">
-        <f>+Z15-SUM(K15:M15)</f>
+        <f t="shared" si="4"/>
         <v>153.97500000000002</v>
       </c>
       <c r="O15" s="7">
         <v>123</v>
       </c>
-      <c r="P15" s="7"/>
+      <c r="P15" s="7">
+        <v>116</v>
+      </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
@@ -2205,7 +2245,7 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="7">
         <v>485</v>
@@ -2217,7 +2257,7 @@
         <v>521</v>
       </c>
       <c r="F16" s="7">
-        <f>+X16-SUM(C16:E16)</f>
+        <f t="shared" si="2"/>
         <v>676</v>
       </c>
       <c r="G16" s="7">
@@ -2230,7 +2270,7 @@
         <v>499</v>
       </c>
       <c r="J16" s="7">
-        <f>+Y16-SUM(G16:I16)</f>
+        <f t="shared" si="3"/>
         <v>687.32400000000007</v>
       </c>
       <c r="K16" s="7">
@@ -2243,13 +2283,15 @@
         <v>483</v>
       </c>
       <c r="N16" s="7">
-        <f>+Z16-SUM(K16:M16)</f>
+        <f t="shared" si="4"/>
         <v>669.26200000000017</v>
       </c>
       <c r="O16" s="7">
         <v>510</v>
       </c>
-      <c r="P16" s="7"/>
+      <c r="P16" s="7">
+        <v>56</v>
+      </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
@@ -2296,7 +2338,7 @@
     </row>
     <row r="17" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="7">
         <v>282</v>
@@ -2308,7 +2350,7 @@
         <v>293</v>
       </c>
       <c r="F17" s="7">
-        <f>+X17-SUM(C17:E17)</f>
+        <f t="shared" si="2"/>
         <v>234</v>
       </c>
       <c r="G17" s="7">
@@ -2321,7 +2363,7 @@
         <v>302</v>
       </c>
       <c r="J17" s="7">
-        <f>+Y17-SUM(G17:I17)</f>
+        <f t="shared" si="3"/>
         <v>270.00700000000006</v>
       </c>
       <c r="K17" s="7">
@@ -2334,13 +2376,15 @@
         <v>281</v>
       </c>
       <c r="N17" s="7">
-        <f>+Z17-SUM(K17:M17)</f>
+        <f t="shared" si="4"/>
         <v>294.38000000000011</v>
       </c>
       <c r="O17" s="7">
         <v>369</v>
       </c>
-      <c r="P17" s="7"/>
+      <c r="P17" s="7">
+        <v>320</v>
+      </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
@@ -2387,7 +2431,7 @@
     </row>
     <row r="18" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="7">
         <v>178</v>
@@ -2399,7 +2443,7 @@
         <v>187</v>
       </c>
       <c r="F18" s="7">
-        <f>+X18-SUM(C18:E18)</f>
+        <f t="shared" si="2"/>
         <v>237</v>
       </c>
       <c r="G18" s="7">
@@ -2412,7 +2456,7 @@
         <v>199</v>
       </c>
       <c r="J18" s="7">
-        <f>+Y18-SUM(G18:I18)</f>
+        <f t="shared" si="3"/>
         <v>262.95299999999997</v>
       </c>
       <c r="K18" s="7">
@@ -2425,13 +2469,15 @@
         <v>201</v>
       </c>
       <c r="N18" s="7">
-        <f>+Z18-SUM(K18:M18)</f>
+        <f t="shared" si="4"/>
         <v>286.65200000000004</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="P18" s="7"/>
+        <v>84</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
@@ -2478,7 +2524,7 @@
     </row>
     <row r="19" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="7">
         <v>23</v>
@@ -2490,7 +2536,7 @@
         <v>26</v>
       </c>
       <c r="F19" s="7">
-        <f>+X19-SUM(C19:E19)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="G19" s="7">
@@ -2503,7 +2549,7 @@
         <v>29</v>
       </c>
       <c r="J19" s="7">
-        <f>+Y19-SUM(G19:I19)</f>
+        <f t="shared" si="3"/>
         <v>31.064999999999998</v>
       </c>
       <c r="K19" s="7">
@@ -2516,13 +2562,15 @@
         <v>25</v>
       </c>
       <c r="N19" s="7">
-        <f>+Z19-SUM(K19:M19)</f>
+        <f t="shared" si="4"/>
         <v>28.543999999999997</v>
       </c>
       <c r="O19" s="7">
         <v>26</v>
       </c>
-      <c r="P19" s="7"/>
+      <c r="P19" s="7">
+        <v>21</v>
+      </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -2595,7 +2643,7 @@
         <v>1027</v>
       </c>
       <c r="F20" s="8">
-        <f>+X20-SUM(C20:E20)</f>
+        <f t="shared" si="2"/>
         <v>1176</v>
       </c>
       <c r="G20" s="8">
@@ -2608,7 +2656,7 @@
         <v>1029</v>
       </c>
       <c r="J20" s="8">
-        <f>+Y20-SUM(G20:I20)</f>
+        <f t="shared" si="3"/>
         <v>1249</v>
       </c>
       <c r="K20" s="8">
@@ -2621,13 +2669,15 @@
         <v>989</v>
       </c>
       <c r="N20" s="8">
-        <f>+Z20-SUM(K20:M20)</f>
+        <f t="shared" si="4"/>
         <v>1279.8379999999997</v>
       </c>
       <c r="O20" s="8">
         <v>905</v>
       </c>
-      <c r="P20" s="8"/>
+      <c r="P20" s="8">
+        <v>905</v>
+      </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="7"/>
@@ -2700,7 +2750,7 @@
         <v>404</v>
       </c>
       <c r="F21" s="7">
-        <f>+X21-SUM(C21:E21)</f>
+        <f t="shared" si="2"/>
         <v>453</v>
       </c>
       <c r="G21" s="7">
@@ -2713,7 +2763,7 @@
         <v>410</v>
       </c>
       <c r="J21" s="7">
-        <f>+Y21-SUM(G21:I21)</f>
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
       <c r="K21" s="7">
@@ -2726,13 +2776,15 @@
         <v>384</v>
       </c>
       <c r="N21" s="7">
-        <f>+Z21-SUM(K21:M21)</f>
+        <f t="shared" si="4"/>
         <v>501.45800000000008</v>
       </c>
       <c r="O21" s="7">
         <v>340</v>
       </c>
-      <c r="P21" s="7"/>
+      <c r="P21" s="7">
+        <v>318</v>
+      </c>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
@@ -2796,58 +2848,61 @@
         <v>21</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:H22" si="2">+C20-C21</f>
+        <f t="shared" ref="C22:H22" si="5">+C20-C21</f>
         <v>594</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>640</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>623</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>723</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>623</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>638</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" ref="I22:O22" si="3">+I20-I21</f>
+        <f t="shared" ref="I22:P22" si="6">+I20-I21</f>
         <v>619</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>779</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>613</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>630</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>605</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>778.37999999999965</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>565</v>
       </c>
-      <c r="P22" s="7"/>
+      <c r="P22" s="7">
+        <f t="shared" si="6"/>
+        <v>587</v>
+      </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
@@ -2956,7 +3011,9 @@
       <c r="O23" s="7">
         <v>410</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <v>409</v>
+      </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
@@ -3061,7 +3118,9 @@
       <c r="O24" s="7">
         <v>119</v>
       </c>
-      <c r="P24" s="7"/>
+      <c r="P24" s="7">
+        <v>119</v>
+      </c>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
@@ -3125,27 +3184,27 @@
         <v>24</v>
       </c>
       <c r="C25" s="7">
-        <f t="shared" ref="C25:H25" si="4">+C22-SUM(C23:C24)</f>
+        <f t="shared" ref="C25:H25" si="7">+C22-SUM(C23:C24)</f>
         <v>66</v>
       </c>
       <c r="D25" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>122</v>
       </c>
       <c r="E25" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>103</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>118</v>
       </c>
       <c r="G25" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>69</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>71</v>
       </c>
       <c r="I25" s="7">
@@ -3153,30 +3212,33 @@
         <v>95</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" ref="J25:O25" si="5">+J22-SUM(J23:J24)</f>
+        <f t="shared" ref="J25:P25" si="8">+J22-SUM(J23:J24)</f>
         <v>125</v>
       </c>
       <c r="K25" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
       <c r="L25" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>81</v>
       </c>
       <c r="M25" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="N25" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>152.7529999999997</v>
       </c>
       <c r="O25" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>36</v>
       </c>
-      <c r="P25" s="7"/>
+      <c r="P25" s="7">
+        <f t="shared" si="8"/>
+        <v>59</v>
+      </c>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
@@ -3285,7 +3347,9 @@
       <c r="O26" s="7">
         <v>-10</v>
       </c>
-      <c r="P26" s="7"/>
+      <c r="P26" s="7">
+        <v>-12</v>
+      </c>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
@@ -3349,27 +3413,27 @@
         <v>26</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" ref="C27:H27" si="6">+C25+C26</f>
+        <f t="shared" ref="C27:H27" si="9">+C25+C26</f>
         <v>54</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>88</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>104</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>57</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
       <c r="I27" s="7">
@@ -3377,30 +3441,33 @@
         <v>77</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" ref="J27:O27" si="7">+J25+J26</f>
+        <f t="shared" ref="J27:P27" si="10">+J25+J26</f>
         <v>112</v>
       </c>
       <c r="K27" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>53</v>
       </c>
       <c r="L27" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>69</v>
       </c>
       <c r="M27" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>83</v>
       </c>
       <c r="N27" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>139.85199999999969</v>
       </c>
       <c r="O27" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
-      <c r="P27" s="7"/>
+      <c r="P27" s="7">
+        <f t="shared" si="10"/>
+        <v>47</v>
+      </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -3509,7 +3576,9 @@
       <c r="O28" s="7">
         <v>7</v>
       </c>
-      <c r="P28" s="7"/>
+      <c r="P28" s="7">
+        <v>13</v>
+      </c>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
@@ -3573,27 +3642,27 @@
         <v>28</v>
       </c>
       <c r="C29" s="7">
-        <f t="shared" ref="C29:H29" si="8">+C27-C28</f>
+        <f t="shared" ref="C29:H29" si="11">+C27-C28</f>
         <v>39</v>
       </c>
       <c r="D29" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
       <c r="E29" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>63</v>
       </c>
       <c r="F29" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>87</v>
       </c>
       <c r="G29" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="I29" s="7">
@@ -3601,30 +3670,33 @@
         <v>55</v>
       </c>
       <c r="J29" s="7">
-        <f t="shared" ref="J29" si="9">+J27-J28</f>
+        <f t="shared" ref="J29" si="12">+J27-J28</f>
         <v>87</v>
       </c>
       <c r="K29" s="7">
-        <f>+K27-K28</f>
+        <f t="shared" ref="K29:P29" si="13">+K27-K28</f>
         <v>38</v>
       </c>
       <c r="L29" s="7">
-        <f>+L27-L28</f>
+        <f t="shared" si="13"/>
         <v>50</v>
       </c>
       <c r="M29" s="7">
-        <f>+M27-M28</f>
+        <f t="shared" si="13"/>
         <v>60</v>
       </c>
       <c r="N29" s="7">
-        <f>+N27-N28</f>
+        <f t="shared" si="13"/>
         <v>111.2849999999997</v>
       </c>
       <c r="O29" s="7">
-        <f>+O27-O28</f>
+        <f t="shared" si="13"/>
         <v>19</v>
       </c>
-      <c r="P29" s="7"/>
+      <c r="P29" s="7">
+        <f t="shared" si="13"/>
+        <v>34</v>
+      </c>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
@@ -3733,7 +3805,9 @@
       <c r="O30" s="16">
         <v>1</v>
       </c>
-      <c r="P30" s="7"/>
+      <c r="P30" s="7">
+        <v>1</v>
+      </c>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
@@ -3797,27 +3871,27 @@
         <v>30</v>
       </c>
       <c r="C31" s="7">
-        <f t="shared" ref="C31:H31" si="10">+C29-C30</f>
+        <f t="shared" ref="C31:H31" si="14">+C29-C30</f>
         <v>35</v>
       </c>
       <c r="D31" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>77</v>
       </c>
       <c r="E31" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>63</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>83</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="I31" s="7">
@@ -3825,30 +3899,33 @@
         <v>54</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" ref="J31" si="11">+J29-J30</f>
+        <f t="shared" ref="J31" si="15">+J29-J30</f>
         <v>83</v>
       </c>
       <c r="K31" s="7">
-        <f>+K29-K30</f>
+        <f t="shared" ref="K31:P31" si="16">+K29-K30</f>
         <v>36</v>
       </c>
       <c r="L31" s="7">
-        <f>+L29-L30</f>
+        <f t="shared" si="16"/>
         <v>47</v>
       </c>
       <c r="M31" s="7">
-        <f>+M29-M30</f>
+        <f t="shared" si="16"/>
         <v>59</v>
       </c>
       <c r="N31" s="7">
-        <f>+N29-N30</f>
+        <f t="shared" si="16"/>
         <v>107.47999999999971</v>
       </c>
       <c r="O31" s="7">
-        <f>+O29-O30</f>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
-      <c r="P31" s="7"/>
+      <c r="P31" s="7">
+        <f t="shared" si="16"/>
+        <v>33</v>
+      </c>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -3981,11 +4058,11 @@
         <v>31</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:D33" si="12">+C31/C34</f>
+        <f t="shared" ref="C33:D33" si="17">+C31/C34</f>
         <v>0.507127532576786</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1.1156805716689291</v>
       </c>
       <c r="E33" s="9">
@@ -3993,63 +4070,66 @@
         <v>0.9128295586382148</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" ref="F33:J33" si="13">+F31/F34</f>
+        <f t="shared" ref="F33:J33" si="18">+F31/F34</f>
         <v>1.2026167201106639</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>0.55059560679765329</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>0.55059560679765329</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>0.78242533597561259</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>1.2026167201106639</v>
       </c>
       <c r="K33" s="9">
-        <f>+K31/K34</f>
+        <f t="shared" ref="K33:P33" si="19">+K31/K34</f>
         <v>0.52161689065040839</v>
       </c>
       <c r="L33" s="9">
-        <f>+L31/L34</f>
+        <f t="shared" si="19"/>
         <v>0.6809998294602555</v>
       </c>
       <c r="M33" s="9">
-        <f>+M31/M34</f>
+        <f t="shared" si="19"/>
         <v>0.85487212634372489</v>
       </c>
       <c r="N33" s="9">
-        <f>+N31/N34</f>
+        <f t="shared" si="19"/>
         <v>1.5573162057529373</v>
       </c>
-      <c r="O33" s="9" t="e">
-        <f>+O31/O34</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P33" s="9"/>
+      <c r="O33" s="9">
+        <f t="shared" si="19"/>
+        <v>0.26080845666204561</v>
+      </c>
+      <c r="P33" s="9">
+        <f t="shared" si="19"/>
+        <v>0.47814883721375023</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="3"/>
       <c r="T33" s="9" t="e">
-        <f t="shared" ref="T33:W33" si="14">+T31/T34</f>
+        <f t="shared" ref="T33:W33" si="20">+T31/T34</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>3.0427651954607158</v>
       </c>
       <c r="X33" s="9">
@@ -4144,8 +4224,12 @@
       <c r="N34" s="3">
         <v>69.016170000000002</v>
       </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
+      <c r="O34" s="3">
+        <v>69.016166999999996</v>
+      </c>
+      <c r="P34" s="3">
+        <v>69.016166999999996</v>
+      </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
@@ -4275,71 +4359,74 @@
     </row>
     <row r="36" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="10">
-        <f t="shared" ref="G36:K37" si="15">+G6/C6-1</f>
+        <f t="shared" ref="G36:K37" si="21">+G6/C6-1</f>
         <v>5.6417489421720646E-3</v>
       </c>
       <c r="H36" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>5.0775740479548581E-2</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>4.6544428772919533E-2</v>
       </c>
       <c r="J36" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>8.0394922425952142E-2</v>
       </c>
       <c r="K36" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>6.5217391304347894E-2</v>
       </c>
       <c r="L36" s="10">
-        <f t="shared" ref="L36:M36" si="16">+L6/H6-1</f>
+        <f t="shared" ref="L36:M36" si="22">+L6/H6-1</f>
         <v>3.3557046979866278E-3</v>
       </c>
       <c r="M36" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>6.738544474393926E-4</v>
       </c>
       <c r="N36" s="10">
-        <f>+N6/J6-1</f>
+        <f t="shared" ref="N36:P37" si="23">+N6/J6-1</f>
         <v>-4.5691906005221883E-2</v>
       </c>
       <c r="O36" s="10">
-        <f>+O6/K6-1</f>
+        <f t="shared" si="23"/>
         <v>-7.4391046741277167E-2</v>
       </c>
-      <c r="P36" s="10"/>
+      <c r="P36" s="10">
+        <f t="shared" si="23"/>
+        <v>-6.6889632107023367E-2</v>
+      </c>
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="10" t="e">
-        <f t="shared" ref="U36:Y36" si="17">+U6/T6-1</f>
+        <f t="shared" ref="U36:Y36" si="24">+U6/T6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V36" s="10" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W36" s="10" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X36" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>7.7507598784194442E-2</v>
       </c>
       <c r="Y36" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>8.0394922425952142E-2</v>
       </c>
       <c r="Z36" s="10">
@@ -4388,71 +4475,74 @@
     </row>
     <row r="37" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>2.044989775051187E-3</v>
       </c>
       <c r="H37" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1.0224948875255713E-2</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>2.044989775051187E-3</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>2.249488752556239E-2</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>2.0408163265306145E-2</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" ref="L37:M37" si="18">+L7/H7-1</f>
+        <f t="shared" ref="L37:M37" si="25">+L7/H7-1</f>
         <v>-6.0728744939271273E-3</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-1.0204081632653073E-2</v>
       </c>
       <c r="N37" s="10">
-        <f>+N7/J7-1</f>
+        <f t="shared" si="23"/>
         <v>-3.0000000000000027E-2</v>
       </c>
       <c r="O37" s="10">
-        <f>+O7/K7-1</f>
+        <f t="shared" si="23"/>
         <v>-6.0000000000000053E-2</v>
       </c>
-      <c r="P37" s="10"/>
+      <c r="P37" s="10">
+        <f t="shared" si="23"/>
+        <v>-5.4989816700610983E-2</v>
+      </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="10" t="e">
-        <f t="shared" ref="U37:Y37" si="19">+U7/T7-1</f>
+        <f t="shared" ref="U37:Y37" si="26">+U7/T7-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V37" s="10" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W37" s="10" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X37" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>4.042553191489362E-2</v>
       </c>
       <c r="Y37" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>2.249488752556239E-2</v>
       </c>
       <c r="Z37" s="10">
@@ -4501,26 +4591,26 @@
     </row>
     <row r="38" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="10">
-        <f t="shared" ref="G38:J47" si="20">+G10/C10-1</f>
+        <f t="shared" ref="G38:J47" si="27">+G10/C10-1</f>
         <v>4.1554959785522705E-2</v>
       </c>
       <c r="H38" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-1.9753086419753041E-2</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-1.2722646310432406E-3</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>6.4551422319474749E-2</v>
       </c>
       <c r="K38" s="10">
@@ -4528,44 +4618,47 @@
         <v>-1.4157014157014203E-2</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" ref="L38:M48" si="21">+L10/H10-1</f>
+        <f t="shared" ref="L38:M48" si="28">+L10/H10-1</f>
         <v>1.7632241813602123E-2</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-2.6751592356687892E-2</v>
       </c>
       <c r="N38" s="10">
-        <f>+N10/J10-1</f>
+        <f t="shared" ref="N38:N48" si="29">+N10/J10-1</f>
         <v>3.5971223021582732E-2</v>
       </c>
       <c r="O38" s="10">
-        <f>+O10/K10-1</f>
+        <f t="shared" ref="O38:P48" si="30">+O10/K10-1</f>
         <v>1.6971279373368064E-2</v>
       </c>
-      <c r="P38" s="10"/>
+      <c r="P38" s="10">
+        <f t="shared" si="30"/>
+        <v>-1.980198019801982E-2</v>
+      </c>
       <c r="Q38" s="10"/>
       <c r="R38" s="10"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="10" t="e">
-        <f t="shared" ref="U38:Y48" si="22">+U10/T10-1</f>
+        <f t="shared" ref="U38:Y48" si="31">+U10/T10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V38" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W38" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X38" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.13528591352859132</v>
       </c>
       <c r="Y38" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>2.2420147420147529E-2</v>
       </c>
       <c r="Z38" s="10">
@@ -4614,75 +4707,76 @@
     </row>
     <row r="39" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>4.4776119402984982E-2</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1.4925373134328401E-2</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1.3698630136986356E-2</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>4.9382716049382713E-2</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" ref="K39:K47" si="23">+K11/G11-1</f>
+        <f t="shared" ref="K39:K47" si="32">+K11/G11-1</f>
         <v>0</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-8.8235294117647078E-2</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-9.4594594594594628E-2</v>
       </c>
       <c r="N39" s="10">
-        <f>+N11/J11-1</f>
+        <f t="shared" si="29"/>
         <v>-4.705882352941182E-2</v>
       </c>
-      <c r="O39" s="10" t="e">
-        <f>+O11/K11-1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P39" s="10"/>
+      <c r="O39" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="P39" s="20" t="s">
+        <v>84</v>
+      </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V39" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W39" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.20502092050209209</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>3.125E-2</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" ref="Z39:Z48" si="24">+Z11/Y11-1</f>
+        <f t="shared" ref="Z39:Z48" si="33">+Z11/Y11-1</f>
         <v>-5.7239057239057201E-2</v>
       </c>
       <c r="AA39" s="3"/>
@@ -4727,75 +4821,78 @@
     </row>
     <row r="40" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>7.7419354838709653E-2</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>2.7027027027026973E-2</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1.1834319526627279E-2</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>6.0773480662983381E-2</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>-2.39520958083832E-2</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-0.13157894736842102</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-7.6023391812865548E-2</v>
       </c>
       <c r="N40" s="10">
-        <f>+N12/J12-1</f>
+        <f t="shared" si="29"/>
         <v>-5.2083333333333703E-3</v>
       </c>
       <c r="O40" s="10">
-        <f>+O12/K12-1</f>
+        <f t="shared" si="30"/>
         <v>-0.23312883435582821</v>
       </c>
-      <c r="P40" s="10"/>
+      <c r="P40" s="10">
+        <f t="shared" si="30"/>
+        <v>-0.14393939393939392</v>
+      </c>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V40" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W40" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.19816513761467891</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>4.4410413476263511E-2</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-5.5718475073313734E-2</v>
       </c>
       <c r="AA40" s="3"/>
@@ -4840,75 +4937,78 @@
     </row>
     <row r="41" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>4.1050903119868698E-2</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-2.5806451612903181E-2</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1.3782542113323082E-2</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>6.6176470588235281E-2</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>-4.7318611987381409E-3</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>2.3178807947019875E-2</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-3.1722054380664666E-2</v>
       </c>
       <c r="N41" s="10">
-        <f>+N13/J13-1</f>
+        <f t="shared" si="29"/>
         <v>0.21125793103448309</v>
       </c>
       <c r="O41" s="10">
-        <f>+O13/K13-1</f>
+        <f t="shared" si="30"/>
         <v>-9.9841521394611776E-2</v>
       </c>
-      <c r="P41" s="10"/>
+      <c r="P41" s="10">
+        <f t="shared" si="30"/>
+        <v>-0.13915857605177995</v>
+      </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V41" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W41" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.11246200607902734</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>2.4590163934426146E-2</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>5.4537904761904787E-2</v>
       </c>
       <c r="AA41" s="3"/>
@@ -4953,75 +5053,78 @@
     </row>
     <row r="42" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.11794871794871797</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>5.9322033898305149E-2</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>9.4594594594594517E-2</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>-2.752293577981646E-2</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-5.600000000000005E-2</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-2.1929824561403466E-2</v>
       </c>
       <c r="N42" s="10">
-        <f>+N14/J14-1</f>
+        <f t="shared" si="29"/>
         <v>-7.0987654320986415E-3</v>
       </c>
       <c r="O42" s="10">
-        <f>+O14/K14-1</f>
+        <f t="shared" si="30"/>
         <v>-0.1132075471698113</v>
       </c>
-      <c r="P42" s="10"/>
+      <c r="P42" s="10">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V42" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W42" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.21039290240811148</v>
       </c>
       <c r="Y42" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>6.8062827225130906E-2</v>
       </c>
       <c r="Z42" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-2.6764705882352913E-2</v>
       </c>
       <c r="AA42" s="3"/>
@@ -5066,75 +5169,78 @@
     </row>
     <row r="43" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-1.4184397163120588E-2</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-6.944444444444442E-2</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-8.333333333333337E-2</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-5.8479532163743242E-3</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>-6.4748201438848962E-2</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-7.4626865671641784E-2</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-8.181818181818179E-2</v>
       </c>
       <c r="N43" s="10">
-        <f>+N15/J15-1</f>
+        <f t="shared" si="29"/>
         <v>-9.4264705882352806E-2</v>
       </c>
       <c r="O43" s="10">
-        <f>+O15/K15-1</f>
+        <f t="shared" si="30"/>
         <v>-5.3846153846153877E-2</v>
       </c>
-      <c r="P43" s="10"/>
+      <c r="P43" s="10">
+        <f t="shared" si="30"/>
+        <v>-6.4516129032258118E-2</v>
+      </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V43" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W43" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X43" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.23340471092077086</v>
       </c>
       <c r="Y43" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>-3.993055555555558E-2</v>
       </c>
       <c r="Z43" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-7.9611211573236806E-2</v>
       </c>
       <c r="AA43" s="3"/>
@@ -5179,75 +5285,78 @@
     </row>
     <row r="44" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1.4432989690721598E-2</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-2.931034482758621E-2</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-4.2226487523992273E-2</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1.6751479289941029E-2</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>-3.8617886178861749E-2</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-3.730017761989346E-2</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-3.2064128256513058E-2</v>
       </c>
       <c r="N44" s="10">
-        <f>+N16/J16-1</f>
+        <f t="shared" si="29"/>
         <v>-2.6278727354202558E-2</v>
       </c>
       <c r="O44" s="10">
-        <f>+O16/K16-1</f>
+        <f t="shared" si="30"/>
         <v>7.8224101479915431E-2</v>
       </c>
-      <c r="P44" s="10"/>
+      <c r="P44" s="10">
+        <f t="shared" si="30"/>
+        <v>-0.89667896678966785</v>
+      </c>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V44" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W44" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X44" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.12202380952380953</v>
       </c>
       <c r="Y44" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>-9.1405835543766356E-3</v>
       </c>
       <c r="Z44" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-3.3043861574676314E-2</v>
       </c>
       <c r="AA44" s="3"/>
@@ -5292,75 +5401,78 @@
     </row>
     <row r="45" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>7.4468085106383031E-2</v>
       </c>
       <c r="H45" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>5.3571428571428603E-2</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>3.0716723549488067E-2</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.15387606837606871</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>-2.3102310231023049E-2</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>4.237288135593209E-3</v>
       </c>
       <c r="M45" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-6.9536423841059625E-2</v>
       </c>
       <c r="N45" s="10">
-        <f>+N17/J17-1</f>
+        <f t="shared" si="29"/>
         <v>9.0268030088108908E-2</v>
       </c>
       <c r="O45" s="10">
-        <f>+O17/K17-1</f>
+        <f t="shared" si="30"/>
         <v>0.24662162162162171</v>
       </c>
-      <c r="P45" s="10"/>
+      <c r="P45" s="10">
+        <f t="shared" si="30"/>
+        <v>0.35021097046413496</v>
+      </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
       <c r="U45" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V45" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W45" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X45" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.15418994413407816</v>
       </c>
       <c r="Y45" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>7.5515004840271072E-2</v>
       </c>
       <c r="Z45" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-2.3645215556696852E-3</v>
       </c>
       <c r="AA45" s="3"/>
@@ -5405,75 +5517,76 @@
     </row>
     <row r="46" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>9.550561797752799E-2</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>-3.5714285714285698E-2</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>6.4171122994652441E-2</v>
       </c>
       <c r="J46" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.10950632911392399</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>4.6153846153846212E-2</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>5.2910052910053018E-2</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>1.0050251256281451E-2</v>
       </c>
       <c r="N46" s="10">
-        <f>+N18/J18-1</f>
+        <f t="shared" si="29"/>
         <v>9.0126372393545928E-2</v>
       </c>
-      <c r="O46" s="10" t="e">
-        <f>+O18/K18-1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P46" s="10"/>
+      <c r="O46" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="P46" s="20" t="s">
+        <v>84</v>
+      </c>
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V46" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W46" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X46" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.2314814814814814</v>
       </c>
       <c r="Y46" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>6.0091478696741918E-2</v>
       </c>
       <c r="Z46" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>5.2838632879131708E-2</v>
       </c>
       <c r="AA46" s="3"/>
@@ -5518,75 +5631,78 @@
     </row>
     <row r="47" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H47" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0.11538461538461542</v>
       </c>
       <c r="J47" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>7.1206896551724075E-2</v>
       </c>
       <c r="K47" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>0.13043478260869557</v>
       </c>
       <c r="L47" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-7.6923076923076872E-2</v>
       </c>
       <c r="M47" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-0.13793103448275867</v>
       </c>
       <c r="N47" s="10">
-        <f>+N19/J19-1</f>
+        <f t="shared" si="29"/>
         <v>-8.1152422340254327E-2</v>
       </c>
       <c r="O47" s="10">
-        <f>+O19/K19-1</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="P47" s="10"/>
+      <c r="P47" s="10">
+        <f t="shared" si="30"/>
+        <v>-0.125</v>
+      </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V47" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W47" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X47" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.13043478260869557</v>
       </c>
       <c r="Y47" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>4.8701923076923004E-2</v>
       </c>
       <c r="Z47" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-5.0621189199101413E-2</v>
       </c>
       <c r="AA47" s="3"/>
@@ -5631,18 +5747,18 @@
     </row>
     <row r="48" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="12">
-        <f t="shared" ref="G48:H48" si="25">+G20/C20-1</f>
+        <f t="shared" ref="G48:H48" si="34">+G20/C20-1</f>
         <v>4.7520661157024691E-2</v>
       </c>
       <c r="H48" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="34"/>
         <v>-1.0721247563352798E-2</v>
       </c>
       <c r="I48" s="12">
@@ -5650,56 +5766,59 @@
         <v>1.9474196689386325E-3</v>
       </c>
       <c r="J48" s="12">
-        <f t="shared" ref="J48:K48" si="26">+J20/F20-1</f>
+        <f t="shared" ref="J48:K48" si="35">+J20/F20-1</f>
         <v>6.2074829931972886E-2</v>
       </c>
       <c r="K48" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>-1.4792899408283988E-2</v>
       </c>
       <c r="L48" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-1.2807881773398977E-2</v>
       </c>
       <c r="M48" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>-3.8872691933916403E-2</v>
       </c>
       <c r="N48" s="12">
-        <f>+N20/J20-1</f>
+        <f t="shared" si="29"/>
         <v>2.4690152121697118E-2</v>
       </c>
       <c r="O48" s="12">
-        <f>+O20/K20-1</f>
+        <f t="shared" si="30"/>
         <v>-9.4094094094094083E-2</v>
       </c>
-      <c r="P48" s="12"/>
+      <c r="P48" s="12">
+        <f t="shared" si="30"/>
+        <v>-9.6806387225548907E-2</v>
+      </c>
       <c r="Q48" s="12"/>
       <c r="R48" s="12"/>
       <c r="S48" s="11"/>
       <c r="T48" s="11"/>
       <c r="U48" s="12" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V48" s="12" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W48" s="12" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X48" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>0.14954806902218576</v>
       </c>
       <c r="Y48" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>2.6209197045508725E-2</v>
       </c>
       <c r="Z48" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>-8.6282795449269534E-3</v>
       </c>
       <c r="AA48" s="11"/>
@@ -5744,30 +5863,30 @@
     </row>
     <row r="49" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" ref="C49:H49" si="27">+C22/C20</f>
+        <f t="shared" ref="C49:H49" si="36">+C22/C20</f>
         <v>0.61363636363636365</v>
       </c>
       <c r="D49" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.62378167641325533</v>
       </c>
       <c r="E49" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.60662122687439146</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.61479591836734693</v>
       </c>
       <c r="G49" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.61439842209072981</v>
       </c>
       <c r="H49" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.62857142857142856</v>
       </c>
       <c r="I49" s="10">
@@ -5783,39 +5902,42 @@
         <v>0.61361361361361366</v>
       </c>
       <c r="L49" s="10">
-        <f t="shared" ref="L49:N49" si="28">+L22/L20</f>
+        <f t="shared" ref="L49:N49" si="37">+L22/L20</f>
         <v>0.62874251497005984</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.61172901921132461</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.60818634858474263</v>
       </c>
       <c r="O49" s="10">
-        <f t="shared" ref="O49" si="29">+O22/O20</f>
+        <f t="shared" ref="O49:P49" si="38">+O22/O20</f>
         <v>0.62430939226519333</v>
       </c>
-      <c r="P49" s="10"/>
+      <c r="P49" s="10">
+        <f t="shared" si="38"/>
+        <v>0.64861878453038679</v>
+      </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
       <c r="S49" s="3"/>
       <c r="T49" s="10" t="e">
-        <f t="shared" ref="T49:W49" si="30">+T22/T20</f>
+        <f t="shared" ref="T49:W49" si="39">+T22/T20</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U49" s="10" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V49" s="10" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W49" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.61791290057518489</v>
       </c>
       <c r="X49" s="10">
@@ -5872,30 +5994,30 @@
     </row>
     <row r="50" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" ref="C50:H50" si="31">+C25/C20</f>
+        <f t="shared" ref="C50:H50" si="40">+C25/C20</f>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0.1189083820662768</v>
       </c>
       <c r="E50" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0.10029211295034079</v>
       </c>
       <c r="F50" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>0.10034013605442177</v>
       </c>
       <c r="G50" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>6.8047337278106509E-2</v>
       </c>
       <c r="H50" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="40"/>
         <v>6.9950738916256153E-2</v>
       </c>
       <c r="I50" s="10">
@@ -5911,39 +6033,42 @@
         <v>6.2062062062062065E-2</v>
       </c>
       <c r="L50" s="10">
-        <f t="shared" ref="L50:N50" si="32">+L25/L20</f>
+        <f t="shared" ref="L50:N50" si="41">+L25/L20</f>
         <v>8.0838323353293412E-2</v>
       </c>
       <c r="M50" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="41"/>
         <v>9.6056622851365014E-2</v>
       </c>
       <c r="N50" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="41"/>
         <v>0.11935338691303098</v>
       </c>
       <c r="O50" s="10">
-        <f t="shared" ref="O50" si="33">+O25/O20</f>
+        <f t="shared" ref="O50:P50" si="42">+O25/O20</f>
         <v>3.9779005524861875E-2</v>
       </c>
-      <c r="P50" s="10"/>
+      <c r="P50" s="10">
+        <f t="shared" si="42"/>
+        <v>6.5193370165745862E-2</v>
+      </c>
       <c r="Q50" s="10"/>
       <c r="R50" s="10"/>
       <c r="S50" s="3"/>
       <c r="T50" s="10" t="e">
-        <f t="shared" ref="T50:W50" si="34">+T25/T20</f>
+        <f t="shared" ref="T50:W50" si="43">+T25/T20</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U50" s="10" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V50" s="10" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W50" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="43"/>
         <v>9.1755683374417973E-2</v>
       </c>
       <c r="X50" s="10">
@@ -6000,30 +6125,30 @@
     </row>
     <row r="51" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" ref="C51:H51" si="35">+C28/C27</f>
+        <f t="shared" ref="C51:H51" si="44">+C28/C27</f>
         <v>0.27777777777777779</v>
       </c>
       <c r="D51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="E51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>0.28409090909090912</v>
       </c>
       <c r="F51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>0.16346153846153846</v>
       </c>
       <c r="G51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>0.2807017543859649</v>
       </c>
       <c r="H51" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="44"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="I51" s="10">
@@ -6039,39 +6164,42 @@
         <v>0.28301886792452829</v>
       </c>
       <c r="L51" s="10">
-        <f t="shared" ref="L51:N51" si="36">+L28/L27</f>
+        <f t="shared" ref="L51:N51" si="45">+L28/L27</f>
         <v>0.27536231884057971</v>
       </c>
       <c r="M51" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.27710843373493976</v>
       </c>
       <c r="N51" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.20426593827760817</v>
       </c>
       <c r="O51" s="10">
-        <f t="shared" ref="O51" si="37">+O28/O27</f>
+        <f t="shared" ref="O51:P51" si="46">+O28/O27</f>
         <v>0.26923076923076922</v>
       </c>
-      <c r="P51" s="10"/>
+      <c r="P51" s="10">
+        <f t="shared" si="46"/>
+        <v>0.27659574468085107</v>
+      </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
       <c r="S51" s="3"/>
       <c r="T51" s="10" t="e">
-        <f t="shared" ref="T51:W51" si="38">+T28/T27</f>
+        <f t="shared" ref="T51:W51" si="47">+T28/T27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U51" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V51" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W51" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="47"/>
         <v>0.22105263157894736</v>
       </c>
       <c r="X51" s="10">
